--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡발주양식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46EB5818-0D2D-4EA1-A74F-54F9A3BFE8AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12AC87F2-CBCA-47FA-B2F6-220B496DD950}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="1177">
   <si>
     <t>주문상품</t>
   </si>
@@ -3562,6 +3562,31 @@
   </si>
   <si>
     <t>A02753</t>
+  </si>
+  <si>
+    <t>오아몬스터퀵케이블-비타오렌지</t>
+  </si>
+  <si>
+    <t>오아몬스터퀵케이블-포그밀크</t>
+  </si>
+  <si>
+    <t>A03150</t>
+  </si>
+  <si>
+    <t>A03151</t>
+  </si>
+  <si>
+    <t>보아르모노반자동커피머신-화이트</t>
+  </si>
+  <si>
+    <t>A02926</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보아르슈트쏙의류관리기-화이트</t>
+  </si>
+  <si>
+    <t>A02634</t>
   </si>
 </sst>
 </file>
@@ -4356,7 +4381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.625" bestFit="1" customWidth="1"/>
@@ -4403,15 +4428,15 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>'sku 정보'!$G2</f>
-        <v>오아커버넥마사지기-베이지</v>
+        <v>오아플라이트-화이트</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>'sku 정보'!$H2</f>
-        <v>A00959</v>
+        <v>L0031</v>
       </c>
       <c r="C2">
         <f>'sku 정보'!$I2</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -4427,25 +4452,25 @@
       </c>
       <c r="J2">
         <f>'sku 정보'!$J2</f>
-        <v>58826</v>
+        <v>21320</v>
       </c>
       <c r="K2">
         <f>$J2*$C2</f>
-        <v>529434</v>
+        <v>341120</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>'sku 정보'!$G3</f>
-        <v>보아르스위프클링전용필터</v>
+        <v>오아무드센서등</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>'sku 정보'!$H3</f>
-        <v>M00313</v>
+        <v>L0080</v>
       </c>
       <c r="C3">
         <f>'sku 정보'!$I3</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -4461,25 +4486,25 @@
       </c>
       <c r="J3">
         <f>'sku 정보'!$J3</f>
-        <v>3283</v>
+        <v>14088</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K17" si="0">$J3*$C3</f>
-        <v>32830</v>
+        <f t="shared" ref="K3:K8" si="0">$J3*$C3</f>
+        <v>197232</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>'sku 정보'!$G4</f>
-        <v>오아슬림에어드라이기-블랙</v>
+        <v>오아모던LED시계R</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>'sku 정보'!$H4</f>
-        <v>A01146</v>
+        <v>C0466</v>
       </c>
       <c r="C4">
         <f>'sku 정보'!$I4</f>
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -4495,25 +4520,25 @@
       </c>
       <c r="J4">
         <f>'sku 정보'!$J4</f>
-        <v>39396</v>
+        <v>48685</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>275772</v>
+        <v>1460550</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>'sku 정보'!$G5</f>
-        <v>오아아이스볼트맥스-베이지</v>
+        <v>오아모던LED시계S</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>'sku 정보'!$H5</f>
-        <v>A01593</v>
+        <v>C0467</v>
       </c>
       <c r="C5">
         <f>'sku 정보'!$I5</f>
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -4529,25 +4554,25 @@
       </c>
       <c r="J5">
         <f>'sku 정보'!$J5</f>
-        <v>19966</v>
+        <v>51935</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>519116</v>
+        <v>1038700</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>'sku 정보'!$G6</f>
-        <v>오아무선뿌리볼륨고데기5000-베이지</v>
+        <v>오아캘린더LED벽시계-우드</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>'sku 정보'!$H6</f>
-        <v>A01672</v>
+        <v>A01099</v>
       </c>
       <c r="C6">
         <f>'sku 정보'!$I6</f>
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -4563,25 +4588,25 @@
       </c>
       <c r="J6">
         <f>'sku 정보'!$J6</f>
-        <v>26733</v>
+        <v>135850</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>3127761</v>
+        <v>679250</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>'sku 정보'!$G7</f>
-        <v>오아폴드Qi2-블랙</v>
+        <v>오아무선모던LED시계R-베이지</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>'sku 정보'!$H7</f>
-        <v>A01471</v>
+        <v>A01584</v>
       </c>
       <c r="C7">
         <f>'sku 정보'!$I7</f>
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -4597,25 +4622,25 @@
       </c>
       <c r="J7">
         <f>'sku 정보'!$J7</f>
-        <v>32830</v>
+        <v>59360</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>459620</v>
+        <v>2374400</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>'sku 정보'!$G8</f>
-        <v>오아에어리스마트-화이트</v>
+        <v>오아데이클락-베이지</v>
       </c>
       <c r="B8" s="3" t="str">
         <f>'sku 정보'!$H8</f>
-        <v>A01676</v>
+        <v>M01628</v>
       </c>
       <c r="C8">
         <f>'sku 정보'!$I8</f>
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -4631,317 +4656,11 @@
       </c>
       <c r="J8">
         <f>'sku 정보'!$J8</f>
-        <v>58960</v>
+        <v>50853</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>1415040</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <f>'sku 정보'!$G9</f>
-        <v>오아이지물결고데기-블루</v>
-      </c>
-      <c r="B9" s="3" t="str">
-        <f>'sku 정보'!$H9</f>
-        <v>A01834</v>
-      </c>
-      <c r="C9">
-        <f>'sku 정보'!$I9</f>
-        <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9">
-        <v>37876</v>
-      </c>
-      <c r="G9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <f>'sku 정보'!$J9</f>
-        <v>30016</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>1500800</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <f>'sku 정보'!$G10</f>
-        <v>오아심플리고데기-아이보리</v>
-      </c>
-      <c r="B10" s="3" t="str">
-        <f>'sku 정보'!$H10</f>
-        <v>A01974</v>
-      </c>
-      <c r="C10">
-        <f>'sku 정보'!$I10</f>
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10">
-        <v>37876</v>
-      </c>
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <f>'sku 정보'!$J10</f>
-        <v>18693</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>486018</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="str">
-        <f>'sku 정보'!$G11</f>
-        <v>보아르위셀음식물처리기</v>
-      </c>
-      <c r="B11" s="3" t="str">
-        <f>'sku 정보'!$H11</f>
-        <v>A02015</v>
-      </c>
-      <c r="C11">
-        <f>'sku 정보'!$I11</f>
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11">
-        <v>37876</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <f>'sku 정보'!$J11</f>
-        <v>213060</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>2343660</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="str">
-        <f>'sku 정보'!$G12</f>
-        <v>오아듀얼미스트맥스-클라우디블루</v>
-      </c>
-      <c r="B12" s="3" t="str">
-        <f>'sku 정보'!$H12</f>
-        <v>A02362</v>
-      </c>
-      <c r="C12">
-        <f>'sku 정보'!$I12</f>
-        <v>8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12">
-        <v>37876</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12">
-        <f>'sku 정보'!$J12</f>
-        <v>23383</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>187064</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="str">
-        <f>'sku 정보'!$G13</f>
-        <v>오아히트워머-핑크</v>
-      </c>
-      <c r="B13" s="3" t="str">
-        <f>'sku 정보'!$H13</f>
-        <v>A02229</v>
-      </c>
-      <c r="C13">
-        <f>'sku 정보'!$I13</f>
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13">
-        <v>37876</v>
-      </c>
-      <c r="G13" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13">
-        <f>'sku 정보'!$J13</f>
-        <v>21976</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>593352</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="str">
-        <f>'sku 정보'!$G14</f>
-        <v>오아미니핏고데기-베이지</v>
-      </c>
-      <c r="B14" s="3" t="str">
-        <f>'sku 정보'!$H14</f>
-        <v>A02234</v>
-      </c>
-      <c r="C14">
-        <f>'sku 정보'!$I14</f>
-        <v>8</v>
-      </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14">
-        <v>37876</v>
-      </c>
-      <c r="G14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14">
-        <f>'sku 정보'!$J14</f>
-        <v>17353</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>138824</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="str">
-        <f>'sku 정보'!$G15</f>
-        <v>오아프리온무선고데기-핑크</v>
-      </c>
-      <c r="B15" s="3" t="str">
-        <f>'sku 정보'!$H15</f>
-        <v>A02459</v>
-      </c>
-      <c r="C15">
-        <f>'sku 정보'!$I15</f>
-        <v>133</v>
-      </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15">
-        <v>37876</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15">
-        <f>'sku 정보'!$J15</f>
-        <v>33433</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>4446589</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="str">
-        <f>'sku 정보'!$G16</f>
-        <v>오아효도손마사지기-블랙</v>
-      </c>
-      <c r="B16" s="3" t="str">
-        <f>'sku 정보'!$H16</f>
-        <v>A00298</v>
-      </c>
-      <c r="C16">
-        <f>'sku 정보'!$I16</f>
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16">
-        <v>37876</v>
-      </c>
-      <c r="G16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16">
-        <f>'sku 정보'!$J16</f>
-        <v>40066</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="0"/>
-        <v>480792</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="str">
-        <f>'sku 정보'!$G17</f>
-        <v>오아클린이스윙P-어비스블랙</v>
-      </c>
-      <c r="B17" s="3" t="str">
-        <f>'sku 정보'!$H17</f>
-        <v>A02862</v>
-      </c>
-      <c r="C17">
-        <f>'sku 정보'!$I17</f>
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17">
-        <v>37876</v>
-      </c>
-      <c r="G17" t="s">
-        <v>10</v>
-      </c>
-      <c r="J17">
-        <f>'sku 정보'!$J17</f>
-        <v>30016</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>1620864</v>
+        <v>508530</v>
       </c>
     </row>
   </sheetData>
@@ -4953,7 +4672,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N569"/>
+  <dimension ref="A1:N573"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="29" bestFit="1" customWidth="1"/>
@@ -5019,22 +4738,22 @@
         <v>25326</v>
       </c>
       <c r="F2" s="7">
-        <v>50875168</v>
+        <v>5462299</v>
       </c>
       <c r="G2" s="7" t="str">
         <f t="shared" ref="G2:G65" si="0">IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
-        <v>오아커버넥마사지기-베이지</v>
+        <v>오아플라이트-화이트</v>
       </c>
       <c r="H2" s="7" t="str">
         <f t="shared" ref="H2:H65" si="1">IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
-        <v>A00959</v>
+        <v>L0031</v>
       </c>
       <c r="I2" s="7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J2" s="7">
         <f t="shared" ref="J2:J65" si="2">IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
-        <v>58826</v>
+        <v>21320</v>
       </c>
       <c r="L2">
         <v>25326</v>
@@ -5061,22 +4780,22 @@
         <v>26666</v>
       </c>
       <c r="F3" s="7">
-        <v>52204284</v>
+        <v>16303007</v>
       </c>
       <c r="G3" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르스위프클링전용필터</v>
+        <v>오아무드센서등</v>
       </c>
       <c r="H3" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>M00313</v>
+        <v>L0080</v>
       </c>
       <c r="I3" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J3" s="7">
         <f t="shared" si="2"/>
-        <v>3283</v>
+        <v>14088</v>
       </c>
       <c r="L3">
         <v>26666</v>
@@ -5103,22 +4822,22 @@
         <v>21976</v>
       </c>
       <c r="F4" s="7">
-        <v>55462718</v>
+        <v>42265154</v>
       </c>
       <c r="G4" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아슬림에어드라이기-블랙</v>
+        <v>오아모던LED시계R</v>
       </c>
       <c r="H4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01146</v>
+        <v>C0466</v>
       </c>
       <c r="I4" s="7">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" si="2"/>
-        <v>39396</v>
+        <v>48685</v>
       </c>
       <c r="L4">
         <v>21976</v>
@@ -5145,22 +4864,22 @@
         <v>72360</v>
       </c>
       <c r="F5" s="7">
-        <v>58716097</v>
+        <v>48105600</v>
       </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아아이스볼트맥스-베이지</v>
+        <v>오아모던LED시계S</v>
       </c>
       <c r="H5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01593</v>
+        <v>C0467</v>
       </c>
       <c r="I5" s="7">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
-        <v>19966</v>
+        <v>51935</v>
       </c>
       <c r="L5">
         <v>72360</v>
@@ -5187,22 +4906,22 @@
         <v>85090</v>
       </c>
       <c r="F6" s="7">
-        <v>60085614</v>
+        <v>64753996</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아무선뿌리볼륨고데기5000-베이지</v>
+        <v>오아캘린더LED벽시계-우드</v>
       </c>
       <c r="H6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01672</v>
+        <v>A01099</v>
       </c>
       <c r="I6" s="7">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>26733</v>
+        <v>135850</v>
       </c>
       <c r="L6">
         <v>85090</v>
@@ -5229,22 +4948,22 @@
         <v>58960</v>
       </c>
       <c r="F7" s="7">
-        <v>61089339</v>
+        <v>64789478</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아폴드Qi2-블랙</v>
+        <v>오아무선모던LED시계R-베이지</v>
       </c>
       <c r="H7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01471</v>
+        <v>A01584</v>
       </c>
       <c r="I7" s="7">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="2"/>
-        <v>32830</v>
+        <v>59360</v>
       </c>
       <c r="L7">
         <v>58960</v>
@@ -5271,22 +4990,22 @@
         <v>71690</v>
       </c>
       <c r="F8" s="7">
-        <v>61199642</v>
+        <v>71030052</v>
       </c>
       <c r="G8" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아에어리스마트-화이트</v>
+        <v>오아데이클락-베이지</v>
       </c>
       <c r="H8" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01676</v>
+        <v>M01628</v>
       </c>
       <c r="I8" s="7">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="2"/>
-        <v>58960</v>
+        <v>50853</v>
       </c>
       <c r="L8">
         <v>71690</v>
@@ -5312,23 +5031,19 @@
       <c r="D9" s="34">
         <v>64990</v>
       </c>
-      <c r="F9" s="7">
-        <v>64330764</v>
-      </c>
-      <c r="G9" s="7" t="str">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>오아이지물결고데기-블루</v>
-      </c>
-      <c r="H9" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <f t="shared" si="1"/>
-        <v>A01834</v>
-      </c>
-      <c r="I9" s="7">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" s="7"/>
       <c r="J9" s="7">
         <f t="shared" si="2"/>
-        <v>30016</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>64990</v>
@@ -5354,23 +5069,19 @@
       <c r="D10" s="34">
         <v>61640</v>
       </c>
-      <c r="F10" s="7">
-        <v>64808932</v>
-      </c>
-      <c r="G10" s="7" t="str">
+      <c r="F10" s="7"/>
+      <c r="G10" s="7">
         <f t="shared" si="0"/>
-        <v>오아심플리고데기-아이보리</v>
-      </c>
-      <c r="H10" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
         <f t="shared" si="1"/>
-        <v>A01974</v>
-      </c>
-      <c r="I10" s="7">
-        <v>26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="7"/>
       <c r="J10" s="7">
         <f t="shared" si="2"/>
-        <v>18693</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>61640</v>
@@ -5396,23 +5107,19 @@
       <c r="D11" s="34">
         <v>40066</v>
       </c>
-      <c r="F11" s="7">
-        <v>65145714</v>
-      </c>
-      <c r="G11" s="7" t="str">
+      <c r="F11" s="7"/>
+      <c r="G11" s="7">
         <f t="shared" si="0"/>
-        <v>보아르위셀음식물처리기</v>
-      </c>
-      <c r="H11" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
         <f t="shared" si="1"/>
-        <v>A02015</v>
-      </c>
-      <c r="I11" s="7">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="7"/>
       <c r="J11" s="7">
         <f t="shared" si="2"/>
-        <v>213060</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>40066</v>
@@ -5438,23 +5145,19 @@
       <c r="D12" s="34">
         <v>38056</v>
       </c>
-      <c r="F12" s="7">
-        <v>65933937</v>
-      </c>
-      <c r="G12" s="7" t="str">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7">
         <f t="shared" si="0"/>
-        <v>오아듀얼미스트맥스-클라우디블루</v>
-      </c>
-      <c r="H12" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
         <f t="shared" si="1"/>
-        <v>A02362</v>
-      </c>
-      <c r="I12" s="7">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I12" s="7"/>
       <c r="J12" s="7">
         <f t="shared" si="2"/>
-        <v>23383</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <v>38056</v>
@@ -5477,23 +5180,19 @@
       <c r="D13" s="34">
         <v>40736</v>
       </c>
-      <c r="F13" s="7">
-        <v>66358440</v>
-      </c>
-      <c r="G13" s="7" t="str">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7">
         <f t="shared" si="0"/>
-        <v>오아히트워머-핑크</v>
-      </c>
-      <c r="H13" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
         <f t="shared" si="1"/>
-        <v>A02229</v>
-      </c>
-      <c r="I13" s="7">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I13" s="7"/>
       <c r="J13" s="7">
         <f t="shared" si="2"/>
-        <v>21976</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>40736</v>
@@ -5516,23 +5215,19 @@
       <c r="D14" s="34">
         <v>45426</v>
       </c>
-      <c r="F14" s="7">
-        <v>66778787</v>
-      </c>
-      <c r="G14" s="7" t="str">
+      <c r="F14" s="7"/>
+      <c r="G14" s="7">
         <f t="shared" si="0"/>
-        <v>오아미니핏고데기-베이지</v>
-      </c>
-      <c r="H14" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
         <f t="shared" si="1"/>
-        <v>A02234</v>
-      </c>
-      <c r="I14" s="7">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I14" s="7"/>
       <c r="J14" s="7">
         <f t="shared" si="2"/>
-        <v>17353</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>45426</v>
@@ -5555,23 +5250,19 @@
       <c r="D15" s="34">
         <v>36046</v>
       </c>
-      <c r="F15" s="7">
-        <v>68938743</v>
-      </c>
-      <c r="G15" s="7" t="str">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7">
         <f t="shared" si="0"/>
-        <v>오아프리온무선고데기-핑크</v>
-      </c>
-      <c r="H15" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
         <f t="shared" si="1"/>
-        <v>A02459</v>
-      </c>
-      <c r="I15" s="7">
-        <v>133</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I15" s="7"/>
       <c r="J15" s="7">
         <f t="shared" si="2"/>
-        <v>33433</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>36046</v>
@@ -5594,23 +5285,19 @@
       <c r="D16" s="34">
         <v>29413</v>
       </c>
-      <c r="F16" s="7">
-        <v>69770093</v>
-      </c>
-      <c r="G16" s="7" t="str">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7">
         <f t="shared" si="0"/>
-        <v>오아효도손마사지기-블랙</v>
-      </c>
-      <c r="H16" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
         <f t="shared" si="1"/>
-        <v>A00298</v>
-      </c>
-      <c r="I16" s="7">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="7"/>
       <c r="J16" s="7">
         <f t="shared" si="2"/>
-        <v>40066</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>29413</v>
@@ -5633,23 +5320,19 @@
       <c r="D17" s="34">
         <v>30016</v>
       </c>
-      <c r="F17" s="7">
-        <v>72910681</v>
-      </c>
-      <c r="G17" s="7" t="str">
+      <c r="F17" s="7"/>
+      <c r="G17" s="7">
         <f t="shared" si="0"/>
-        <v>오아클린이스윙P-어비스블랙</v>
-      </c>
-      <c r="H17" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
         <f t="shared" si="1"/>
-        <v>A02862</v>
-      </c>
-      <c r="I17" s="7">
-        <v>54</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="7"/>
       <c r="J17" s="7">
         <f t="shared" si="2"/>
-        <v>30016</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>30016</v>
@@ -11516,7 +11199,7 @@
         <v>519</v>
       </c>
       <c r="D185" s="34">
-        <v>49446</v>
+        <v>43416</v>
       </c>
       <c r="F185" s="7"/>
       <c r="G185" s="7">
@@ -11537,7 +11220,7 @@
       </c>
       <c r="M185" t="b">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.3">
@@ -22870,7 +22553,7 @@
         <v>1127</v>
       </c>
       <c r="D549" s="37">
-        <v>19363</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.3">
@@ -22884,7 +22567,7 @@
         <v>1128</v>
       </c>
       <c r="D550" s="37">
-        <v>19363</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.3">
@@ -22898,7 +22581,7 @@
         <v>1129</v>
       </c>
       <c r="D551" s="37">
-        <v>20033</v>
+        <v>17181</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">
@@ -22912,7 +22595,7 @@
         <v>1130</v>
       </c>
       <c r="D552" s="37">
-        <v>20033</v>
+        <v>17181</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
@@ -23151,6 +22834,62 @@
       </c>
       <c r="D569" s="37">
         <v>33433</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A570" s="14">
+        <v>74826973</v>
+      </c>
+      <c r="B570" s="14" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C570" s="14" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D570" s="37">
+        <v>5106</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A571" s="14">
+        <v>74826974</v>
+      </c>
+      <c r="B571" s="14" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C571" s="14" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D571" s="37">
+        <v>5106</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A572" s="14">
+        <v>74884452</v>
+      </c>
+      <c r="B572" s="14" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C572" s="14" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D572" s="37">
+        <v>82110</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A573" s="14">
+        <v>75077119</v>
+      </c>
+      <c r="B573" s="14" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C573" s="14" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D573" s="37">
+        <v>34431</v>
       </c>
     </row>
   </sheetData>

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡발주양식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12AC87F2-CBCA-47FA-B2F6-220B496DD950}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29666C4A-4AFB-4C42-A003-C969807EE1D0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="1177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="1179">
   <si>
     <t>주문상품</t>
   </si>
@@ -3587,6 +3587,12 @@
   </si>
   <si>
     <t>A02634</t>
+  </si>
+  <si>
+    <t>오아에어리소닉드라이기-화이트</t>
+  </si>
+  <si>
+    <t>A03110</t>
   </si>
 </sst>
 </file>
@@ -4381,7 +4387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.625" bestFit="1" customWidth="1"/>
@@ -4428,15 +4434,15 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>'sku 정보'!$G2</f>
-        <v>오아플라이트-화이트</v>
+        <v>오아클린이펭귄-블루</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>'sku 정보'!$H2</f>
-        <v>L0031</v>
+        <v>O0024</v>
       </c>
       <c r="C2">
         <f>'sku 정보'!$I2</f>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -4452,25 +4458,25 @@
       </c>
       <c r="J2">
         <f>'sku 정보'!$J2</f>
-        <v>21320</v>
+        <v>8241</v>
       </c>
       <c r="K2">
         <f>$J2*$C2</f>
-        <v>341120</v>
+        <v>41205</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>'sku 정보'!$G3</f>
-        <v>오아무드센서등</v>
+        <v>오아히트스팟S-블랙</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>'sku 정보'!$H3</f>
-        <v>L0080</v>
+        <v>A01985</v>
       </c>
       <c r="C3">
         <f>'sku 정보'!$I3</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -4486,25 +4492,25 @@
       </c>
       <c r="J3">
         <f>'sku 정보'!$J3</f>
-        <v>14088</v>
+        <v>32093</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K8" si="0">$J3*$C3</f>
-        <v>197232</v>
+        <f t="shared" ref="K3:K11" si="0">$J3*$C3</f>
+        <v>962790</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>'sku 정보'!$G4</f>
-        <v>오아모던LED시계R</v>
+        <v>오아커버넥마사지기-베이지</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>'sku 정보'!$H4</f>
-        <v>C0466</v>
+        <v>A00959</v>
       </c>
       <c r="C4">
         <f>'sku 정보'!$I4</f>
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -4520,25 +4526,25 @@
       </c>
       <c r="J4">
         <f>'sku 정보'!$J4</f>
-        <v>48685</v>
+        <v>58826</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>1460550</v>
+        <v>58826</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>'sku 정보'!$G5</f>
-        <v>오아모던LED시계S</v>
+        <v>오아클린이퓨어S-화이트</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>'sku 정보'!$H5</f>
-        <v>C0467</v>
+        <v>A01503</v>
       </c>
       <c r="C5">
         <f>'sku 정보'!$I5</f>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -4554,25 +4560,25 @@
       </c>
       <c r="J5">
         <f>'sku 정보'!$J5</f>
-        <v>51935</v>
+        <v>12663</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>1038700</v>
+        <v>12663</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>'sku 정보'!$G6</f>
-        <v>오아캘린더LED벽시계-우드</v>
+        <v>오아히트스팟S-베이지</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>'sku 정보'!$H6</f>
-        <v>A01099</v>
+        <v>A01986</v>
       </c>
       <c r="C6">
         <f>'sku 정보'!$I6</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -4588,25 +4594,25 @@
       </c>
       <c r="J6">
         <f>'sku 정보'!$J6</f>
-        <v>135850</v>
+        <v>32093</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>679250</v>
+        <v>128372</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>'sku 정보'!$G7</f>
-        <v>오아무선모던LED시계R-베이지</v>
+        <v>오아클린이소프트미세모2p-블랙</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>'sku 정보'!$H7</f>
-        <v>A01584</v>
+        <v>E0235</v>
       </c>
       <c r="C7">
         <f>'sku 정보'!$I7</f>
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -4622,25 +4628,25 @@
       </c>
       <c r="J7">
         <f>'sku 정보'!$J7</f>
-        <v>59360</v>
+        <v>4020</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>2374400</v>
+        <v>20100</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>'sku 정보'!$G8</f>
-        <v>오아데이클락-베이지</v>
+        <v>오아몬스터퀵케이블-포그밀크</v>
       </c>
       <c r="B8" s="3" t="str">
         <f>'sku 정보'!$H8</f>
-        <v>M01628</v>
+        <v>A03151</v>
       </c>
       <c r="C8">
         <f>'sku 정보'!$I8</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -4656,11 +4662,113 @@
       </c>
       <c r="J8">
         <f>'sku 정보'!$J8</f>
-        <v>50853</v>
+        <v>5106</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>508530</v>
+        <v>30636</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f>'sku 정보'!$G9</f>
+        <v>오아볼트건-블랙</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <f>'sku 정보'!$H9</f>
+        <v>A02202</v>
+      </c>
+      <c r="C9">
+        <f>'sku 정보'!$I9</f>
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>37876</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <f>'sku 정보'!$J9</f>
+        <v>26733</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>187131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f>'sku 정보'!$G10</f>
+        <v>오아제로버그-화이트</v>
+      </c>
+      <c r="B10" s="3" t="str">
+        <f>'sku 정보'!$H10</f>
+        <v>A01451</v>
+      </c>
+      <c r="C10">
+        <f>'sku 정보'!$I10</f>
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>37876</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <f>'sku 정보'!$J10</f>
+        <v>26666</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>239994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f>'sku 정보'!$G11</f>
+        <v>보아르워시스핀C</v>
+      </c>
+      <c r="B11" s="3" t="str">
+        <f>'sku 정보'!$H11</f>
+        <v>C0178</v>
+      </c>
+      <c r="C11">
+        <f>'sku 정보'!$I11</f>
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <v>37876</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <f>'sku 정보'!$J11</f>
+        <v>16616</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>166160</v>
       </c>
     </row>
   </sheetData>
@@ -4672,7 +4780,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N573"/>
+  <dimension ref="A1:N574"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="29" bestFit="1" customWidth="1"/>
@@ -4738,22 +4846,22 @@
         <v>25326</v>
       </c>
       <c r="F2" s="7">
-        <v>5462299</v>
+        <v>25512595</v>
       </c>
       <c r="G2" s="7" t="str">
         <f t="shared" ref="G2:G65" si="0">IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
-        <v>오아플라이트-화이트</v>
+        <v>오아클린이펭귄-블루</v>
       </c>
       <c r="H2" s="7" t="str">
         <f t="shared" ref="H2:H65" si="1">IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
-        <v>L0031</v>
+        <v>O0024</v>
       </c>
       <c r="I2" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J2" s="7">
         <f t="shared" ref="J2:J65" si="2">IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
-        <v>21320</v>
+        <v>8241</v>
       </c>
       <c r="L2">
         <v>25326</v>
@@ -4780,22 +4888,22 @@
         <v>26666</v>
       </c>
       <c r="F3" s="7">
-        <v>16303007</v>
+        <v>64214259</v>
       </c>
       <c r="G3" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아무드센서등</v>
+        <v>오아히트스팟S-블랙</v>
       </c>
       <c r="H3" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>L0080</v>
+        <v>A01985</v>
       </c>
       <c r="I3" s="7">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J3" s="7">
         <f t="shared" si="2"/>
-        <v>14088</v>
+        <v>32093</v>
       </c>
       <c r="L3">
         <v>26666</v>
@@ -4822,22 +4930,22 @@
         <v>21976</v>
       </c>
       <c r="F4" s="7">
-        <v>42265154</v>
+        <v>50875168</v>
       </c>
       <c r="G4" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아모던LED시계R</v>
+        <v>오아커버넥마사지기-베이지</v>
       </c>
       <c r="H4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>C0466</v>
+        <v>A00959</v>
       </c>
       <c r="I4" s="7">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" si="2"/>
-        <v>48685</v>
+        <v>58826</v>
       </c>
       <c r="L4">
         <v>21976</v>
@@ -4864,22 +4972,22 @@
         <v>72360</v>
       </c>
       <c r="F5" s="7">
-        <v>48105600</v>
+        <v>60725132</v>
       </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아모던LED시계S</v>
+        <v>오아클린이퓨어S-화이트</v>
       </c>
       <c r="H5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>C0467</v>
+        <v>A01503</v>
       </c>
       <c r="I5" s="7">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
-        <v>51935</v>
+        <v>12663</v>
       </c>
       <c r="L5">
         <v>72360</v>
@@ -4906,22 +5014,22 @@
         <v>85090</v>
       </c>
       <c r="F6" s="7">
-        <v>64753996</v>
+        <v>64214258</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아캘린더LED벽시계-우드</v>
+        <v>오아히트스팟S-베이지</v>
       </c>
       <c r="H6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01099</v>
+        <v>A01986</v>
       </c>
       <c r="I6" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>135850</v>
+        <v>32093</v>
       </c>
       <c r="L6">
         <v>85090</v>
@@ -4948,22 +5056,22 @@
         <v>58960</v>
       </c>
       <c r="F7" s="7">
-        <v>64789478</v>
+        <v>32711387</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아무선모던LED시계R-베이지</v>
+        <v>오아클린이소프트미세모2p-블랙</v>
       </c>
       <c r="H7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01584</v>
+        <v>E0235</v>
       </c>
       <c r="I7" s="7">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="2"/>
-        <v>59360</v>
+        <v>4020</v>
       </c>
       <c r="L7">
         <v>58960</v>
@@ -4990,22 +5098,22 @@
         <v>71690</v>
       </c>
       <c r="F8" s="7">
-        <v>71030052</v>
+        <v>74826974</v>
       </c>
       <c r="G8" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아데이클락-베이지</v>
+        <v>오아몬스터퀵케이블-포그밀크</v>
       </c>
       <c r="H8" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>M01628</v>
+        <v>A03151</v>
       </c>
       <c r="I8" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="2"/>
-        <v>50853</v>
+        <v>5106</v>
       </c>
       <c r="L8">
         <v>71690</v>
@@ -5031,19 +5139,23 @@
       <c r="D9" s="34">
         <v>64990</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7">
+      <c r="F9" s="7">
+        <v>67191572</v>
+      </c>
+      <c r="G9" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+        <v>오아볼트건-블랙</v>
+      </c>
+      <c r="H9" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="7"/>
+        <v>A02202</v>
+      </c>
+      <c r="I9" s="7">
+        <v>7</v>
+      </c>
       <c r="J9" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26733</v>
       </c>
       <c r="L9">
         <v>64990</v>
@@ -5069,19 +5181,23 @@
       <c r="D10" s="34">
         <v>61640</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7">
+      <c r="F10" s="7">
+        <v>59199875</v>
+      </c>
+      <c r="G10" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
+        <v>오아제로버그-화이트</v>
+      </c>
+      <c r="H10" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="7"/>
+        <v>A01451</v>
+      </c>
+      <c r="I10" s="7">
+        <v>9</v>
+      </c>
       <c r="J10" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26666</v>
       </c>
       <c r="L10">
         <v>61640</v>
@@ -5107,19 +5223,23 @@
       <c r="D11" s="34">
         <v>40066</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7">
+      <c r="F11" s="7">
+        <v>27056005</v>
+      </c>
+      <c r="G11" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
+        <v>보아르워시스핀C</v>
+      </c>
+      <c r="H11" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="7"/>
+        <v>C0178</v>
+      </c>
+      <c r="I11" s="7">
+        <v>10</v>
+      </c>
       <c r="J11" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16616</v>
       </c>
       <c r="L11">
         <v>40066</v>
@@ -8329,7 +8449,7 @@
         <v>451</v>
       </c>
       <c r="D103" s="34">
-        <v>18626</v>
+        <v>17112</v>
       </c>
       <c r="F103" s="7"/>
       <c r="G103" s="7">
@@ -8350,7 +8470,7 @@
       </c>
       <c r="M103" t="b">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
@@ -13719,7 +13839,7 @@
         <v>1164</v>
       </c>
       <c r="D257" s="35">
-        <v>33366</v>
+        <v>34362</v>
       </c>
       <c r="F257" s="41"/>
       <c r="G257" s="41">
@@ -13740,7 +13860,7 @@
       </c>
       <c r="M257" s="33" t="b">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.3">
@@ -22890,6 +23010,20 @@
       </c>
       <c r="D573" s="37">
         <v>34431</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A574" s="14">
+        <v>75741354</v>
+      </c>
+      <c r="B574" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C574" s="14" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D574" s="37">
+        <v>43416</v>
       </c>
     </row>
   </sheetData>

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡발주양식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29666C4A-4AFB-4C42-A003-C969807EE1D0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2529244E-E383-4B21-BF7E-960529313F7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="1179">
   <si>
     <t>주문상품</t>
   </si>
@@ -4387,7 +4387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.625" bestFit="1" customWidth="1"/>
@@ -4434,15 +4434,15 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>'sku 정보'!$G2</f>
-        <v>오아클린이펭귄-블루</v>
+        <v>보아르투웨이텀블러-아이보리</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>'sku 정보'!$H2</f>
-        <v>O0024</v>
+        <v>E0446</v>
       </c>
       <c r="C2">
         <f>'sku 정보'!$I2</f>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -4458,25 +4458,25 @@
       </c>
       <c r="J2">
         <f>'sku 정보'!$J2</f>
-        <v>8241</v>
+        <v>14129</v>
       </c>
       <c r="K2">
         <f>$J2*$C2</f>
-        <v>41205</v>
+        <v>353225</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>'sku 정보'!$G3</f>
-        <v>오아히트스팟S-블랙</v>
+        <v>보아르퓨어스텐</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>'sku 정보'!$H3</f>
-        <v>A01985</v>
+        <v>E0387</v>
       </c>
       <c r="C3">
         <f>'sku 정보'!$I3</f>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -4492,25 +4492,25 @@
       </c>
       <c r="J3">
         <f>'sku 정보'!$J3</f>
-        <v>32093</v>
+        <v>22511</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K11" si="0">$J3*$C3</f>
-        <v>962790</v>
+        <f t="shared" ref="K3:K7" si="0">$J3*$C3</f>
+        <v>90044</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>'sku 정보'!$G4</f>
-        <v>오아커버넥마사지기-베이지</v>
+        <v>보아르투웨이폴든텀블러-민트</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>'sku 정보'!$H4</f>
-        <v>A00959</v>
+        <v>A02701</v>
       </c>
       <c r="C4">
         <f>'sku 정보'!$I4</f>
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -4526,25 +4526,25 @@
       </c>
       <c r="J4">
         <f>'sku 정보'!$J4</f>
-        <v>58826</v>
+        <v>23359</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>58826</v>
+        <v>607334</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>'sku 정보'!$G5</f>
-        <v>오아클린이퓨어S-화이트</v>
+        <v>보아르투웨이폴든텀블러-핑크</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>'sku 정보'!$H5</f>
-        <v>A01503</v>
+        <v>A02700</v>
       </c>
       <c r="C5">
         <f>'sku 정보'!$I5</f>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -4560,25 +4560,25 @@
       </c>
       <c r="J5">
         <f>'sku 정보'!$J5</f>
-        <v>12663</v>
+        <v>23359</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>12663</v>
+        <v>420462</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>'sku 정보'!$G6</f>
-        <v>오아히트스팟S-베이지</v>
+        <v>보아르아가맘마쪽쪽이살균기</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>'sku 정보'!$H6</f>
-        <v>A01986</v>
+        <v>S0262</v>
       </c>
       <c r="C6">
         <f>'sku 정보'!$I6</f>
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -4594,25 +4594,25 @@
       </c>
       <c r="J6">
         <f>'sku 정보'!$J6</f>
-        <v>32093</v>
+        <v>23940</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>128372</v>
+        <v>3447360</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>'sku 정보'!$G7</f>
-        <v>오아클린이소프트미세모2p-블랙</v>
+        <v>보아르투웨이텀블러-레인보우</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>'sku 정보'!$H7</f>
-        <v>E0235</v>
+        <v>E0447</v>
       </c>
       <c r="C7">
         <f>'sku 정보'!$I7</f>
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -4628,147 +4628,11 @@
       </c>
       <c r="J7">
         <f>'sku 정보'!$J7</f>
-        <v>4020</v>
+        <v>14129</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>20100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
-        <f>'sku 정보'!$G8</f>
-        <v>오아몬스터퀵케이블-포그밀크</v>
-      </c>
-      <c r="B8" s="3" t="str">
-        <f>'sku 정보'!$H8</f>
-        <v>A03151</v>
-      </c>
-      <c r="C8">
-        <f>'sku 정보'!$I8</f>
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8">
-        <v>37876</v>
-      </c>
-      <c r="G8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <f>'sku 정보'!$J8</f>
-        <v>5106</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
-        <v>30636</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <f>'sku 정보'!$G9</f>
-        <v>오아볼트건-블랙</v>
-      </c>
-      <c r="B9" s="3" t="str">
-        <f>'sku 정보'!$H9</f>
-        <v>A02202</v>
-      </c>
-      <c r="C9">
-        <f>'sku 정보'!$I9</f>
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9">
-        <v>37876</v>
-      </c>
-      <c r="G9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <f>'sku 정보'!$J9</f>
-        <v>26733</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>187131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <f>'sku 정보'!$G10</f>
-        <v>오아제로버그-화이트</v>
-      </c>
-      <c r="B10" s="3" t="str">
-        <f>'sku 정보'!$H10</f>
-        <v>A01451</v>
-      </c>
-      <c r="C10">
-        <f>'sku 정보'!$I10</f>
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10">
-        <v>37876</v>
-      </c>
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <f>'sku 정보'!$J10</f>
-        <v>26666</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>239994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="str">
-        <f>'sku 정보'!$G11</f>
-        <v>보아르워시스핀C</v>
-      </c>
-      <c r="B11" s="3" t="str">
-        <f>'sku 정보'!$H11</f>
-        <v>C0178</v>
-      </c>
-      <c r="C11">
-        <f>'sku 정보'!$I11</f>
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11">
-        <v>37876</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <f>'sku 정보'!$J11</f>
-        <v>16616</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>166160</v>
+        <v>1412900</v>
       </c>
     </row>
   </sheetData>
@@ -4846,22 +4710,22 @@
         <v>25326</v>
       </c>
       <c r="F2" s="7">
-        <v>25512595</v>
+        <v>53583387</v>
       </c>
       <c r="G2" s="7" t="str">
         <f t="shared" ref="G2:G65" si="0">IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
-        <v>오아클린이펭귄-블루</v>
+        <v>보아르투웨이텀블러-아이보리</v>
       </c>
       <c r="H2" s="7" t="str">
         <f t="shared" ref="H2:H65" si="1">IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
-        <v>O0024</v>
+        <v>E0446</v>
       </c>
       <c r="I2" s="7">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J2" s="7">
         <f t="shared" ref="J2:J65" si="2">IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
-        <v>8241</v>
+        <v>14129</v>
       </c>
       <c r="L2">
         <v>25326</v>
@@ -4888,22 +4752,22 @@
         <v>26666</v>
       </c>
       <c r="F3" s="7">
-        <v>64214259</v>
+        <v>39384055</v>
       </c>
       <c r="G3" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아히트스팟S-블랙</v>
+        <v>보아르퓨어스텐</v>
       </c>
       <c r="H3" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01985</v>
+        <v>E0387</v>
       </c>
       <c r="I3" s="7">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J3" s="7">
         <f t="shared" si="2"/>
-        <v>32093</v>
+        <v>22511</v>
       </c>
       <c r="L3">
         <v>26666</v>
@@ -4930,22 +4794,22 @@
         <v>21976</v>
       </c>
       <c r="F4" s="7">
-        <v>50875168</v>
+        <v>73316684</v>
       </c>
       <c r="G4" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아커버넥마사지기-베이지</v>
+        <v>보아르투웨이폴든텀블러-민트</v>
       </c>
       <c r="H4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A00959</v>
+        <v>A02701</v>
       </c>
       <c r="I4" s="7">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" si="2"/>
-        <v>58826</v>
+        <v>23359</v>
       </c>
       <c r="L4">
         <v>21976</v>
@@ -4972,22 +4836,22 @@
         <v>72360</v>
       </c>
       <c r="F5" s="7">
-        <v>60725132</v>
+        <v>73316683</v>
       </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아클린이퓨어S-화이트</v>
+        <v>보아르투웨이폴든텀블러-핑크</v>
       </c>
       <c r="H5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01503</v>
+        <v>A02700</v>
       </c>
       <c r="I5" s="7">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
-        <v>12663</v>
+        <v>23359</v>
       </c>
       <c r="L5">
         <v>72360</v>
@@ -5014,22 +4878,22 @@
         <v>85090</v>
       </c>
       <c r="F6" s="7">
-        <v>64214258</v>
+        <v>37161537</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아히트스팟S-베이지</v>
+        <v>보아르아가맘마쪽쪽이살균기</v>
       </c>
       <c r="H6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01986</v>
+        <v>S0262</v>
       </c>
       <c r="I6" s="7">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>32093</v>
+        <v>23940</v>
       </c>
       <c r="L6">
         <v>85090</v>
@@ -5056,22 +4920,22 @@
         <v>58960</v>
       </c>
       <c r="F7" s="7">
-        <v>32711387</v>
+        <v>53564659</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아클린이소프트미세모2p-블랙</v>
+        <v>보아르투웨이텀블러-레인보우</v>
       </c>
       <c r="H7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>E0235</v>
+        <v>E0447</v>
       </c>
       <c r="I7" s="7">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="2"/>
-        <v>4020</v>
+        <v>14129</v>
       </c>
       <c r="L7">
         <v>58960</v>
@@ -5097,23 +4961,19 @@
       <c r="D8" s="34">
         <v>71690</v>
       </c>
-      <c r="F8" s="7">
-        <v>74826974</v>
-      </c>
-      <c r="G8" s="7" t="str">
+      <c r="F8" s="7"/>
+      <c r="G8" s="7">
         <f t="shared" si="0"/>
-        <v>오아몬스터퀵케이블-포그밀크</v>
-      </c>
-      <c r="H8" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
         <f t="shared" si="1"/>
-        <v>A03151</v>
-      </c>
-      <c r="I8" s="7">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I8" s="7"/>
       <c r="J8" s="7">
         <f t="shared" si="2"/>
-        <v>5106</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>71690</v>
@@ -5139,23 +4999,19 @@
       <c r="D9" s="34">
         <v>64990</v>
       </c>
-      <c r="F9" s="7">
-        <v>67191572</v>
-      </c>
-      <c r="G9" s="7" t="str">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>오아볼트건-블랙</v>
-      </c>
-      <c r="H9" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <f t="shared" si="1"/>
-        <v>A02202</v>
-      </c>
-      <c r="I9" s="7">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" s="7"/>
       <c r="J9" s="7">
         <f t="shared" si="2"/>
-        <v>26733</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>64990</v>
@@ -5181,23 +5037,19 @@
       <c r="D10" s="34">
         <v>61640</v>
       </c>
-      <c r="F10" s="7">
-        <v>59199875</v>
-      </c>
-      <c r="G10" s="7" t="str">
+      <c r="F10" s="7"/>
+      <c r="G10" s="7">
         <f t="shared" si="0"/>
-        <v>오아제로버그-화이트</v>
-      </c>
-      <c r="H10" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
         <f t="shared" si="1"/>
-        <v>A01451</v>
-      </c>
-      <c r="I10" s="7">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="7"/>
       <c r="J10" s="7">
         <f t="shared" si="2"/>
-        <v>26666</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>61640</v>
@@ -5223,23 +5075,19 @@
       <c r="D11" s="34">
         <v>40066</v>
       </c>
-      <c r="F11" s="7">
-        <v>27056005</v>
-      </c>
-      <c r="G11" s="7" t="str">
+      <c r="F11" s="7"/>
+      <c r="G11" s="7">
         <f t="shared" si="0"/>
-        <v>보아르워시스핀C</v>
-      </c>
-      <c r="H11" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
         <f t="shared" si="1"/>
-        <v>C0178</v>
-      </c>
-      <c r="I11" s="7">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="7"/>
       <c r="J11" s="7">
         <f t="shared" si="2"/>
-        <v>16616</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>40066</v>
@@ -8169,7 +8017,7 @@
         <v>443</v>
       </c>
       <c r="D95" s="34">
-        <v>23316</v>
+        <v>22043</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7">
@@ -8190,7 +8038,7 @@
       </c>
       <c r="M95" t="b">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
@@ -8204,7 +8052,7 @@
         <v>444</v>
       </c>
       <c r="D96" s="34">
-        <v>23316</v>
+        <v>22043</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7">
@@ -8225,7 +8073,7 @@
       </c>
       <c r="M96" t="b">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
@@ -22589,7 +22437,7 @@
         <v>1111</v>
       </c>
       <c r="D543" s="37">
-        <v>23383</v>
+        <v>19966</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.3">

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡발주양식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2529244E-E383-4B21-BF7E-960529313F7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AE4DB2C-2B96-420E-8C00-CAF143C6EAD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="1183">
   <si>
     <t>주문상품</t>
   </si>
@@ -3593,6 +3593,18 @@
   </si>
   <si>
     <t>A03110</t>
+  </si>
+  <si>
+    <t>오아워터쉴드드라이백-어비스블랙</t>
+  </si>
+  <si>
+    <t>A03156</t>
+  </si>
+  <si>
+    <t>오아씬플로우드라이기-메탈그레이</t>
+  </si>
+  <si>
+    <t>A03226</t>
   </si>
 </sst>
 </file>
@@ -4387,7 +4399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.625" bestFit="1" customWidth="1"/>
@@ -4434,15 +4446,15 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>'sku 정보'!$G2</f>
-        <v>보아르투웨이텀블러-아이보리</v>
+        <v>오아우드led시계R</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>'sku 정보'!$H2</f>
-        <v>E0446</v>
+        <v>C0324</v>
       </c>
       <c r="C2">
         <f>'sku 정보'!$I2</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -4458,25 +4470,25 @@
       </c>
       <c r="J2">
         <f>'sku 정보'!$J2</f>
-        <v>14129</v>
+        <v>42500</v>
       </c>
       <c r="K2">
         <f>$J2*$C2</f>
-        <v>353225</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>'sku 정보'!$G3</f>
-        <v>보아르퓨어스텐</v>
+        <v>오아뷰티LED거울-화이트</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>'sku 정보'!$H3</f>
-        <v>E0387</v>
+        <v>A01461</v>
       </c>
       <c r="C3">
         <f>'sku 정보'!$I3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -4492,25 +4504,25 @@
       </c>
       <c r="J3">
         <f>'sku 정보'!$J3</f>
-        <v>22511</v>
+        <v>12935</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K7" si="0">$J3*$C3</f>
-        <v>90044</v>
+        <f t="shared" ref="K3:K6" si="0">$J3*$C3</f>
+        <v>12935</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>'sku 정보'!$G4</f>
-        <v>보아르투웨이폴든텀블러-민트</v>
+        <v>보아르컴플릿10L쓰레기통-베이지</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>'sku 정보'!$H4</f>
-        <v>A02701</v>
+        <v>A01869</v>
       </c>
       <c r="C4">
         <f>'sku 정보'!$I4</f>
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -4526,25 +4538,25 @@
       </c>
       <c r="J4">
         <f>'sku 정보'!$J4</f>
-        <v>23359</v>
+        <v>21638</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>607334</v>
+        <v>86552</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>'sku 정보'!$G5</f>
-        <v>보아르투웨이폴든텀블러-핑크</v>
+        <v>오아포터블램프S-블랙</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>'sku 정보'!$H5</f>
-        <v>A02700</v>
+        <v>A01521</v>
       </c>
       <c r="C5">
         <f>'sku 정보'!$I5</f>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -4560,25 +4572,25 @@
       </c>
       <c r="J5">
         <f>'sku 정보'!$J5</f>
-        <v>23359</v>
+        <v>19734</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>420462</v>
+        <v>19734</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>'sku 정보'!$G6</f>
-        <v>보아르아가맘마쪽쪽이살균기</v>
+        <v>오아젤디스펜서-실버</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>'sku 정보'!$H6</f>
-        <v>S0262</v>
+        <v>A02554</v>
       </c>
       <c r="C6">
         <f>'sku 정보'!$I6</f>
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -4594,45 +4606,11 @@
       </c>
       <c r="J6">
         <f>'sku 정보'!$J6</f>
-        <v>23940</v>
+        <v>31296</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>3447360</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <f>'sku 정보'!$G7</f>
-        <v>보아르투웨이텀블러-레인보우</v>
-      </c>
-      <c r="B7" s="3" t="str">
-        <f>'sku 정보'!$H7</f>
-        <v>E0447</v>
-      </c>
-      <c r="C7">
-        <f>'sku 정보'!$I7</f>
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>37876</v>
-      </c>
-      <c r="G7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <f>'sku 정보'!$J7</f>
-        <v>14129</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>1412900</v>
+        <v>31296</v>
       </c>
     </row>
   </sheetData>
@@ -4644,7 +4622,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N574"/>
+  <dimension ref="A1:N576"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="29" bestFit="1" customWidth="1"/>
@@ -4710,22 +4688,22 @@
         <v>25326</v>
       </c>
       <c r="F2" s="7">
-        <v>53583387</v>
+        <v>34348663</v>
       </c>
       <c r="G2" s="7" t="str">
         <f t="shared" ref="G2:G65" si="0">IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
-        <v>보아르투웨이텀블러-아이보리</v>
+        <v>오아우드led시계R</v>
       </c>
       <c r="H2" s="7" t="str">
         <f t="shared" ref="H2:H65" si="1">IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
-        <v>E0446</v>
+        <v>C0324</v>
       </c>
       <c r="I2" s="7">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J2" s="7">
         <f t="shared" ref="J2:J65" si="2">IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
-        <v>14129</v>
+        <v>42500</v>
       </c>
       <c r="L2">
         <v>25326</v>
@@ -4752,22 +4730,22 @@
         <v>26666</v>
       </c>
       <c r="F3" s="7">
-        <v>39384055</v>
+        <v>61044622</v>
       </c>
       <c r="G3" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르퓨어스텐</v>
+        <v>오아뷰티LED거울-화이트</v>
       </c>
       <c r="H3" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>E0387</v>
+        <v>A01461</v>
       </c>
       <c r="I3" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" s="7">
         <f t="shared" si="2"/>
-        <v>22511</v>
+        <v>12935</v>
       </c>
       <c r="L3">
         <v>26666</v>
@@ -4794,22 +4772,22 @@
         <v>21976</v>
       </c>
       <c r="F4" s="7">
-        <v>73316684</v>
+        <v>63346456</v>
       </c>
       <c r="G4" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르투웨이폴든텀블러-민트</v>
+        <v>보아르컴플릿10L쓰레기통-베이지</v>
       </c>
       <c r="H4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A02701</v>
+        <v>A01869</v>
       </c>
       <c r="I4" s="7">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" si="2"/>
-        <v>23359</v>
+        <v>21638</v>
       </c>
       <c r="L4">
         <v>21976</v>
@@ -4836,22 +4814,22 @@
         <v>72360</v>
       </c>
       <c r="F5" s="7">
-        <v>73316683</v>
+        <v>67989839</v>
       </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르투웨이폴든텀블러-핑크</v>
+        <v>오아포터블램프S-블랙</v>
       </c>
       <c r="H5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A02700</v>
+        <v>A01521</v>
       </c>
       <c r="I5" s="7">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
-        <v>23359</v>
+        <v>19734</v>
       </c>
       <c r="L5">
         <v>72360</v>
@@ -4878,22 +4856,22 @@
         <v>85090</v>
       </c>
       <c r="F6" s="7">
-        <v>37161537</v>
+        <v>69279032</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르아가맘마쪽쪽이살균기</v>
+        <v>오아젤디스펜서-실버</v>
       </c>
       <c r="H6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>S0262</v>
+        <v>A02554</v>
       </c>
       <c r="I6" s="7">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>23940</v>
+        <v>31296</v>
       </c>
       <c r="L6">
         <v>85090</v>
@@ -4919,23 +4897,19 @@
       <c r="D7" s="34">
         <v>58960</v>
       </c>
-      <c r="F7" s="7">
-        <v>53564659</v>
-      </c>
-      <c r="G7" s="7" t="str">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7">
         <f t="shared" si="0"/>
-        <v>보아르투웨이텀블러-레인보우</v>
-      </c>
-      <c r="H7" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
         <f t="shared" si="1"/>
-        <v>E0447</v>
-      </c>
-      <c r="I7" s="7">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" s="7"/>
       <c r="J7" s="7">
         <f t="shared" si="2"/>
-        <v>14129</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>58960</v>
@@ -21072,14 +21046,14 @@
         <v>872</v>
       </c>
       <c r="D468" s="34">
-        <v>23383</v>
+        <v>26666</v>
       </c>
       <c r="L468">
         <v>23383</v>
       </c>
       <c r="M468" t="b">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469" spans="1:14" x14ac:dyDescent="0.3">
@@ -21093,14 +21067,14 @@
         <v>873</v>
       </c>
       <c r="D469" s="34">
-        <v>23383</v>
+        <v>26666</v>
       </c>
       <c r="L469">
         <v>23383</v>
       </c>
       <c r="M469" t="b">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="470" spans="1:14" x14ac:dyDescent="0.3">
@@ -21114,14 +21088,14 @@
         <v>874</v>
       </c>
       <c r="D470" s="34">
-        <v>23383</v>
+        <v>26666</v>
       </c>
       <c r="L470">
         <v>23383</v>
       </c>
       <c r="M470" t="b">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471" spans="1:14" x14ac:dyDescent="0.3">
@@ -22872,6 +22846,34 @@
       </c>
       <c r="D574" s="37">
         <v>43416</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A575" s="14">
+        <v>75989703</v>
+      </c>
+      <c r="B575" s="14" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C575" s="14" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D575" s="37">
+        <v>9858</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A576" s="14">
+        <v>76241042</v>
+      </c>
+      <c r="B576" s="14" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C576" s="14" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D576" s="37">
+        <v>54510</v>
       </c>
     </row>
   </sheetData>

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡발주양식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AE4DB2C-2B96-420E-8C00-CAF143C6EAD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485A55B9-0FD4-4026-994B-037DDEB9F048}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="1183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="1193">
   <si>
     <t>주문상품</t>
   </si>
@@ -3605,6 +3605,36 @@
   </si>
   <si>
     <t>A03226</t>
+  </si>
+  <si>
+    <t>오아컬리미-핑크</t>
+  </si>
+  <si>
+    <t>오아컬리미-화이트</t>
+  </si>
+  <si>
+    <t>오아올리미-핑크</t>
+  </si>
+  <si>
+    <t>오아올리미-화이트</t>
+  </si>
+  <si>
+    <t>A03211</t>
+  </si>
+  <si>
+    <t>A03212</t>
+  </si>
+  <si>
+    <t>A03209</t>
+  </si>
+  <si>
+    <t>A03210</t>
+  </si>
+  <si>
+    <t>보아르컴플릿M20L쓰레기통-베이지</t>
+  </si>
+  <si>
+    <t>A03243</t>
   </si>
 </sst>
 </file>
@@ -4399,7 +4429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.625" bestFit="1" customWidth="1"/>
@@ -4446,15 +4476,15 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>'sku 정보'!$G2</f>
-        <v>오아우드led시계R</v>
+        <v>보아르투웨이텀블러-핑크</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>'sku 정보'!$H2</f>
-        <v>C0324</v>
+        <v>A01695</v>
       </c>
       <c r="C2">
         <f>'sku 정보'!$I2</f>
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -4470,25 +4500,25 @@
       </c>
       <c r="J2">
         <f>'sku 정보'!$J2</f>
-        <v>42500</v>
+        <v>14129</v>
       </c>
       <c r="K2">
         <f>$J2*$C2</f>
-        <v>85000</v>
+        <v>706450</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>'sku 정보'!$G3</f>
-        <v>오아뷰티LED거울-화이트</v>
+        <v>보아르투웨이텀블러-블랙</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>'sku 정보'!$H3</f>
-        <v>A01461</v>
+        <v>E0442</v>
       </c>
       <c r="C3">
         <f>'sku 정보'!$I3</f>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -4504,25 +4534,25 @@
       </c>
       <c r="J3">
         <f>'sku 정보'!$J3</f>
-        <v>12935</v>
+        <v>14129</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K6" si="0">$J3*$C3</f>
-        <v>12935</v>
+        <f t="shared" ref="K3:K7" si="0">$J3*$C3</f>
+        <v>296709</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>'sku 정보'!$G4</f>
-        <v>보아르컴플릿10L쓰레기통-베이지</v>
+        <v>보아르투웨이폴든텀블러-민트</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>'sku 정보'!$H4</f>
-        <v>A01869</v>
+        <v>A02701</v>
       </c>
       <c r="C4">
         <f>'sku 정보'!$I4</f>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -4538,25 +4568,25 @@
       </c>
       <c r="J4">
         <f>'sku 정보'!$J4</f>
-        <v>21638</v>
+        <v>23359</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>86552</v>
+        <v>467180</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>'sku 정보'!$G5</f>
-        <v>오아포터블램프S-블랙</v>
+        <v>보아르투웨이텀블러-아이보리</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>'sku 정보'!$H5</f>
-        <v>A01521</v>
+        <v>E0446</v>
       </c>
       <c r="C5">
         <f>'sku 정보'!$I5</f>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -4572,25 +4602,25 @@
       </c>
       <c r="J5">
         <f>'sku 정보'!$J5</f>
-        <v>19734</v>
+        <v>14129</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>19734</v>
+        <v>240193</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>'sku 정보'!$G6</f>
-        <v>오아젤디스펜서-실버</v>
+        <v>보아르투웨이폴든텀블러-핑크</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>'sku 정보'!$H6</f>
-        <v>A02554</v>
+        <v>A02700</v>
       </c>
       <c r="C6">
         <f>'sku 정보'!$I6</f>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -4606,11 +4636,45 @@
       </c>
       <c r="J6">
         <f>'sku 정보'!$J6</f>
-        <v>31296</v>
+        <v>23359</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>31296</v>
+        <v>280308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f>'sku 정보'!$G7</f>
+        <v>보아르투웨이텀블러-민트</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <f>'sku 정보'!$H7</f>
+        <v>A01694</v>
+      </c>
+      <c r="C7">
+        <f>'sku 정보'!$I7</f>
+        <v>100</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>37876</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <f>'sku 정보'!$J7</f>
+        <v>14129</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>1412900</v>
       </c>
     </row>
   </sheetData>
@@ -4622,7 +4686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N576"/>
+  <dimension ref="A1:N581"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="29" bestFit="1" customWidth="1"/>
@@ -4688,22 +4752,22 @@
         <v>25326</v>
       </c>
       <c r="F2" s="7">
-        <v>34348663</v>
+        <v>60380162</v>
       </c>
       <c r="G2" s="7" t="str">
         <f t="shared" ref="G2:G65" si="0">IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
-        <v>오아우드led시계R</v>
+        <v>보아르투웨이텀블러-핑크</v>
       </c>
       <c r="H2" s="7" t="str">
         <f t="shared" ref="H2:H65" si="1">IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
-        <v>C0324</v>
+        <v>A01695</v>
       </c>
       <c r="I2" s="7">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="J2" s="7">
         <f t="shared" ref="J2:J65" si="2">IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
-        <v>42500</v>
+        <v>14129</v>
       </c>
       <c r="L2">
         <v>25326</v>
@@ -4730,22 +4794,22 @@
         <v>26666</v>
       </c>
       <c r="F3" s="7">
-        <v>61044622</v>
+        <v>53569741</v>
       </c>
       <c r="G3" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아뷰티LED거울-화이트</v>
+        <v>보아르투웨이텀블러-블랙</v>
       </c>
       <c r="H3" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01461</v>
+        <v>E0442</v>
       </c>
       <c r="I3" s="7">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J3" s="7">
         <f t="shared" si="2"/>
-        <v>12935</v>
+        <v>14129</v>
       </c>
       <c r="L3">
         <v>26666</v>
@@ -4772,22 +4836,22 @@
         <v>21976</v>
       </c>
       <c r="F4" s="7">
-        <v>63346456</v>
+        <v>73316684</v>
       </c>
       <c r="G4" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르컴플릿10L쓰레기통-베이지</v>
+        <v>보아르투웨이폴든텀블러-민트</v>
       </c>
       <c r="H4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01869</v>
+        <v>A02701</v>
       </c>
       <c r="I4" s="7">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" si="2"/>
-        <v>21638</v>
+        <v>23359</v>
       </c>
       <c r="L4">
         <v>21976</v>
@@ -4814,22 +4878,22 @@
         <v>72360</v>
       </c>
       <c r="F5" s="7">
-        <v>67989839</v>
+        <v>53583387</v>
       </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아포터블램프S-블랙</v>
+        <v>보아르투웨이텀블러-아이보리</v>
       </c>
       <c r="H5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01521</v>
+        <v>E0446</v>
       </c>
       <c r="I5" s="7">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
-        <v>19734</v>
+        <v>14129</v>
       </c>
       <c r="L5">
         <v>72360</v>
@@ -4856,22 +4920,22 @@
         <v>85090</v>
       </c>
       <c r="F6" s="7">
-        <v>69279032</v>
+        <v>73316683</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>오아젤디스펜서-실버</v>
+        <v>보아르투웨이폴든텀블러-핑크</v>
       </c>
       <c r="H6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A02554</v>
+        <v>A02700</v>
       </c>
       <c r="I6" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>31296</v>
+        <v>23359</v>
       </c>
       <c r="L6">
         <v>85090</v>
@@ -4897,19 +4961,23 @@
       <c r="D7" s="34">
         <v>58960</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7">
+      <c r="F7" s="7">
+        <v>60450424</v>
+      </c>
+      <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
+        <v>보아르투웨이텀블러-민트</v>
+      </c>
+      <c r="H7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="7"/>
+        <v>A01694</v>
+      </c>
+      <c r="I7" s="7">
+        <v>100</v>
+      </c>
       <c r="J7" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14129</v>
       </c>
       <c r="L7">
         <v>58960</v>
@@ -6381,7 +6449,7 @@
         <v>400</v>
       </c>
       <c r="D49" s="34">
-        <v>23316</v>
+        <v>24656</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7">
@@ -6402,7 +6470,7 @@
       </c>
       <c r="M49" t="b">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
@@ -6416,7 +6484,7 @@
         <v>401</v>
       </c>
       <c r="D50" s="34">
-        <v>23316</v>
+        <v>24656</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7">
@@ -6437,7 +6505,7 @@
       </c>
       <c r="M50" t="b">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
@@ -13801,7 +13869,7 @@
         <v>714</v>
       </c>
       <c r="D261" s="34">
-        <v>105190</v>
+        <v>95910</v>
       </c>
       <c r="F261" s="7"/>
       <c r="G261" s="7">
@@ -13822,7 +13890,7 @@
       </c>
       <c r="M261" t="b">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.3">
@@ -13836,7 +13904,7 @@
         <v>585</v>
       </c>
       <c r="D262" s="34">
-        <v>105190</v>
+        <v>95910</v>
       </c>
       <c r="F262" s="7"/>
       <c r="G262" s="7">
@@ -13857,7 +13925,7 @@
       </c>
       <c r="M262" t="b">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.3">
@@ -18806,7 +18874,7 @@
         <v>760</v>
       </c>
       <c r="D404" s="34">
-        <v>246560</v>
+        <v>220430</v>
       </c>
       <c r="F404" s="7"/>
       <c r="G404" s="7">
@@ -18827,7 +18895,7 @@
       </c>
       <c r="M404" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.3">
@@ -19086,7 +19154,7 @@
         <v>768</v>
       </c>
       <c r="D412" s="34">
-        <v>66330</v>
+        <v>59630</v>
       </c>
       <c r="F412" s="7"/>
       <c r="G412" s="7">
@@ -19107,7 +19175,7 @@
       </c>
       <c r="M412" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.3">
@@ -19786,7 +19854,7 @@
         <v>834</v>
       </c>
       <c r="D432" s="34">
-        <v>186930</v>
+        <v>166830</v>
       </c>
       <c r="F432" s="7"/>
       <c r="G432" s="7">
@@ -22874,6 +22942,76 @@
       </c>
       <c r="D576" s="37">
         <v>54510</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A577" s="14">
+        <v>76375598</v>
+      </c>
+      <c r="B577" s="14" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C577" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D577" s="37">
+        <v>16491</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A578" s="14">
+        <v>76375597</v>
+      </c>
+      <c r="B578" s="14" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C578" s="14" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D578" s="37">
+        <v>16491</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A579" s="14">
+        <v>76374400</v>
+      </c>
+      <c r="B579" s="14" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C579" s="14" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D579" s="37">
+        <v>16491</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A580" s="14">
+        <v>76374401</v>
+      </c>
+      <c r="B580" s="14" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C580" s="14" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D580" s="37">
+        <v>16491</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A581" s="14">
+        <v>76533940</v>
+      </c>
+      <c r="B581" s="14" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C581" s="14" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D581" s="37">
+        <v>50932</v>
       </c>
     </row>
   </sheetData>

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡발주양식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485A55B9-0FD4-4026-994B-037DDEB9F048}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA5A6872-904A-43A3-8F47-2C96A696AEAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="1193">
   <si>
     <t>주문상품</t>
   </si>
@@ -4429,7 +4429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.625" bestFit="1" customWidth="1"/>
@@ -4476,15 +4476,15 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>'sku 정보'!$G2</f>
-        <v>보아르투웨이텀블러-핑크</v>
+        <v>오아블링-화이트</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>'sku 정보'!$H2</f>
-        <v>A01695</v>
+        <v>B0023</v>
       </c>
       <c r="C2">
         <f>'sku 정보'!$I2</f>
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -4500,25 +4500,25 @@
       </c>
       <c r="J2">
         <f>'sku 정보'!$J2</f>
-        <v>14129</v>
+        <v>23100</v>
       </c>
       <c r="K2">
         <f>$J2*$C2</f>
-        <v>706450</v>
+        <v>369600</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>'sku 정보'!$G3</f>
-        <v>보아르투웨이텀블러-블랙</v>
+        <v>오아이지탭램프</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>'sku 정보'!$H3</f>
-        <v>E0442</v>
+        <v>L0065</v>
       </c>
       <c r="C3">
         <f>'sku 정보'!$I3</f>
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -4534,25 +4534,25 @@
       </c>
       <c r="J3">
         <f>'sku 정보'!$J3</f>
-        <v>14129</v>
+        <v>20210</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K7" si="0">$J3*$C3</f>
-        <v>296709</v>
+        <f t="shared" ref="K3:K19" si="0">$J3*$C3</f>
+        <v>121260</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>'sku 정보'!$G4</f>
-        <v>보아르투웨이폴든텀블러-민트</v>
+        <v>오아무드센서등</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>'sku 정보'!$H4</f>
-        <v>A02701</v>
+        <v>L0080</v>
       </c>
       <c r="C4">
         <f>'sku 정보'!$I4</f>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -4568,25 +4568,25 @@
       </c>
       <c r="J4">
         <f>'sku 정보'!$J4</f>
-        <v>23359</v>
+        <v>14088</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>467180</v>
+        <v>169056</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>'sku 정보'!$G5</f>
-        <v>보아르투웨이텀블러-아이보리</v>
+        <v>오아무드워머-화이트</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>'sku 정보'!$H5</f>
-        <v>E0446</v>
+        <v>L0083</v>
       </c>
       <c r="C5">
         <f>'sku 정보'!$I5</f>
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -4602,25 +4602,25 @@
       </c>
       <c r="J5">
         <f>'sku 정보'!$J5</f>
-        <v>14129</v>
+        <v>29634</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>240193</v>
+        <v>177804</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>'sku 정보'!$G6</f>
-        <v>보아르투웨이폴든텀블러-핑크</v>
+        <v>오아우드led시계R</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>'sku 정보'!$H6</f>
-        <v>A02700</v>
+        <v>C0324</v>
       </c>
       <c r="C6">
         <f>'sku 정보'!$I6</f>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -4636,25 +4636,25 @@
       </c>
       <c r="J6">
         <f>'sku 정보'!$J6</f>
-        <v>23359</v>
+        <v>42500</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>280308</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>'sku 정보'!$G7</f>
-        <v>보아르투웨이텀블러-민트</v>
+        <v>오아우드led시계S</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>'sku 정보'!$H7</f>
-        <v>A01694</v>
+        <v>C0325</v>
       </c>
       <c r="C7">
         <f>'sku 정보'!$I7</f>
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -4670,11 +4670,419 @@
       </c>
       <c r="J7">
         <f>'sku 정보'!$J7</f>
-        <v>14129</v>
+        <v>42500</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>1412900</v>
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <f>'sku 정보'!$G8</f>
+        <v>보아르컴플릿20L쓰레기통-베이지</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <f>'sku 정보'!$H8</f>
+        <v>S0287</v>
+      </c>
+      <c r="C8">
+        <f>'sku 정보'!$I8</f>
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>37876</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <f>'sku 정보'!$J8</f>
+        <v>33932</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>67864</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f>'sku 정보'!$G9</f>
+        <v>오아모던미니알람시계-화이트</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <f>'sku 정보'!$H9</f>
+        <v>A00077</v>
+      </c>
+      <c r="C9">
+        <f>'sku 정보'!$I9</f>
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>37876</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <f>'sku 정보'!$J9</f>
+        <v>9685</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>96850</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f>'sku 정보'!$G10</f>
+        <v>오아모던미니LED시계-베이지</v>
+      </c>
+      <c r="B10" s="3" t="str">
+        <f>'sku 정보'!$H10</f>
+        <v>A01116</v>
+      </c>
+      <c r="C10">
+        <f>'sku 정보'!$I10</f>
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>37876</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <f>'sku 정보'!$J10</f>
+        <v>35620</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>213720</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f>'sku 정보'!$G11</f>
+        <v>보아르컴플릿D20L쓰레기통-베이지</v>
+      </c>
+      <c r="B11" s="3" t="str">
+        <f>'sku 정보'!$H11</f>
+        <v>A01222</v>
+      </c>
+      <c r="C11">
+        <f>'sku 정보'!$I11</f>
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <v>37876</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <f>'sku 정보'!$J11</f>
+        <v>40800</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>408000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
+        <f>'sku 정보'!$G12</f>
+        <v>오아포켓터-베이지</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <f>'sku 정보'!$H12</f>
+        <v>A01488</v>
+      </c>
+      <c r="C12">
+        <f>'sku 정보'!$I12</f>
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>37876</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <f>'sku 정보'!$J12</f>
+        <v>20860</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>41720</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="str">
+        <f>'sku 정보'!$G13</f>
+        <v>오아윙즈스탠드-화이트</v>
+      </c>
+      <c r="B13" s="3" t="str">
+        <f>'sku 정보'!$H13</f>
+        <v>A01744</v>
+      </c>
+      <c r="C13">
+        <f>'sku 정보'!$I13</f>
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13">
+        <v>37876</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <f>'sku 정보'!$J13</f>
+        <v>50430</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>504300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="str">
+        <f>'sku 정보'!$G14</f>
+        <v>오아버블디스펜서-화이트</v>
+      </c>
+      <c r="B14" s="3" t="str">
+        <f>'sku 정보'!$H14</f>
+        <v>A01588</v>
+      </c>
+      <c r="C14">
+        <f>'sku 정보'!$I14</f>
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>37876</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14">
+        <f>'sku 정보'!$J14</f>
+        <v>18538</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>278070</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
+        <f>'sku 정보'!$G15</f>
+        <v>보아르컴플릿10L쓰레기통-베이지</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <f>'sku 정보'!$H15</f>
+        <v>A01869</v>
+      </c>
+      <c r="C15">
+        <f>'sku 정보'!$I15</f>
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>37876</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <f>'sku 정보'!$J15</f>
+        <v>21638</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>108190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <f>'sku 정보'!$G16</f>
+        <v>오아포인트클락-핑크</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <f>'sku 정보'!$H16</f>
+        <v>A01853</v>
+      </c>
+      <c r="C16">
+        <f>'sku 정보'!$I16</f>
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>37876</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <f>'sku 정보'!$J16</f>
+        <v>14885</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>119080</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="str">
+        <f>'sku 정보'!$G17</f>
+        <v>오아젤디스펜서-화이트</v>
+      </c>
+      <c r="B17" s="3" t="str">
+        <f>'sku 정보'!$H17</f>
+        <v>A01819</v>
+      </c>
+      <c r="C17">
+        <f>'sku 정보'!$I17</f>
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17">
+        <v>37876</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <f>'sku 정보'!$J17</f>
+        <v>31296</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>375552</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="str">
+        <f>'sku 정보'!$G18</f>
+        <v>오아젤디스펜서-실버</v>
+      </c>
+      <c r="B18" s="3" t="str">
+        <f>'sku 정보'!$H18</f>
+        <v>A02554</v>
+      </c>
+      <c r="C18">
+        <f>'sku 정보'!$I18</f>
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18">
+        <v>37876</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <f>'sku 정보'!$J18</f>
+        <v>31296</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>93888</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="str">
+        <f>'sku 정보'!$G19</f>
+        <v>오아데이클락-베이지</v>
+      </c>
+      <c r="B19" s="3" t="str">
+        <f>'sku 정보'!$H19</f>
+        <v>M01628</v>
+      </c>
+      <c r="C19">
+        <f>'sku 정보'!$I19</f>
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <v>37876</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <f>'sku 정보'!$J19</f>
+        <v>50853</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>508530</v>
       </c>
     </row>
   </sheetData>
@@ -4752,22 +5160,22 @@
         <v>25326</v>
       </c>
       <c r="F2" s="7">
-        <v>60380162</v>
+        <v>5359040</v>
       </c>
       <c r="G2" s="7" t="str">
         <f t="shared" ref="G2:G65" si="0">IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
-        <v>보아르투웨이텀블러-핑크</v>
+        <v>오아블링-화이트</v>
       </c>
       <c r="H2" s="7" t="str">
         <f t="shared" ref="H2:H65" si="1">IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
-        <v>A01695</v>
+        <v>B0023</v>
       </c>
       <c r="I2" s="7">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J2" s="7">
         <f t="shared" ref="J2:J65" si="2">IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
-        <v>14129</v>
+        <v>23100</v>
       </c>
       <c r="L2">
         <v>25326</v>
@@ -4794,22 +5202,22 @@
         <v>26666</v>
       </c>
       <c r="F3" s="7">
-        <v>53569741</v>
+        <v>8837870</v>
       </c>
       <c r="G3" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르투웨이텀블러-블랙</v>
+        <v>오아이지탭램프</v>
       </c>
       <c r="H3" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>E0442</v>
+        <v>L0065</v>
       </c>
       <c r="I3" s="7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J3" s="7">
         <f t="shared" si="2"/>
-        <v>14129</v>
+        <v>20210</v>
       </c>
       <c r="L3">
         <v>26666</v>
@@ -4836,22 +5244,22 @@
         <v>21976</v>
       </c>
       <c r="F4" s="7">
-        <v>73316684</v>
+        <v>16303007</v>
       </c>
       <c r="G4" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르투웨이폴든텀블러-민트</v>
+        <v>오아무드센서등</v>
       </c>
       <c r="H4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A02701</v>
+        <v>L0080</v>
       </c>
       <c r="I4" s="7">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" si="2"/>
-        <v>23359</v>
+        <v>14088</v>
       </c>
       <c r="L4">
         <v>21976</v>
@@ -4878,22 +5286,22 @@
         <v>72360</v>
       </c>
       <c r="F5" s="7">
-        <v>53583387</v>
+        <v>22441147</v>
       </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르투웨이텀블러-아이보리</v>
+        <v>오아무드워머-화이트</v>
       </c>
       <c r="H5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>E0446</v>
+        <v>L0083</v>
       </c>
       <c r="I5" s="7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
-        <v>14129</v>
+        <v>29634</v>
       </c>
       <c r="L5">
         <v>72360</v>
@@ -4920,22 +5328,22 @@
         <v>85090</v>
       </c>
       <c r="F6" s="7">
-        <v>73316683</v>
+        <v>34348663</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르투웨이폴든텀블러-핑크</v>
+        <v>오아우드led시계R</v>
       </c>
       <c r="H6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A02700</v>
+        <v>C0324</v>
       </c>
       <c r="I6" s="7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>23359</v>
+        <v>42500</v>
       </c>
       <c r="L6">
         <v>85090</v>
@@ -4962,22 +5370,22 @@
         <v>58960</v>
       </c>
       <c r="F7" s="7">
-        <v>60450424</v>
+        <v>34535085</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>보아르투웨이텀블러-민트</v>
+        <v>오아우드led시계S</v>
       </c>
       <c r="H7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>A01694</v>
+        <v>C0325</v>
       </c>
       <c r="I7" s="7">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="2"/>
-        <v>14129</v>
+        <v>42500</v>
       </c>
       <c r="L7">
         <v>58960</v>
@@ -5003,19 +5411,23 @@
       <c r="D8" s="34">
         <v>71690</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7">
+      <c r="F8" s="7">
+        <v>45342904</v>
+      </c>
+      <c r="G8" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
+        <v>보아르컴플릿20L쓰레기통-베이지</v>
+      </c>
+      <c r="H8" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="7"/>
+        <v>S0287</v>
+      </c>
+      <c r="I8" s="7">
+        <v>2</v>
+      </c>
       <c r="J8" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>33932</v>
       </c>
       <c r="L8">
         <v>71690</v>
@@ -5041,19 +5453,23 @@
       <c r="D9" s="34">
         <v>64990</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7">
+      <c r="F9" s="7">
+        <v>52362395</v>
+      </c>
+      <c r="G9" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+        <v>오아모던미니알람시계-화이트</v>
+      </c>
+      <c r="H9" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="7"/>
+        <v>A00077</v>
+      </c>
+      <c r="I9" s="7">
+        <v>10</v>
+      </c>
       <c r="J9" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9685</v>
       </c>
       <c r="L9">
         <v>64990</v>
@@ -5079,19 +5495,23 @@
       <c r="D10" s="34">
         <v>61640</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7">
+      <c r="F10" s="7">
+        <v>52390638</v>
+      </c>
+      <c r="G10" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
+        <v>오아모던미니LED시계-베이지</v>
+      </c>
+      <c r="H10" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="7"/>
+        <v>A01116</v>
+      </c>
+      <c r="I10" s="7">
+        <v>6</v>
+      </c>
       <c r="J10" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>35620</v>
       </c>
       <c r="L10">
         <v>61640</v>
@@ -5117,19 +5537,23 @@
       <c r="D11" s="34">
         <v>40066</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7">
+      <c r="F11" s="7">
+        <v>56663811</v>
+      </c>
+      <c r="G11" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
+        <v>보아르컴플릿D20L쓰레기통-베이지</v>
+      </c>
+      <c r="H11" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="7"/>
+        <v>A01222</v>
+      </c>
+      <c r="I11" s="7">
+        <v>10</v>
+      </c>
       <c r="J11" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>40800</v>
       </c>
       <c r="L11">
         <v>40066</v>
@@ -5155,19 +5579,23 @@
       <c r="D12" s="34">
         <v>38056</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7">
+      <c r="F12" s="7">
+        <v>59058036</v>
+      </c>
+      <c r="G12" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
+        <v>오아포켓터-베이지</v>
+      </c>
+      <c r="H12" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="7"/>
+        <v>A01488</v>
+      </c>
+      <c r="I12" s="7">
+        <v>2</v>
+      </c>
       <c r="J12" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20860</v>
       </c>
       <c r="L12">
         <v>38056</v>
@@ -5190,19 +5618,23 @@
       <c r="D13" s="34">
         <v>40736</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7">
+      <c r="F13" s="7">
+        <v>61923953</v>
+      </c>
+      <c r="G13" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="7">
+        <v>오아윙즈스탠드-화이트</v>
+      </c>
+      <c r="H13" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="7"/>
+        <v>A01744</v>
+      </c>
+      <c r="I13" s="7">
+        <v>10</v>
+      </c>
       <c r="J13" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50430</v>
       </c>
       <c r="L13">
         <v>40736</v>
@@ -5225,19 +5657,23 @@
       <c r="D14" s="34">
         <v>45426</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7">
+      <c r="F14" s="7">
+        <v>62575565</v>
+      </c>
+      <c r="G14" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
+        <v>오아버블디스펜서-화이트</v>
+      </c>
+      <c r="H14" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="7"/>
+        <v>A01588</v>
+      </c>
+      <c r="I14" s="7">
+        <v>15</v>
+      </c>
       <c r="J14" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18538</v>
       </c>
       <c r="L14">
         <v>45426</v>
@@ -5260,19 +5696,23 @@
       <c r="D15" s="34">
         <v>36046</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7">
+      <c r="F15" s="7">
+        <v>63346456</v>
+      </c>
+      <c r="G15" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="7">
+        <v>보아르컴플릿10L쓰레기통-베이지</v>
+      </c>
+      <c r="H15" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="7"/>
+        <v>A01869</v>
+      </c>
+      <c r="I15" s="7">
+        <v>5</v>
+      </c>
       <c r="J15" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21638</v>
       </c>
       <c r="L15">
         <v>36046</v>
@@ -5295,19 +5735,23 @@
       <c r="D16" s="34">
         <v>29413</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7">
+      <c r="F16" s="7">
+        <v>64114088</v>
+      </c>
+      <c r="G16" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="7">
+        <v>오아포인트클락-핑크</v>
+      </c>
+      <c r="H16" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="7"/>
+        <v>A01853</v>
+      </c>
+      <c r="I16" s="7">
+        <v>8</v>
+      </c>
       <c r="J16" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14885</v>
       </c>
       <c r="L16">
         <v>29413</v>
@@ -5330,19 +5774,23 @@
       <c r="D17" s="34">
         <v>30016</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7">
+      <c r="F17" s="7">
+        <v>64270608</v>
+      </c>
+      <c r="G17" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="7">
+        <v>오아젤디스펜서-화이트</v>
+      </c>
+      <c r="H17" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="7"/>
+        <v>A01819</v>
+      </c>
+      <c r="I17" s="7">
+        <v>12</v>
+      </c>
       <c r="J17" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>31296</v>
       </c>
       <c r="L17">
         <v>30016</v>
@@ -5365,19 +5813,23 @@
       <c r="D18" s="34">
         <v>30016</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7">
+      <c r="F18" s="7">
+        <v>69279032</v>
+      </c>
+      <c r="G18" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
+        <v>오아젤디스펜서-실버</v>
+      </c>
+      <c r="H18" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="7"/>
+        <v>A02554</v>
+      </c>
+      <c r="I18" s="7">
+        <v>3</v>
+      </c>
       <c r="J18" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>31296</v>
       </c>
       <c r="L18">
         <v>30016</v>
@@ -5400,19 +5852,23 @@
       <c r="D19" s="34">
         <v>30016</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7">
+      <c r="F19" s="7">
+        <v>71030052</v>
+      </c>
+      <c r="G19" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="7">
+        <v>오아데이클락-베이지</v>
+      </c>
+      <c r="H19" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="7"/>
+        <v>M01628</v>
+      </c>
+      <c r="I19" s="7">
+        <v>10</v>
+      </c>
       <c r="J19" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50853</v>
       </c>
       <c r="L19">
         <v>30016</v>
@@ -12994,7 +13450,7 @@
         <v>565</v>
       </c>
       <c r="D236" s="34">
-        <v>62980</v>
+        <v>60720</v>
       </c>
       <c r="F236" s="7"/>
       <c r="G236" s="7">
@@ -13015,7 +13471,7 @@
       </c>
       <c r="M236" t="b">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.3">
@@ -14744,7 +15200,7 @@
         <v>609</v>
       </c>
       <c r="D286" s="34">
-        <v>172190</v>
+        <v>173530</v>
       </c>
       <c r="F286" s="7"/>
       <c r="G286" s="7">
@@ -14765,7 +15221,7 @@
       </c>
       <c r="M286" t="b">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.3">
@@ -14849,7 +15305,7 @@
         <v>611</v>
       </c>
       <c r="D289" s="34">
-        <v>78390</v>
+        <v>73030</v>
       </c>
       <c r="F289" s="7"/>
       <c r="G289" s="7">
@@ -14870,7 +15326,7 @@
       </c>
       <c r="M289" t="b">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.3">

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="1191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="1195">
   <si>
     <t>주문상품</t>
   </si>
@@ -3625,6 +3625,20 @@
   </si>
   <si>
     <t>A03243</t>
+  </si>
+  <si>
+    <t>오아에어스트레이트-핑크</t>
+  </si>
+  <si>
+    <t>오아에어스트레이트-베이지</t>
+  </si>
+  <si>
+    <t>A03267</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A03268</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3935,7 +3949,87 @@
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5071,7 +5165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L581"/>
+  <dimension ref="A1:L583"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="28" bestFit="1" customWidth="1"/>
@@ -19798,53 +19892,103 @@
         <v>50932</v>
       </c>
     </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A582" s="13">
+        <v>77463489</v>
+      </c>
+      <c r="B582" s="13" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C582" s="13" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D582" s="36">
+        <v>102810</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A583" s="13">
+        <v>77463490</v>
+      </c>
+      <c r="B583" s="13" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C583" s="13" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D583" s="36">
+        <v>102810</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L510"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A378:A410 A412:A1048576 A1:A372">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+  <conditionalFormatting sqref="A378:A410 A412:A581 A1:A372 A584:A1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45:F49">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  <conditionalFormatting sqref="A1:A581 A584:A1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A378:B379 A382:B410 A380:A381 A412:B1048576 A1:B122 A124:B176 A123 A178:B372 A177">
-    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
+  <conditionalFormatting sqref="A378:B379 A382:B410 A380:A381 A412:B581 A1:B122 A124:B176 A123 A178:B372 A177 A584:B1048576">
+    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A382:B410 A380:A381 A1:B122 A412:B1048576 A124:B176 A123 A178:B379 A177">
-    <cfRule type="duplicateValues" dxfId="5" priority="27"/>
+  <conditionalFormatting sqref="A382:B410 A380:A381 A1:B122 A412:B581 A124:B176 A123 A178:B379 A177 A584:B1048576">
+    <cfRule type="duplicateValues" dxfId="13" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C468:C1048576 C114:C389 C1:C112">
-    <cfRule type="duplicateValues" dxfId="4" priority="29"/>
+  <conditionalFormatting sqref="C468:C581 C114:C389 C1:C112 C584:C1048576">
+    <cfRule type="duplicateValues" dxfId="12" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B178:B1048576 B1:B122 B124:B176">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  <conditionalFormatting sqref="B178:B581 B1:B122 B124:B176 B584:B1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A177 A1:C122 A124:C176 A123 C123 C177 A178:C1048576">
+  <conditionalFormatting sqref="A177 A1:C122 A124:C176 A123 C123 C177 A178:C581 A584:C1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F9">
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:A583">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:A583">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:B583">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:B583">
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C582:C583">
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B582:B583">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="A582:C583">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="1209">
   <si>
     <t>주문상품</t>
   </si>
@@ -3638,6 +3638,55 @@
   </si>
   <si>
     <t>A03268</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오아클린이스쿨-코튼핑크</t>
+  </si>
+  <si>
+    <t>오아클린이스쿨-클라우디블루</t>
+  </si>
+  <si>
+    <t>오아클린이워터스쿨-코튼핑크</t>
+  </si>
+  <si>
+    <t>오아클린이워터스쿨-클라우디블루</t>
+  </si>
+  <si>
+    <t>오아클린이퓨어T-포그밀크</t>
+  </si>
+  <si>
+    <t>오아모근제거기-화이트</t>
+  </si>
+  <si>
+    <t>보아르다이닝전동후추그라인더-화이트</t>
+  </si>
+  <si>
+    <t>A03172</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A03173</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A03174</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A03175</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A03225</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A02814</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A03124</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5165,7 +5214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L583"/>
+  <dimension ref="A1:L590"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="28" bestFit="1" customWidth="1"/>
@@ -19918,6 +19967,104 @@
       </c>
       <c r="D583" s="36">
         <v>102810</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A584" s="13">
+        <v>78907466</v>
+      </c>
+      <c r="B584" s="13" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C584" s="13" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D584" s="36">
+        <v>27531</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A585" s="13">
+        <v>78907465</v>
+      </c>
+      <c r="B585" s="13" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C585" s="13" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D585" s="36">
+        <v>27531</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A586" s="13">
+        <v>78903848</v>
+      </c>
+      <c r="B586" s="13" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C586" s="13" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D586" s="36">
+        <v>27531</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A587" s="13">
+        <v>78903849</v>
+      </c>
+      <c r="B587" s="13" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C587" s="13" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D587" s="36">
+        <v>27531</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A588" s="13">
+        <v>78621004</v>
+      </c>
+      <c r="B588" s="13" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C588" s="13" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D588" s="36">
+        <v>20631</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A589" s="13">
+        <v>78867502</v>
+      </c>
+      <c r="B589" s="13" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C589" s="13" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D589" s="36">
+        <v>29601</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A590" s="13">
+        <v>78625461</v>
+      </c>
+      <c r="B590" s="13" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C590" s="13" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D590" s="36">
+        <v>34431</v>
       </c>
     </row>
   </sheetData>

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\02. 발주용 매입가 파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\17. claude\po\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="1209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="1211">
   <si>
     <t>주문상품</t>
   </si>
@@ -3687,6 +3687,13 @@
   </si>
   <si>
     <t>A03124</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오아포핸드손마사지기-샌드크림</t>
+  </si>
+  <si>
+    <t>A03224</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3998,7 +4005,347 @@
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="58">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5214,7 +5561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L590"/>
+  <dimension ref="A1:L591"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="28" bestFit="1" customWidth="1"/>
@@ -5274,16 +5621,16 @@
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7">
-        <f t="shared" ref="G2:G65" si="0">IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
+        <f>IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H2" s="7">
-        <f t="shared" ref="H2:H65" si="1">IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
+        <f>IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7">
-        <f t="shared" ref="J2:J65" si="2">IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
+        <f>IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" t="s">
@@ -5305,16 +5652,16 @@
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F3,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H3" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F3,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F3,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L3" t="s">
@@ -5336,16 +5683,16 @@
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F4,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H4" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F4,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F4,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L4" t="s">
@@ -5367,16 +5714,16 @@
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F5,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H5" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F5,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F5,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L5" t="s">
@@ -5398,16 +5745,16 @@
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F6,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H6" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F6,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F6,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L6" t="s">
@@ -5429,16 +5776,16 @@
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F7,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H7" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F7,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F7,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L7" t="s">
@@ -5460,16 +5807,16 @@
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F8,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H8" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F8,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F8,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L8" s="5" t="s">
@@ -5491,16 +5838,16 @@
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F9,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F9,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F9,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L9" s="5" t="s">
@@ -5522,16 +5869,16 @@
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F10,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H10" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F10,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F10,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L10" s="5" t="s">
@@ -5553,16 +5900,16 @@
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F11,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F11,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F11,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L11" s="5" t="s">
@@ -5584,16 +5931,16 @@
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F12,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H12" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F12,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F12,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5612,16 +5959,16 @@
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F13,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F13,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F13,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5640,16 +5987,16 @@
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F14,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F14,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F14,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5668,16 +6015,16 @@
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F15,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F15,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F15,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5696,16 +6043,16 @@
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F16,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F16,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F16,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5724,16 +6071,16 @@
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F17,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F17,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F17,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5752,16 +6099,16 @@
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F18,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F18,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F18,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5780,16 +6127,16 @@
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F19,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F19,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F19,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5808,16 +6155,16 @@
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F20,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H20" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F20,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F20,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5836,16 +6183,16 @@
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F21,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H21" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F21,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F21,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5864,16 +6211,16 @@
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F22,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F22,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F22,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5892,16 +6239,16 @@
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F23,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H23" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F23,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F23,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5920,16 +6267,16 @@
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F24,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H24" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F24,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F24,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5948,16 +6295,16 @@
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F25,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F25,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F25,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5976,16 +6323,16 @@
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F26,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F26,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F26,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6004,16 +6351,16 @@
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F27,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F27,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F27,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6032,16 +6379,16 @@
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F28,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F28,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F28,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6060,16 +6407,16 @@
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F29,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F29,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F29,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6088,16 +6435,16 @@
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F30,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F30,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F30,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6116,16 +6463,16 @@
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F31,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F31,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F31,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6144,16 +6491,16 @@
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F32,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F32,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F32,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6172,16 +6519,16 @@
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F33,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F33,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F33,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6200,16 +6547,16 @@
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F34,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H34" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F34,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F34,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6228,16 +6575,16 @@
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F35,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H35" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F35,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F35,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6256,16 +6603,16 @@
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F36,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H36" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F36,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F36,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6284,16 +6631,16 @@
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F37,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H37" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F37,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F37,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6312,16 +6659,16 @@
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F38,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F38,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F38,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6340,16 +6687,16 @@
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F39,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H39" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F39,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F39,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6368,16 +6715,16 @@
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F40,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H40" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F40,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F40,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6396,16 +6743,16 @@
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F41,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H41" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F41,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F41,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6425,16 +6772,16 @@
       <c r="E42" s="4"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F42,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F42,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F42,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6453,16 +6800,16 @@
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F43,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H43" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F43,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I43" s="7"/>
       <c r="J43" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F43,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6481,16 +6828,16 @@
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F44,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H44" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F44,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F44,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6509,16 +6856,16 @@
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F45,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H45" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F45,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F45,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6537,16 +6884,16 @@
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F46,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H46" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F46,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I46" s="7"/>
       <c r="J46" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F46,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6565,16 +6912,16 @@
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F47,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H47" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F47,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F47,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6593,16 +6940,16 @@
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F48,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H48" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F48,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F48,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6621,16 +6968,16 @@
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F49,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F49,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F49,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6649,16 +6996,16 @@
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F50,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H50" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F50,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F50,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6677,16 +7024,16 @@
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F51,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H51" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F51,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I51" s="7"/>
       <c r="J51" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F51,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6705,16 +7052,16 @@
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F52,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H52" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F52,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I52" s="7"/>
       <c r="J52" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F52,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6733,16 +7080,16 @@
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F53,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H53" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F53,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F53,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6761,16 +7108,16 @@
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F54,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H54" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F54,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I54" s="7"/>
       <c r="J54" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F54,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6789,16 +7136,16 @@
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F55,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H55" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F55,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F55,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6817,16 +7164,16 @@
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F56,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H56" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F56,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F56,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6845,16 +7192,16 @@
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F57,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H57" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F57,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F57,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6873,16 +7220,16 @@
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F58,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H58" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F58,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F58,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6901,16 +7248,16 @@
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F59,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H59" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F59,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F59,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6929,16 +7276,16 @@
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F60,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H60" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F60,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F60,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6957,16 +7304,16 @@
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F61,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H61" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F61,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F61,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6985,16 +7332,16 @@
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F62,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H62" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F62,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F62,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7013,16 +7360,16 @@
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F63,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H63" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F63,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F63,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7041,16 +7388,16 @@
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F64,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H64" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F64,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F64,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7069,16 +7416,16 @@
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7">
-        <f t="shared" si="0"/>
+        <f>IFERROR(VLOOKUP($F65,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H65" s="7">
-        <f t="shared" si="1"/>
+        <f>IFERROR(VLOOKUP($F65,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="7">
-        <f t="shared" si="2"/>
+        <f>IFERROR(VLOOKUP($F65,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7097,16 +7444,16 @@
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7">
-        <f t="shared" ref="G66:G129" si="3">IFERROR(VLOOKUP($F66,$A:$B,2,0),0)</f>
+        <f>IFERROR(VLOOKUP($F66,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H66" s="7">
-        <f t="shared" ref="H66:H129" si="4">IFERROR(VLOOKUP($F66,$A:$D,3,0),0)</f>
+        <f>IFERROR(VLOOKUP($F66,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="7">
-        <f t="shared" ref="J66:J129" si="5">IFERROR(VLOOKUP($F66,$A:$D,4,0),0)</f>
+        <f>IFERROR(VLOOKUP($F66,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7125,16 +7472,16 @@
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F67,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H67" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F67,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F67,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7153,16 +7500,16 @@
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F68,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H68" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F68,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F68,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7181,16 +7528,16 @@
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F69,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H69" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F69,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F69,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7209,16 +7556,16 @@
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F70,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H70" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F70,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F70,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7237,16 +7584,16 @@
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F71,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H71" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F71,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F71,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7265,16 +7612,16 @@
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F72,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H72" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F72,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F72,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7293,16 +7640,16 @@
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F73,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H73" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F73,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I73" s="7"/>
       <c r="J73" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F73,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7321,16 +7668,16 @@
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F74,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H74" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F74,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F74,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7349,16 +7696,16 @@
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F75,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H75" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F75,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F75,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7377,16 +7724,16 @@
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F76,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H76" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F76,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F76,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7405,16 +7752,16 @@
       </c>
       <c r="F77" s="7"/>
       <c r="G77" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F77,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H77" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F77,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F77,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7433,16 +7780,16 @@
       </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F78,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H78" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F78,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I78" s="7"/>
       <c r="J78" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F78,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7461,16 +7808,16 @@
       </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F79,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H79" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F79,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F79,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7489,16 +7836,16 @@
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F80,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H80" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F80,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I80" s="7"/>
       <c r="J80" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F80,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7517,16 +7864,16 @@
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F81,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H81" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F81,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I81" s="7"/>
       <c r="J81" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F81,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7545,16 +7892,16 @@
       </c>
       <c r="F82" s="7"/>
       <c r="G82" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F82,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H82" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F82,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F82,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7573,16 +7920,16 @@
       </c>
       <c r="F83" s="7"/>
       <c r="G83" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F83,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H83" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F83,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F83,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7601,16 +7948,16 @@
       </c>
       <c r="F84" s="7"/>
       <c r="G84" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F84,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H84" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F84,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F84,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7629,16 +7976,16 @@
       </c>
       <c r="F85" s="7"/>
       <c r="G85" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F85,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H85" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F85,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F85,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7657,16 +8004,16 @@
       </c>
       <c r="F86" s="7"/>
       <c r="G86" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F86,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H86" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F86,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I86" s="7"/>
       <c r="J86" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F86,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7685,16 +8032,16 @@
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F87,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H87" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F87,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F87,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7713,16 +8060,16 @@
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F88,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H88" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F88,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F88,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7741,16 +8088,16 @@
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F89,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H89" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F89,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F89,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7769,16 +8116,16 @@
       </c>
       <c r="F90" s="7"/>
       <c r="G90" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F90,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H90" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F90,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F90,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7797,16 +8144,16 @@
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F91,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H91" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F91,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I91" s="7"/>
       <c r="J91" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F91,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7825,16 +8172,16 @@
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F92,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H92" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F92,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F92,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7853,16 +8200,16 @@
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F93,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H93" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F93,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I93" s="7"/>
       <c r="J93" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F93,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7881,16 +8228,16 @@
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F94,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H94" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F94,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I94" s="7"/>
       <c r="J94" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F94,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7909,16 +8256,16 @@
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F95,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H95" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F95,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I95" s="7"/>
       <c r="J95" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F95,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7937,16 +8284,16 @@
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F96,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H96" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F96,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I96" s="7"/>
       <c r="J96" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F96,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7965,16 +8312,16 @@
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F97,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H97" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F97,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F97,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7993,16 +8340,16 @@
       </c>
       <c r="F98" s="7"/>
       <c r="G98" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F98,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H98" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F98,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F98,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8021,16 +8368,16 @@
       </c>
       <c r="F99" s="7"/>
       <c r="G99" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F99,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H99" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F99,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F99,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8049,16 +8396,16 @@
       </c>
       <c r="F100" s="7"/>
       <c r="G100" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F100,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H100" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F100,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F100,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8077,16 +8424,16 @@
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F101,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H101" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F101,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F101,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8105,16 +8452,16 @@
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F102,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H102" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F102,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I102" s="7"/>
       <c r="J102" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F102,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8133,16 +8480,16 @@
       </c>
       <c r="F103" s="7"/>
       <c r="G103" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F103,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H103" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F103,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F103,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8161,16 +8508,16 @@
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F104,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H104" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F104,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I104" s="7"/>
       <c r="J104" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F104,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8189,16 +8536,16 @@
       </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F105,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H105" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F105,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F105,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8217,16 +8564,16 @@
       </c>
       <c r="F106" s="7"/>
       <c r="G106" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F106,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H106" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F106,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I106" s="7"/>
       <c r="J106" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F106,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8245,16 +8592,16 @@
       </c>
       <c r="F107" s="7"/>
       <c r="G107" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F107,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H107" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F107,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I107" s="7"/>
       <c r="J107" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F107,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8273,16 +8620,16 @@
       </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F108,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H108" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F108,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I108" s="7"/>
       <c r="J108" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F108,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8301,16 +8648,16 @@
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F109,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H109" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F109,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I109" s="7"/>
       <c r="J109" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F109,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8329,16 +8676,16 @@
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F110,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H110" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F110,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I110" s="7"/>
       <c r="J110" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F110,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8357,16 +8704,16 @@
       </c>
       <c r="F111" s="7"/>
       <c r="G111" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F111,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H111" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F111,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I111" s="7"/>
       <c r="J111" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F111,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8385,16 +8732,16 @@
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F112,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H112" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F112,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I112" s="7"/>
       <c r="J112" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F112,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8413,16 +8760,16 @@
       </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F113,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H113" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F113,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I113" s="7"/>
       <c r="J113" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F113,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8441,16 +8788,16 @@
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F114,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H114" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F114,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F114,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8469,16 +8816,16 @@
       </c>
       <c r="F115" s="7"/>
       <c r="G115" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F115,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H115" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F115,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I115" s="7"/>
       <c r="J115" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F115,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8497,16 +8844,16 @@
       </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F116,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H116" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F116,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I116" s="7"/>
       <c r="J116" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F116,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8525,16 +8872,16 @@
       </c>
       <c r="F117" s="7"/>
       <c r="G117" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F117,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H117" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F117,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I117" s="7"/>
       <c r="J117" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F117,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8553,16 +8900,16 @@
       </c>
       <c r="F118" s="7"/>
       <c r="G118" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F118,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H118" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F118,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I118" s="7"/>
       <c r="J118" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F118,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8581,16 +8928,16 @@
       </c>
       <c r="F119" s="7"/>
       <c r="G119" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F119,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H119" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F119,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I119" s="7"/>
       <c r="J119" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F119,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8609,16 +8956,16 @@
       </c>
       <c r="F120" s="7"/>
       <c r="G120" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F120,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H120" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F120,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I120" s="7"/>
       <c r="J120" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F120,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8637,16 +8984,16 @@
       </c>
       <c r="F121" s="7"/>
       <c r="G121" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F121,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H121" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F121,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I121" s="7"/>
       <c r="J121" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F121,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8665,16 +9012,16 @@
       </c>
       <c r="F122" s="7"/>
       <c r="G122" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F122,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H122" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F122,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I122" s="7"/>
       <c r="J122" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F122,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8693,16 +9040,16 @@
       </c>
       <c r="F123" s="7"/>
       <c r="G123" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F123,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H123" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F123,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F123,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8721,16 +9068,16 @@
       </c>
       <c r="F124" s="7"/>
       <c r="G124" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F124,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H124" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F124,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I124" s="7"/>
       <c r="J124" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F124,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8749,16 +9096,16 @@
       </c>
       <c r="F125" s="7"/>
       <c r="G125" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F125,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H125" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F125,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I125" s="7"/>
       <c r="J125" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F125,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8777,16 +9124,16 @@
       </c>
       <c r="F126" s="7"/>
       <c r="G126" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F126,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H126" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F126,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I126" s="7"/>
       <c r="J126" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F126,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8805,16 +9152,16 @@
       </c>
       <c r="F127" s="7"/>
       <c r="G127" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F127,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H127" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F127,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I127" s="7"/>
       <c r="J127" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F127,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8833,16 +9180,16 @@
       </c>
       <c r="F128" s="7"/>
       <c r="G128" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F128,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H128" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F128,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I128" s="7"/>
       <c r="J128" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F128,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8861,16 +9208,16 @@
       </c>
       <c r="F129" s="7"/>
       <c r="G129" s="7">
-        <f t="shared" si="3"/>
+        <f>IFERROR(VLOOKUP($F129,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H129" s="7">
-        <f t="shared" si="4"/>
+        <f>IFERROR(VLOOKUP($F129,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I129" s="7"/>
       <c r="J129" s="7">
-        <f t="shared" si="5"/>
+        <f>IFERROR(VLOOKUP($F129,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8889,16 +9236,16 @@
       </c>
       <c r="F130" s="7"/>
       <c r="G130" s="7">
-        <f t="shared" ref="G130:G193" si="6">IFERROR(VLOOKUP($F130,$A:$B,2,0),0)</f>
+        <f>IFERROR(VLOOKUP($F130,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H130" s="7">
-        <f t="shared" ref="H130:H193" si="7">IFERROR(VLOOKUP($F130,$A:$D,3,0),0)</f>
+        <f>IFERROR(VLOOKUP($F130,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I130" s="7"/>
       <c r="J130" s="7">
-        <f t="shared" ref="J130:J193" si="8">IFERROR(VLOOKUP($F130,$A:$D,4,0),0)</f>
+        <f>IFERROR(VLOOKUP($F130,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8917,16 +9264,16 @@
       </c>
       <c r="F131" s="7"/>
       <c r="G131" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F131,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H131" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F131,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I131" s="7"/>
       <c r="J131" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F131,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8945,16 +9292,16 @@
       </c>
       <c r="F132" s="7"/>
       <c r="G132" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F132,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H132" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F132,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I132" s="7"/>
       <c r="J132" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F132,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -8973,16 +9320,16 @@
       </c>
       <c r="F133" s="7"/>
       <c r="G133" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F133,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H133" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F133,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I133" s="7"/>
       <c r="J133" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F133,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9001,16 +9348,16 @@
       </c>
       <c r="F134" s="7"/>
       <c r="G134" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F134,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H134" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F134,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I134" s="7"/>
       <c r="J134" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F134,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9029,16 +9376,16 @@
       </c>
       <c r="F135" s="7"/>
       <c r="G135" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F135,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H135" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F135,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I135" s="7"/>
       <c r="J135" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F135,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9057,16 +9404,16 @@
       </c>
       <c r="F136" s="7"/>
       <c r="G136" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F136,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H136" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F136,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I136" s="7"/>
       <c r="J136" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F136,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9085,16 +9432,16 @@
       </c>
       <c r="F137" s="7"/>
       <c r="G137" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F137,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H137" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F137,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I137" s="7"/>
       <c r="J137" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F137,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9113,16 +9460,16 @@
       </c>
       <c r="F138" s="7"/>
       <c r="G138" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F138,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H138" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F138,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I138" s="7"/>
       <c r="J138" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F138,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9141,16 +9488,16 @@
       </c>
       <c r="F139" s="7"/>
       <c r="G139" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F139,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H139" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F139,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I139" s="7"/>
       <c r="J139" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F139,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9169,16 +9516,16 @@
       </c>
       <c r="F140" s="7"/>
       <c r="G140" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F140,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H140" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F140,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I140" s="7"/>
       <c r="J140" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F140,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9197,16 +9544,16 @@
       </c>
       <c r="F141" s="7"/>
       <c r="G141" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F141,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H141" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F141,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I141" s="7"/>
       <c r="J141" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F141,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9225,16 +9572,16 @@
       </c>
       <c r="F142" s="7"/>
       <c r="G142" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F142,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H142" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F142,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I142" s="7"/>
       <c r="J142" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F142,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9253,16 +9600,16 @@
       </c>
       <c r="F143" s="7"/>
       <c r="G143" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F143,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H143" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F143,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I143" s="7"/>
       <c r="J143" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F143,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9281,16 +9628,16 @@
       </c>
       <c r="F144" s="7"/>
       <c r="G144" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F144,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H144" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F144,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I144" s="7"/>
       <c r="J144" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F144,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9309,16 +9656,16 @@
       </c>
       <c r="F145" s="7"/>
       <c r="G145" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F145,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H145" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F145,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I145" s="7"/>
       <c r="J145" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F145,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9337,16 +9684,16 @@
       </c>
       <c r="F146" s="7"/>
       <c r="G146" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F146,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H146" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F146,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I146" s="7"/>
       <c r="J146" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F146,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9365,16 +9712,16 @@
       </c>
       <c r="F147" s="7"/>
       <c r="G147" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F147,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H147" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F147,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I147" s="7"/>
       <c r="J147" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F147,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9393,16 +9740,16 @@
       </c>
       <c r="F148" s="7"/>
       <c r="G148" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F148,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H148" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F148,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I148" s="7"/>
       <c r="J148" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F148,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9421,16 +9768,16 @@
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F149,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H149" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F149,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I149" s="7"/>
       <c r="J149" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F149,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9449,16 +9796,16 @@
       </c>
       <c r="F150" s="7"/>
       <c r="G150" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F150,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H150" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F150,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I150" s="7"/>
       <c r="J150" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F150,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9477,16 +9824,16 @@
       </c>
       <c r="F151" s="7"/>
       <c r="G151" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F151,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H151" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F151,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F151,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9505,16 +9852,16 @@
       </c>
       <c r="F152" s="7"/>
       <c r="G152" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F152,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H152" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F152,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I152" s="7"/>
       <c r="J152" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F152,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9533,16 +9880,16 @@
       </c>
       <c r="F153" s="7"/>
       <c r="G153" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F153,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H153" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F153,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I153" s="7"/>
       <c r="J153" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F153,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9561,16 +9908,16 @@
       </c>
       <c r="F154" s="7"/>
       <c r="G154" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F154,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H154" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F154,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F154,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9589,16 +9936,16 @@
       </c>
       <c r="F155" s="7"/>
       <c r="G155" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F155,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H155" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F155,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I155" s="7"/>
       <c r="J155" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F155,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9617,16 +9964,16 @@
       </c>
       <c r="F156" s="7"/>
       <c r="G156" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F156,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H156" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F156,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I156" s="7"/>
       <c r="J156" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F156,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9645,16 +9992,16 @@
       </c>
       <c r="F157" s="7"/>
       <c r="G157" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F157,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H157" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F157,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I157" s="7"/>
       <c r="J157" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F157,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9673,16 +10020,16 @@
       </c>
       <c r="F158" s="7"/>
       <c r="G158" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F158,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H158" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F158,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I158" s="7"/>
       <c r="J158" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F158,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9701,16 +10048,16 @@
       </c>
       <c r="F159" s="7"/>
       <c r="G159" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F159,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H159" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F159,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I159" s="7"/>
       <c r="J159" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F159,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9729,16 +10076,16 @@
       </c>
       <c r="F160" s="7"/>
       <c r="G160" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F160,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H160" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F160,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I160" s="7"/>
       <c r="J160" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F160,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9757,16 +10104,16 @@
       </c>
       <c r="F161" s="7"/>
       <c r="G161" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F161,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H161" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F161,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I161" s="7"/>
       <c r="J161" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F161,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9785,16 +10132,16 @@
       </c>
       <c r="F162" s="7"/>
       <c r="G162" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F162,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H162" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F162,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I162" s="7"/>
       <c r="J162" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F162,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9813,16 +10160,16 @@
       </c>
       <c r="F163" s="7"/>
       <c r="G163" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F163,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H163" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F163,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I163" s="7"/>
       <c r="J163" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F163,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9841,16 +10188,16 @@
       </c>
       <c r="F164" s="7"/>
       <c r="G164" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F164,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H164" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F164,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I164" s="7"/>
       <c r="J164" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F164,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9869,16 +10216,16 @@
       </c>
       <c r="F165" s="7"/>
       <c r="G165" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F165,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H165" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F165,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I165" s="7"/>
       <c r="J165" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F165,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9897,16 +10244,16 @@
       </c>
       <c r="F166" s="7"/>
       <c r="G166" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F166,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H166" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F166,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I166" s="7"/>
       <c r="J166" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F166,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9925,16 +10272,16 @@
       </c>
       <c r="F167" s="7"/>
       <c r="G167" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F167,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H167" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F167,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I167" s="7"/>
       <c r="J167" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F167,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9953,16 +10300,16 @@
       </c>
       <c r="F168" s="7"/>
       <c r="G168" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F168,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H168" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F168,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I168" s="7"/>
       <c r="J168" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F168,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9981,16 +10328,16 @@
       </c>
       <c r="F169" s="7"/>
       <c r="G169" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F169,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H169" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F169,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I169" s="7"/>
       <c r="J169" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F169,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10009,16 +10356,16 @@
       </c>
       <c r="F170" s="7"/>
       <c r="G170" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F170,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H170" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F170,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I170" s="7"/>
       <c r="J170" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F170,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10037,16 +10384,16 @@
       </c>
       <c r="F171" s="7"/>
       <c r="G171" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F171,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H171" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F171,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I171" s="7"/>
       <c r="J171" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F171,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10065,16 +10412,16 @@
       </c>
       <c r="F172" s="7"/>
       <c r="G172" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F172,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H172" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F172,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I172" s="7"/>
       <c r="J172" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F172,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10093,16 +10440,16 @@
       </c>
       <c r="F173" s="7"/>
       <c r="G173" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F173,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H173" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F173,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I173" s="7"/>
       <c r="J173" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F173,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10121,16 +10468,16 @@
       </c>
       <c r="F174" s="7"/>
       <c r="G174" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F174,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H174" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F174,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I174" s="7"/>
       <c r="J174" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F174,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10149,16 +10496,16 @@
       </c>
       <c r="F175" s="7"/>
       <c r="G175" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F175,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H175" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F175,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I175" s="7"/>
       <c r="J175" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F175,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10177,16 +10524,16 @@
       </c>
       <c r="F176" s="7"/>
       <c r="G176" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F176,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H176" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F176,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I176" s="7"/>
       <c r="J176" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F176,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10205,16 +10552,16 @@
       </c>
       <c r="F177" s="7"/>
       <c r="G177" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F177,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H177" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F177,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I177" s="7"/>
       <c r="J177" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F177,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10233,16 +10580,16 @@
       </c>
       <c r="F178" s="7"/>
       <c r="G178" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F178,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H178" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F178,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I178" s="7"/>
       <c r="J178" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F178,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10261,16 +10608,16 @@
       </c>
       <c r="F179" s="7"/>
       <c r="G179" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F179,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H179" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F179,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I179" s="7"/>
       <c r="J179" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F179,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10289,16 +10636,16 @@
       </c>
       <c r="F180" s="7"/>
       <c r="G180" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F180,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H180" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F180,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I180" s="7"/>
       <c r="J180" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F180,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10317,16 +10664,16 @@
       </c>
       <c r="F181" s="7"/>
       <c r="G181" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F181,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H181" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F181,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I181" s="7"/>
       <c r="J181" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F181,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10345,16 +10692,16 @@
       </c>
       <c r="F182" s="7"/>
       <c r="G182" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F182,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H182" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F182,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I182" s="7"/>
       <c r="J182" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F182,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10373,16 +10720,16 @@
       </c>
       <c r="F183" s="7"/>
       <c r="G183" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F183,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H183" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F183,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I183" s="7"/>
       <c r="J183" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F183,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10401,16 +10748,16 @@
       </c>
       <c r="F184" s="7"/>
       <c r="G184" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F184,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H184" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F184,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I184" s="7"/>
       <c r="J184" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F184,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10429,16 +10776,16 @@
       </c>
       <c r="F185" s="7"/>
       <c r="G185" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F185,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H185" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F185,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I185" s="7"/>
       <c r="J185" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F185,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10457,16 +10804,16 @@
       </c>
       <c r="F186" s="7"/>
       <c r="G186" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F186,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H186" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F186,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I186" s="7"/>
       <c r="J186" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F186,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10485,16 +10832,16 @@
       </c>
       <c r="F187" s="7"/>
       <c r="G187" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F187,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H187" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F187,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I187" s="7"/>
       <c r="J187" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F187,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10513,16 +10860,16 @@
       </c>
       <c r="F188" s="7"/>
       <c r="G188" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F188,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H188" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F188,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I188" s="7"/>
       <c r="J188" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F188,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10541,16 +10888,16 @@
       </c>
       <c r="F189" s="7"/>
       <c r="G189" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F189,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H189" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F189,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I189" s="7"/>
       <c r="J189" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F189,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10569,16 +10916,16 @@
       </c>
       <c r="F190" s="7"/>
       <c r="G190" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F190,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H190" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F190,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I190" s="7"/>
       <c r="J190" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F190,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10597,16 +10944,16 @@
       </c>
       <c r="F191" s="7"/>
       <c r="G191" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F191,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H191" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F191,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I191" s="7"/>
       <c r="J191" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F191,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10625,16 +10972,16 @@
       </c>
       <c r="F192" s="7"/>
       <c r="G192" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F192,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H192" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F192,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I192" s="7"/>
       <c r="J192" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F192,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10653,16 +11000,16 @@
       </c>
       <c r="F193" s="7"/>
       <c r="G193" s="7">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP($F193,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H193" s="7">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP($F193,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I193" s="7"/>
       <c r="J193" s="7">
-        <f t="shared" si="8"/>
+        <f>IFERROR(VLOOKUP($F193,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10681,16 +11028,16 @@
       </c>
       <c r="F194" s="7"/>
       <c r="G194" s="7">
-        <f t="shared" ref="G194:G257" si="9">IFERROR(VLOOKUP($F194,$A:$B,2,0),0)</f>
+        <f>IFERROR(VLOOKUP($F194,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H194" s="7">
-        <f t="shared" ref="H194:H257" si="10">IFERROR(VLOOKUP($F194,$A:$D,3,0),0)</f>
+        <f>IFERROR(VLOOKUP($F194,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I194" s="7"/>
       <c r="J194" s="7">
-        <f t="shared" ref="J194:J257" si="11">IFERROR(VLOOKUP($F194,$A:$D,4,0),0)</f>
+        <f>IFERROR(VLOOKUP($F194,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10709,16 +11056,16 @@
       </c>
       <c r="F195" s="7"/>
       <c r="G195" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F195,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H195" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F195,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I195" s="7"/>
       <c r="J195" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F195,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10737,16 +11084,16 @@
       </c>
       <c r="F196" s="7"/>
       <c r="G196" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F196,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H196" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F196,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I196" s="7"/>
       <c r="J196" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F196,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10765,16 +11112,16 @@
       </c>
       <c r="F197" s="7"/>
       <c r="G197" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F197,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H197" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F197,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I197" s="7"/>
       <c r="J197" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F197,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10793,16 +11140,16 @@
       </c>
       <c r="F198" s="7"/>
       <c r="G198" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F198,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H198" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F198,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I198" s="7"/>
       <c r="J198" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F198,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10821,16 +11168,16 @@
       </c>
       <c r="F199" s="7"/>
       <c r="G199" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F199,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H199" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F199,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I199" s="7"/>
       <c r="J199" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F199,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10849,16 +11196,16 @@
       </c>
       <c r="F200" s="7"/>
       <c r="G200" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F200,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H200" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F200,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I200" s="7"/>
       <c r="J200" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F200,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10877,16 +11224,16 @@
       </c>
       <c r="F201" s="7"/>
       <c r="G201" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F201,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H201" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F201,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I201" s="7"/>
       <c r="J201" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F201,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10905,16 +11252,16 @@
       </c>
       <c r="F202" s="7"/>
       <c r="G202" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F202,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H202" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F202,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I202" s="7"/>
       <c r="J202" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F202,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10933,16 +11280,16 @@
       </c>
       <c r="F203" s="7"/>
       <c r="G203" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F203,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H203" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F203,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I203" s="7"/>
       <c r="J203" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F203,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10961,16 +11308,16 @@
       </c>
       <c r="F204" s="7"/>
       <c r="G204" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F204,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H204" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F204,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I204" s="7"/>
       <c r="J204" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F204,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10989,16 +11336,16 @@
       </c>
       <c r="F205" s="7"/>
       <c r="G205" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F205,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H205" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F205,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I205" s="7"/>
       <c r="J205" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F205,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11017,16 +11364,16 @@
       </c>
       <c r="F206" s="7"/>
       <c r="G206" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F206,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H206" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F206,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I206" s="7"/>
       <c r="J206" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F206,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11045,16 +11392,16 @@
       </c>
       <c r="F207" s="7"/>
       <c r="G207" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F207,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H207" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F207,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I207" s="7"/>
       <c r="J207" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F207,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11073,16 +11420,16 @@
       </c>
       <c r="F208" s="7"/>
       <c r="G208" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F208,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H208" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F208,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I208" s="7"/>
       <c r="J208" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F208,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11101,16 +11448,16 @@
       </c>
       <c r="F209" s="7"/>
       <c r="G209" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F209,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H209" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F209,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I209" s="7"/>
       <c r="J209" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F209,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11129,16 +11476,16 @@
       </c>
       <c r="F210" s="7"/>
       <c r="G210" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F210,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H210" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F210,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I210" s="7"/>
       <c r="J210" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F210,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11157,16 +11504,16 @@
       </c>
       <c r="F211" s="7"/>
       <c r="G211" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F211,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H211" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F211,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I211" s="7"/>
       <c r="J211" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F211,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11185,16 +11532,16 @@
       </c>
       <c r="F212" s="7"/>
       <c r="G212" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F212,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H212" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F212,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I212" s="7"/>
       <c r="J212" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F212,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11213,16 +11560,16 @@
       </c>
       <c r="F213" s="7"/>
       <c r="G213" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F213,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H213" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F213,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I213" s="7"/>
       <c r="J213" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F213,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11241,16 +11588,16 @@
       </c>
       <c r="F214" s="7"/>
       <c r="G214" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F214,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H214" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F214,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I214" s="7"/>
       <c r="J214" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F214,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11269,16 +11616,16 @@
       </c>
       <c r="F215" s="7"/>
       <c r="G215" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F215,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H215" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F215,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I215" s="7"/>
       <c r="J215" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F215,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11297,16 +11644,16 @@
       </c>
       <c r="F216" s="7"/>
       <c r="G216" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F216,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H216" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F216,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I216" s="7"/>
       <c r="J216" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F216,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11325,16 +11672,16 @@
       </c>
       <c r="F217" s="7"/>
       <c r="G217" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F217,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H217" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F217,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I217" s="7"/>
       <c r="J217" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F217,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11353,16 +11700,16 @@
       </c>
       <c r="F218" s="7"/>
       <c r="G218" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F218,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H218" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F218,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I218" s="7"/>
       <c r="J218" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F218,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11381,16 +11728,16 @@
       </c>
       <c r="F219" s="7"/>
       <c r="G219" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F219,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H219" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F219,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I219" s="7"/>
       <c r="J219" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F219,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11409,16 +11756,16 @@
       </c>
       <c r="F220" s="7"/>
       <c r="G220" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F220,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H220" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F220,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I220" s="7"/>
       <c r="J220" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F220,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11437,16 +11784,16 @@
       </c>
       <c r="F221" s="7"/>
       <c r="G221" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F221,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H221" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F221,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I221" s="7"/>
       <c r="J221" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F221,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11465,16 +11812,16 @@
       </c>
       <c r="F222" s="7"/>
       <c r="G222" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F222,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H222" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F222,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I222" s="7"/>
       <c r="J222" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F222,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11493,16 +11840,16 @@
       </c>
       <c r="F223" s="7"/>
       <c r="G223" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F223,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H223" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F223,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I223" s="7"/>
       <c r="J223" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F223,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11521,16 +11868,16 @@
       </c>
       <c r="F224" s="7"/>
       <c r="G224" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F224,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H224" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F224,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I224" s="7"/>
       <c r="J224" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F224,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11549,16 +11896,16 @@
       </c>
       <c r="F225" s="7"/>
       <c r="G225" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F225,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H225" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F225,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I225" s="7"/>
       <c r="J225" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F225,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11577,16 +11924,16 @@
       </c>
       <c r="F226" s="7"/>
       <c r="G226" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F226,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H226" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F226,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I226" s="7"/>
       <c r="J226" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F226,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11605,16 +11952,16 @@
       </c>
       <c r="F227" s="7"/>
       <c r="G227" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F227,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H227" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F227,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I227" s="7"/>
       <c r="J227" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F227,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11633,16 +11980,16 @@
       </c>
       <c r="F228" s="7"/>
       <c r="G228" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F228,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H228" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F228,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I228" s="7"/>
       <c r="J228" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F228,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11661,16 +12008,16 @@
       </c>
       <c r="F229" s="7"/>
       <c r="G229" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F229,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H229" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F229,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I229" s="7"/>
       <c r="J229" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F229,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11689,16 +12036,16 @@
       </c>
       <c r="F230" s="7"/>
       <c r="G230" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F230,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H230" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F230,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I230" s="7"/>
       <c r="J230" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F230,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11717,16 +12064,16 @@
       </c>
       <c r="F231" s="7"/>
       <c r="G231" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F231,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H231" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F231,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I231" s="7"/>
       <c r="J231" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F231,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11745,16 +12092,16 @@
       </c>
       <c r="F232" s="7"/>
       <c r="G232" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F232,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H232" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F232,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I232" s="7"/>
       <c r="J232" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F232,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11773,16 +12120,16 @@
       </c>
       <c r="F233" s="7"/>
       <c r="G233" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F233,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H233" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F233,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I233" s="7"/>
       <c r="J233" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F233,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11801,16 +12148,16 @@
       </c>
       <c r="F234" s="7"/>
       <c r="G234" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F234,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H234" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F234,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I234" s="7"/>
       <c r="J234" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F234,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11829,16 +12176,16 @@
       </c>
       <c r="F235" s="7"/>
       <c r="G235" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F235,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H235" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F235,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I235" s="7"/>
       <c r="J235" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F235,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11857,16 +12204,16 @@
       </c>
       <c r="F236" s="7"/>
       <c r="G236" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F236,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H236" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F236,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I236" s="7"/>
       <c r="J236" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F236,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11885,16 +12232,16 @@
       </c>
       <c r="F237" s="7"/>
       <c r="G237" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F237,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H237" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F237,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I237" s="7"/>
       <c r="J237" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F237,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11913,16 +12260,16 @@
       </c>
       <c r="F238" s="7"/>
       <c r="G238" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F238,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H238" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F238,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I238" s="7"/>
       <c r="J238" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F238,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11941,16 +12288,16 @@
       </c>
       <c r="F239" s="7"/>
       <c r="G239" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F239,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H239" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F239,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I239" s="7"/>
       <c r="J239" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F239,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11969,16 +12316,16 @@
       </c>
       <c r="F240" s="7"/>
       <c r="G240" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F240,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H240" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F240,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I240" s="7"/>
       <c r="J240" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F240,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11997,16 +12344,16 @@
       </c>
       <c r="F241" s="7"/>
       <c r="G241" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F241,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H241" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F241,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I241" s="7"/>
       <c r="J241" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F241,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12025,16 +12372,16 @@
       </c>
       <c r="F242" s="7"/>
       <c r="G242" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F242,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H242" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F242,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I242" s="7"/>
       <c r="J242" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F242,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12053,16 +12400,16 @@
       </c>
       <c r="F243" s="7"/>
       <c r="G243" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F243,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H243" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F243,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I243" s="7"/>
       <c r="J243" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F243,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12081,16 +12428,16 @@
       </c>
       <c r="F244" s="7"/>
       <c r="G244" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F244,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H244" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F244,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I244" s="7"/>
       <c r="J244" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F244,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12109,16 +12456,16 @@
       </c>
       <c r="F245" s="7"/>
       <c r="G245" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F245,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H245" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F245,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I245" s="7"/>
       <c r="J245" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F245,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12137,16 +12484,16 @@
       </c>
       <c r="F246" s="7"/>
       <c r="G246" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F246,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H246" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F246,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I246" s="7"/>
       <c r="J246" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F246,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12165,16 +12512,16 @@
       </c>
       <c r="F247" s="7"/>
       <c r="G247" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F247,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H247" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F247,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I247" s="7"/>
       <c r="J247" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F247,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12193,16 +12540,16 @@
       </c>
       <c r="F248" s="7"/>
       <c r="G248" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F248,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H248" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F248,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I248" s="7"/>
       <c r="J248" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F248,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12221,16 +12568,16 @@
       </c>
       <c r="F249" s="7"/>
       <c r="G249" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F249,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H249" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F249,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I249" s="7"/>
       <c r="J249" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F249,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12249,16 +12596,16 @@
       </c>
       <c r="F250" s="7"/>
       <c r="G250" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F250,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H250" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F250,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I250" s="7"/>
       <c r="J250" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F250,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12277,16 +12624,16 @@
       </c>
       <c r="F251" s="7"/>
       <c r="G251" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F251,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H251" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F251,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I251" s="7"/>
       <c r="J251" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F251,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12305,16 +12652,16 @@
       </c>
       <c r="F252" s="7"/>
       <c r="G252" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F252,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H252" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F252,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I252" s="7"/>
       <c r="J252" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F252,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12333,16 +12680,16 @@
       </c>
       <c r="F253" s="7"/>
       <c r="G253" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F253,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H253" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F253,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I253" s="7"/>
       <c r="J253" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F253,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12361,16 +12708,16 @@
       </c>
       <c r="F254" s="7"/>
       <c r="G254" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F254,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H254" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F254,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I254" s="7"/>
       <c r="J254" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F254,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12389,16 +12736,16 @@
       </c>
       <c r="F255" s="7"/>
       <c r="G255" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F255,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H255" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F255,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I255" s="7"/>
       <c r="J255" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F255,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12417,16 +12764,16 @@
       </c>
       <c r="F256" s="7"/>
       <c r="G256" s="7">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F256,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H256" s="7">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F256,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I256" s="7"/>
       <c r="J256" s="7">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F256,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12445,16 +12792,16 @@
       </c>
       <c r="F257" s="40"/>
       <c r="G257" s="40">
-        <f t="shared" si="9"/>
+        <f>IFERROR(VLOOKUP($F257,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H257" s="40">
-        <f t="shared" si="10"/>
+        <f>IFERROR(VLOOKUP($F257,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I257" s="40"/>
       <c r="J257" s="40">
-        <f t="shared" si="11"/>
+        <f>IFERROR(VLOOKUP($F257,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12473,16 +12820,16 @@
       </c>
       <c r="F258" s="7"/>
       <c r="G258" s="7">
-        <f t="shared" ref="G258:G321" si="12">IFERROR(VLOOKUP($F258,$A:$B,2,0),0)</f>
+        <f>IFERROR(VLOOKUP($F258,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H258" s="7">
-        <f t="shared" ref="H258:H321" si="13">IFERROR(VLOOKUP($F258,$A:$D,3,0),0)</f>
+        <f>IFERROR(VLOOKUP($F258,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I258" s="7"/>
       <c r="J258" s="7">
-        <f t="shared" ref="J258:J321" si="14">IFERROR(VLOOKUP($F258,$A:$D,4,0),0)</f>
+        <f>IFERROR(VLOOKUP($F258,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12501,16 +12848,16 @@
       </c>
       <c r="F259" s="7"/>
       <c r="G259" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F259,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H259" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F259,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I259" s="7"/>
       <c r="J259" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F259,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12529,16 +12876,16 @@
       </c>
       <c r="F260" s="7"/>
       <c r="G260" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F260,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H260" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F260,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I260" s="7"/>
       <c r="J260" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F260,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12557,16 +12904,16 @@
       </c>
       <c r="F261" s="7"/>
       <c r="G261" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F261,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H261" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F261,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I261" s="7"/>
       <c r="J261" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F261,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12585,16 +12932,16 @@
       </c>
       <c r="F262" s="7"/>
       <c r="G262" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F262,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H262" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F262,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I262" s="7"/>
       <c r="J262" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F262,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12613,16 +12960,16 @@
       </c>
       <c r="F263" s="7"/>
       <c r="G263" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F263,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H263" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F263,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I263" s="7"/>
       <c r="J263" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F263,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12641,16 +12988,16 @@
       </c>
       <c r="F264" s="7"/>
       <c r="G264" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F264,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H264" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F264,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I264" s="7"/>
       <c r="J264" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F264,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12669,16 +13016,16 @@
       </c>
       <c r="F265" s="7"/>
       <c r="G265" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F265,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H265" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F265,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I265" s="7"/>
       <c r="J265" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F265,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12697,16 +13044,16 @@
       </c>
       <c r="F266" s="7"/>
       <c r="G266" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F266,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H266" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F266,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I266" s="7"/>
       <c r="J266" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F266,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12725,16 +13072,16 @@
       </c>
       <c r="F267" s="7"/>
       <c r="G267" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F267,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H267" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F267,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F267,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12753,16 +13100,16 @@
       </c>
       <c r="F268" s="7"/>
       <c r="G268" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F268,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H268" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F268,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I268" s="7"/>
       <c r="J268" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F268,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12781,16 +13128,16 @@
       </c>
       <c r="F269" s="7"/>
       <c r="G269" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F269,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H269" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F269,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I269" s="7"/>
       <c r="J269" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F269,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12809,16 +13156,16 @@
       </c>
       <c r="F270" s="7"/>
       <c r="G270" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F270,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H270" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F270,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I270" s="7"/>
       <c r="J270" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F270,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12837,16 +13184,16 @@
       </c>
       <c r="F271" s="7"/>
       <c r="G271" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F271,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H271" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F271,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I271" s="7"/>
       <c r="J271" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F271,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12865,16 +13212,16 @@
       </c>
       <c r="F272" s="7"/>
       <c r="G272" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F272,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H272" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F272,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I272" s="7"/>
       <c r="J272" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F272,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12893,16 +13240,16 @@
       </c>
       <c r="F273" s="7"/>
       <c r="G273" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F273,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H273" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F273,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I273" s="7"/>
       <c r="J273" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F273,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12921,16 +13268,16 @@
       </c>
       <c r="F274" s="7"/>
       <c r="G274" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F274,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H274" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F274,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I274" s="7"/>
       <c r="J274" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F274,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12949,16 +13296,16 @@
       </c>
       <c r="F275" s="7"/>
       <c r="G275" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F275,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H275" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F275,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I275" s="7"/>
       <c r="J275" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F275,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12977,16 +13324,16 @@
       </c>
       <c r="F276" s="7"/>
       <c r="G276" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F276,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H276" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F276,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I276" s="7"/>
       <c r="J276" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F276,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13005,16 +13352,16 @@
       </c>
       <c r="F277" s="7"/>
       <c r="G277" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F277,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H277" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F277,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I277" s="7"/>
       <c r="J277" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F277,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13033,16 +13380,16 @@
       </c>
       <c r="F278" s="7"/>
       <c r="G278" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F278,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H278" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F278,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I278" s="7"/>
       <c r="J278" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F278,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13061,16 +13408,16 @@
       </c>
       <c r="F279" s="7"/>
       <c r="G279" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F279,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H279" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F279,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I279" s="7"/>
       <c r="J279" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F279,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13089,16 +13436,16 @@
       </c>
       <c r="F280" s="7"/>
       <c r="G280" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F280,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H280" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F280,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I280" s="7"/>
       <c r="J280" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F280,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13117,16 +13464,16 @@
       </c>
       <c r="F281" s="7"/>
       <c r="G281" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F281,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H281" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F281,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I281" s="7"/>
       <c r="J281" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F281,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13145,16 +13492,16 @@
       </c>
       <c r="F282" s="7"/>
       <c r="G282" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F282,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H282" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F282,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I282" s="7"/>
       <c r="J282" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F282,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13173,16 +13520,16 @@
       </c>
       <c r="F283" s="7"/>
       <c r="G283" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F283,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H283" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F283,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I283" s="7"/>
       <c r="J283" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F283,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13201,16 +13548,16 @@
       </c>
       <c r="F284" s="7"/>
       <c r="G284" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F284,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H284" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F284,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I284" s="7"/>
       <c r="J284" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F284,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13229,16 +13576,16 @@
       </c>
       <c r="F285" s="7"/>
       <c r="G285" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F285,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H285" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F285,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I285" s="7"/>
       <c r="J285" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F285,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13257,16 +13604,16 @@
       </c>
       <c r="F286" s="7"/>
       <c r="G286" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F286,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H286" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F286,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I286" s="7"/>
       <c r="J286" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F286,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13285,16 +13632,16 @@
       </c>
       <c r="F287" s="7"/>
       <c r="G287" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F287,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H287" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F287,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I287" s="7"/>
       <c r="J287" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F287,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13313,16 +13660,16 @@
       </c>
       <c r="F288" s="7"/>
       <c r="G288" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F288,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H288" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F288,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I288" s="7"/>
       <c r="J288" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F288,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13341,16 +13688,16 @@
       </c>
       <c r="F289" s="7"/>
       <c r="G289" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F289,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H289" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F289,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I289" s="7"/>
       <c r="J289" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F289,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13369,16 +13716,16 @@
       </c>
       <c r="F290" s="7"/>
       <c r="G290" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F290,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H290" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F290,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I290" s="7"/>
       <c r="J290" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F290,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13397,16 +13744,16 @@
       </c>
       <c r="F291" s="7"/>
       <c r="G291" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F291,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H291" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F291,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I291" s="7"/>
       <c r="J291" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F291,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13425,16 +13772,16 @@
       </c>
       <c r="F292" s="7"/>
       <c r="G292" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F292,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H292" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F292,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I292" s="7"/>
       <c r="J292" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F292,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13453,16 +13800,16 @@
       </c>
       <c r="F293" s="7"/>
       <c r="G293" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F293,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H293" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F293,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I293" s="7"/>
       <c r="J293" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F293,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13481,16 +13828,16 @@
       </c>
       <c r="F294" s="7"/>
       <c r="G294" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F294,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H294" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F294,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I294" s="7"/>
       <c r="J294" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F294,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13509,16 +13856,16 @@
       </c>
       <c r="F295" s="7"/>
       <c r="G295" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F295,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H295" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F295,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I295" s="7"/>
       <c r="J295" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F295,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13537,16 +13884,16 @@
       </c>
       <c r="F296" s="7"/>
       <c r="G296" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F296,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H296" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F296,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I296" s="7"/>
       <c r="J296" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F296,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13565,16 +13912,16 @@
       </c>
       <c r="F297" s="7"/>
       <c r="G297" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F297,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H297" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F297,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I297" s="7"/>
       <c r="J297" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F297,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13593,16 +13940,16 @@
       </c>
       <c r="F298" s="7"/>
       <c r="G298" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F298,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H298" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F298,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I298" s="7"/>
       <c r="J298" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F298,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13621,16 +13968,16 @@
       </c>
       <c r="F299" s="7"/>
       <c r="G299" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F299,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H299" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F299,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I299" s="7"/>
       <c r="J299" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F299,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13649,16 +13996,16 @@
       </c>
       <c r="F300" s="7"/>
       <c r="G300" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F300,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H300" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F300,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I300" s="7"/>
       <c r="J300" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F300,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13677,16 +14024,16 @@
       </c>
       <c r="F301" s="7"/>
       <c r="G301" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F301,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H301" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F301,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I301" s="7"/>
       <c r="J301" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F301,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13705,16 +14052,16 @@
       </c>
       <c r="F302" s="7"/>
       <c r="G302" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F302,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H302" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F302,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I302" s="7"/>
       <c r="J302" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F302,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13733,16 +14080,16 @@
       </c>
       <c r="F303" s="7"/>
       <c r="G303" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F303,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H303" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F303,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I303" s="7"/>
       <c r="J303" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F303,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13761,16 +14108,16 @@
       </c>
       <c r="F304" s="7"/>
       <c r="G304" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F304,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H304" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F304,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I304" s="7"/>
       <c r="J304" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F304,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13789,16 +14136,16 @@
       </c>
       <c r="F305" s="7"/>
       <c r="G305" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F305,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H305" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F305,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I305" s="7"/>
       <c r="J305" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F305,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13817,16 +14164,16 @@
       </c>
       <c r="F306" s="7"/>
       <c r="G306" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F306,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H306" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F306,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I306" s="7"/>
       <c r="J306" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F306,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13845,16 +14192,16 @@
       </c>
       <c r="F307" s="7"/>
       <c r="G307" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F307,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H307" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F307,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I307" s="7"/>
       <c r="J307" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F307,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13873,16 +14220,16 @@
       </c>
       <c r="F308" s="7"/>
       <c r="G308" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F308,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H308" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F308,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I308" s="7"/>
       <c r="J308" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F308,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13901,16 +14248,16 @@
       </c>
       <c r="F309" s="7"/>
       <c r="G309" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F309,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H309" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F309,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I309" s="7"/>
       <c r="J309" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F309,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13929,16 +14276,16 @@
       </c>
       <c r="F310" s="7"/>
       <c r="G310" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F310,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H310" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F310,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I310" s="7"/>
       <c r="J310" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F310,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13957,16 +14304,16 @@
       </c>
       <c r="F311" s="7"/>
       <c r="G311" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F311,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H311" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F311,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I311" s="7"/>
       <c r="J311" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F311,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -13985,16 +14332,16 @@
       </c>
       <c r="F312" s="7"/>
       <c r="G312" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F312,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H312" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F312,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I312" s="7"/>
       <c r="J312" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F312,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14013,16 +14360,16 @@
       </c>
       <c r="F313" s="7"/>
       <c r="G313" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F313,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H313" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F313,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I313" s="7"/>
       <c r="J313" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F313,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14041,16 +14388,16 @@
       </c>
       <c r="F314" s="7"/>
       <c r="G314" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F314,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H314" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F314,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I314" s="7"/>
       <c r="J314" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F314,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14069,16 +14416,16 @@
       </c>
       <c r="F315" s="7"/>
       <c r="G315" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F315,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H315" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F315,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I315" s="7"/>
       <c r="J315" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F315,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14097,16 +14444,16 @@
       </c>
       <c r="F316" s="7"/>
       <c r="G316" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F316,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H316" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F316,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I316" s="7"/>
       <c r="J316" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F316,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14125,16 +14472,16 @@
       </c>
       <c r="F317" s="7"/>
       <c r="G317" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F317,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H317" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F317,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I317" s="7"/>
       <c r="J317" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F317,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14153,16 +14500,16 @@
       </c>
       <c r="F318" s="7"/>
       <c r="G318" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F318,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H318" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F318,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I318" s="7"/>
       <c r="J318" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F318,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14181,16 +14528,16 @@
       </c>
       <c r="F319" s="7"/>
       <c r="G319" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F319,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H319" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F319,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I319" s="7"/>
       <c r="J319" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F319,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14209,16 +14556,16 @@
       </c>
       <c r="F320" s="7"/>
       <c r="G320" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F320,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H320" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F320,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I320" s="7"/>
       <c r="J320" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F320,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14237,16 +14584,16 @@
       </c>
       <c r="F321" s="7"/>
       <c r="G321" s="7">
-        <f t="shared" si="12"/>
+        <f>IFERROR(VLOOKUP($F321,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H321" s="7">
-        <f t="shared" si="13"/>
+        <f>IFERROR(VLOOKUP($F321,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I321" s="7"/>
       <c r="J321" s="7">
-        <f t="shared" si="14"/>
+        <f>IFERROR(VLOOKUP($F321,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14265,16 +14612,16 @@
       </c>
       <c r="F322" s="7"/>
       <c r="G322" s="7">
-        <f t="shared" ref="G322:G385" si="15">IFERROR(VLOOKUP($F322,$A:$B,2,0),0)</f>
+        <f>IFERROR(VLOOKUP($F322,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H322" s="7">
-        <f t="shared" ref="H322:H385" si="16">IFERROR(VLOOKUP($F322,$A:$D,3,0),0)</f>
+        <f>IFERROR(VLOOKUP($F322,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I322" s="7"/>
       <c r="J322" s="7">
-        <f t="shared" ref="J322:J385" si="17">IFERROR(VLOOKUP($F322,$A:$D,4,0),0)</f>
+        <f>IFERROR(VLOOKUP($F322,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14293,16 +14640,16 @@
       </c>
       <c r="F323" s="7"/>
       <c r="G323" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F323,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H323" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F323,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I323" s="7"/>
       <c r="J323" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F323,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14321,16 +14668,16 @@
       </c>
       <c r="F324" s="7"/>
       <c r="G324" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F324,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H324" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F324,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I324" s="7"/>
       <c r="J324" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F324,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14349,16 +14696,16 @@
       </c>
       <c r="F325" s="7"/>
       <c r="G325" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F325,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H325" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F325,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I325" s="7"/>
       <c r="J325" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F325,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14377,16 +14724,16 @@
       </c>
       <c r="F326" s="7"/>
       <c r="G326" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F326,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H326" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F326,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I326" s="7"/>
       <c r="J326" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F326,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14405,16 +14752,16 @@
       </c>
       <c r="F327" s="7"/>
       <c r="G327" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F327,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H327" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F327,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I327" s="7"/>
       <c r="J327" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F327,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14433,16 +14780,16 @@
       </c>
       <c r="F328" s="7"/>
       <c r="G328" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F328,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H328" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F328,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I328" s="7"/>
       <c r="J328" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F328,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14461,16 +14808,16 @@
       </c>
       <c r="F329" s="7"/>
       <c r="G329" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F329,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H329" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F329,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I329" s="7"/>
       <c r="J329" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F329,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14489,16 +14836,16 @@
       </c>
       <c r="F330" s="7"/>
       <c r="G330" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F330,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H330" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F330,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I330" s="7"/>
       <c r="J330" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F330,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14517,16 +14864,16 @@
       </c>
       <c r="F331" s="7"/>
       <c r="G331" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F331,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H331" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F331,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I331" s="7"/>
       <c r="J331" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F331,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14545,16 +14892,16 @@
       </c>
       <c r="F332" s="7"/>
       <c r="G332" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F332,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H332" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F332,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I332" s="7"/>
       <c r="J332" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F332,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14573,16 +14920,16 @@
       </c>
       <c r="F333" s="7"/>
       <c r="G333" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F333,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H333" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F333,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I333" s="7"/>
       <c r="J333" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F333,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14601,16 +14948,16 @@
       </c>
       <c r="F334" s="7"/>
       <c r="G334" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F334,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H334" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F334,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I334" s="7"/>
       <c r="J334" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F334,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14629,16 +14976,16 @@
       </c>
       <c r="F335" s="7"/>
       <c r="G335" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F335,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H335" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F335,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I335" s="7"/>
       <c r="J335" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F335,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14657,16 +15004,16 @@
       </c>
       <c r="F336" s="7"/>
       <c r="G336" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F336,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H336" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F336,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I336" s="7"/>
       <c r="J336" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F336,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14685,16 +15032,16 @@
       </c>
       <c r="F337" s="7"/>
       <c r="G337" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F337,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H337" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F337,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I337" s="7"/>
       <c r="J337" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F337,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14713,16 +15060,16 @@
       </c>
       <c r="F338" s="7"/>
       <c r="G338" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F338,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H338" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F338,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I338" s="7"/>
       <c r="J338" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F338,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14741,16 +15088,16 @@
       </c>
       <c r="F339" s="7"/>
       <c r="G339" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F339,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H339" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F339,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I339" s="7"/>
       <c r="J339" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F339,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14769,16 +15116,16 @@
       </c>
       <c r="F340" s="7"/>
       <c r="G340" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F340,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H340" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F340,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I340" s="7"/>
       <c r="J340" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F340,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14797,16 +15144,16 @@
       </c>
       <c r="F341" s="7"/>
       <c r="G341" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F341,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H341" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F341,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I341" s="7"/>
       <c r="J341" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F341,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14825,16 +15172,16 @@
       </c>
       <c r="F342" s="7"/>
       <c r="G342" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F342,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H342" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F342,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I342" s="7"/>
       <c r="J342" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F342,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14853,16 +15200,16 @@
       </c>
       <c r="F343" s="7"/>
       <c r="G343" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F343,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H343" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F343,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I343" s="7"/>
       <c r="J343" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F343,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14881,16 +15228,16 @@
       </c>
       <c r="F344" s="7"/>
       <c r="G344" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F344,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H344" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F344,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I344" s="7"/>
       <c r="J344" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F344,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14909,16 +15256,16 @@
       </c>
       <c r="F345" s="7"/>
       <c r="G345" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F345,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H345" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F345,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I345" s="7"/>
       <c r="J345" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F345,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14937,16 +15284,16 @@
       </c>
       <c r="F346" s="7"/>
       <c r="G346" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F346,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H346" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F346,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I346" s="7"/>
       <c r="J346" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F346,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14965,16 +15312,16 @@
       </c>
       <c r="F347" s="7"/>
       <c r="G347" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F347,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H347" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F347,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I347" s="7"/>
       <c r="J347" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F347,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14993,16 +15340,16 @@
       </c>
       <c r="F348" s="7"/>
       <c r="G348" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F348,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H348" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F348,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I348" s="7"/>
       <c r="J348" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F348,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15021,16 +15368,16 @@
       </c>
       <c r="F349" s="7"/>
       <c r="G349" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F349,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H349" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F349,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I349" s="7"/>
       <c r="J349" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F349,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15049,16 +15396,16 @@
       </c>
       <c r="F350" s="7"/>
       <c r="G350" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F350,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H350" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F350,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I350" s="7"/>
       <c r="J350" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F350,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15077,16 +15424,16 @@
       </c>
       <c r="F351" s="7"/>
       <c r="G351" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F351,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H351" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F351,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I351" s="7"/>
       <c r="J351" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F351,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15105,16 +15452,16 @@
       </c>
       <c r="F352" s="7"/>
       <c r="G352" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F352,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H352" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F352,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I352" s="7"/>
       <c r="J352" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F352,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15133,16 +15480,16 @@
       </c>
       <c r="F353" s="7"/>
       <c r="G353" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F353,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H353" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F353,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I353" s="7"/>
       <c r="J353" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F353,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15161,16 +15508,16 @@
       </c>
       <c r="F354" s="7"/>
       <c r="G354" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F354,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H354" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F354,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I354" s="7"/>
       <c r="J354" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F354,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15189,16 +15536,16 @@
       </c>
       <c r="F355" s="7"/>
       <c r="G355" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F355,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H355" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F355,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I355" s="7"/>
       <c r="J355" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F355,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15217,16 +15564,16 @@
       </c>
       <c r="F356" s="7"/>
       <c r="G356" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F356,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H356" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F356,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I356" s="7"/>
       <c r="J356" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F356,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15245,16 +15592,16 @@
       </c>
       <c r="F357" s="7"/>
       <c r="G357" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F357,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H357" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F357,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I357" s="7"/>
       <c r="J357" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F357,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15273,16 +15620,16 @@
       </c>
       <c r="F358" s="7"/>
       <c r="G358" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F358,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H358" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F358,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I358" s="7"/>
       <c r="J358" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F358,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15301,16 +15648,16 @@
       </c>
       <c r="F359" s="7"/>
       <c r="G359" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F359,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H359" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F359,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I359" s="7"/>
       <c r="J359" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F359,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15329,16 +15676,16 @@
       </c>
       <c r="F360" s="7"/>
       <c r="G360" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F360,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H360" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F360,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I360" s="7"/>
       <c r="J360" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F360,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15357,16 +15704,16 @@
       </c>
       <c r="F361" s="7"/>
       <c r="G361" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F361,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H361" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F361,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I361" s="7"/>
       <c r="J361" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F361,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15385,16 +15732,16 @@
       </c>
       <c r="F362" s="7"/>
       <c r="G362" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F362,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H362" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F362,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I362" s="7"/>
       <c r="J362" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F362,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15413,16 +15760,16 @@
       </c>
       <c r="F363" s="7"/>
       <c r="G363" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F363,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H363" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F363,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I363" s="7"/>
       <c r="J363" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F363,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15441,16 +15788,16 @@
       </c>
       <c r="F364" s="7"/>
       <c r="G364" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F364,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H364" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F364,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I364" s="7"/>
       <c r="J364" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F364,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15469,16 +15816,16 @@
       </c>
       <c r="F365" s="7"/>
       <c r="G365" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F365,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H365" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F365,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I365" s="7"/>
       <c r="J365" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F365,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15497,16 +15844,16 @@
       </c>
       <c r="F366" s="7"/>
       <c r="G366" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F366,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H366" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F366,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I366" s="7"/>
       <c r="J366" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F366,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15525,16 +15872,16 @@
       </c>
       <c r="F367" s="40"/>
       <c r="G367" s="40">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F367,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H367" s="40">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F367,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I367" s="40"/>
       <c r="J367" s="40">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F367,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15553,16 +15900,16 @@
       </c>
       <c r="F368" s="7"/>
       <c r="G368" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F368,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H368" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F368,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I368" s="7"/>
       <c r="J368" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F368,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15581,16 +15928,16 @@
       </c>
       <c r="F369" s="7"/>
       <c r="G369" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F369,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H369" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F369,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I369" s="7"/>
       <c r="J369" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F369,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15609,16 +15956,16 @@
       </c>
       <c r="F370" s="7"/>
       <c r="G370" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F370,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H370" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F370,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I370" s="7"/>
       <c r="J370" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F370,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15637,16 +15984,16 @@
       </c>
       <c r="F371" s="7"/>
       <c r="G371" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F371,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H371" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F371,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I371" s="7"/>
       <c r="J371" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F371,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15665,16 +16012,16 @@
       </c>
       <c r="F372" s="7"/>
       <c r="G372" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F372,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H372" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F372,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I372" s="7"/>
       <c r="J372" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F372,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15693,16 +16040,16 @@
       </c>
       <c r="F373" s="7"/>
       <c r="G373" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F373,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H373" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F373,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I373" s="7"/>
       <c r="J373" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F373,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15721,16 +16068,16 @@
       </c>
       <c r="F374" s="7"/>
       <c r="G374" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F374,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H374" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F374,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I374" s="7"/>
       <c r="J374" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F374,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15749,16 +16096,16 @@
       </c>
       <c r="F375" s="7"/>
       <c r="G375" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F375,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H375" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F375,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I375" s="7"/>
       <c r="J375" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F375,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15777,16 +16124,16 @@
       </c>
       <c r="F376" s="7"/>
       <c r="G376" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F376,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H376" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F376,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I376" s="7"/>
       <c r="J376" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F376,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15805,16 +16152,16 @@
       </c>
       <c r="F377" s="7"/>
       <c r="G377" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F377,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H377" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F377,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I377" s="7"/>
       <c r="J377" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F377,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15833,16 +16180,16 @@
       </c>
       <c r="F378" s="7"/>
       <c r="G378" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F378,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H378" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F378,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I378" s="7"/>
       <c r="J378" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F378,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15861,16 +16208,16 @@
       </c>
       <c r="F379" s="7"/>
       <c r="G379" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F379,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H379" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F379,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I379" s="7"/>
       <c r="J379" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F379,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15889,16 +16236,16 @@
       </c>
       <c r="F380" s="7"/>
       <c r="G380" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F380,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H380" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F380,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I380" s="7"/>
       <c r="J380" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F380,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15917,16 +16264,16 @@
       </c>
       <c r="F381" s="7"/>
       <c r="G381" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F381,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H381" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F381,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I381" s="7"/>
       <c r="J381" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F381,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15945,16 +16292,16 @@
       </c>
       <c r="F382" s="7"/>
       <c r="G382" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F382,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H382" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F382,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I382" s="7"/>
       <c r="J382" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F382,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15973,16 +16320,16 @@
       </c>
       <c r="F383" s="7"/>
       <c r="G383" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F383,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H383" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F383,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I383" s="7"/>
       <c r="J383" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F383,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16001,16 +16348,16 @@
       </c>
       <c r="F384" s="7"/>
       <c r="G384" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F384,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H384" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F384,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I384" s="7"/>
       <c r="J384" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F384,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16029,16 +16376,16 @@
       </c>
       <c r="F385" s="7"/>
       <c r="G385" s="7">
-        <f t="shared" si="15"/>
+        <f>IFERROR(VLOOKUP($F385,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H385" s="7">
-        <f t="shared" si="16"/>
+        <f>IFERROR(VLOOKUP($F385,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I385" s="7"/>
       <c r="J385" s="7">
-        <f t="shared" si="17"/>
+        <f>IFERROR(VLOOKUP($F385,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16057,16 +16404,16 @@
       </c>
       <c r="F386" s="7"/>
       <c r="G386" s="7">
-        <f t="shared" ref="G386:G449" si="18">IFERROR(VLOOKUP($F386,$A:$B,2,0),0)</f>
+        <f>IFERROR(VLOOKUP($F386,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H386" s="7">
-        <f t="shared" ref="H386:H449" si="19">IFERROR(VLOOKUP($F386,$A:$D,3,0),0)</f>
+        <f>IFERROR(VLOOKUP($F386,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I386" s="7"/>
       <c r="J386" s="7">
-        <f t="shared" ref="J386:J449" si="20">IFERROR(VLOOKUP($F386,$A:$D,4,0),0)</f>
+        <f>IFERROR(VLOOKUP($F386,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16085,16 +16432,16 @@
       </c>
       <c r="F387" s="7"/>
       <c r="G387" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F387,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H387" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F387,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I387" s="7"/>
       <c r="J387" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F387,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16113,16 +16460,16 @@
       </c>
       <c r="F388" s="7"/>
       <c r="G388" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F388,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H388" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F388,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I388" s="7"/>
       <c r="J388" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F388,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16141,16 +16488,16 @@
       </c>
       <c r="F389" s="7"/>
       <c r="G389" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F389,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H389" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F389,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I389" s="7"/>
       <c r="J389" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F389,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16169,16 +16516,16 @@
       </c>
       <c r="F390" s="7"/>
       <c r="G390" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F390,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H390" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F390,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I390" s="7"/>
       <c r="J390" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F390,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16197,16 +16544,16 @@
       </c>
       <c r="F391" s="7"/>
       <c r="G391" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F391,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H391" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F391,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I391" s="7"/>
       <c r="J391" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F391,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16225,16 +16572,16 @@
       </c>
       <c r="F392" s="7"/>
       <c r="G392" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F392,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H392" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F392,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I392" s="7"/>
       <c r="J392" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F392,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16253,16 +16600,16 @@
       </c>
       <c r="F393" s="7"/>
       <c r="G393" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F393,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H393" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F393,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I393" s="7"/>
       <c r="J393" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F393,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16281,16 +16628,16 @@
       </c>
       <c r="F394" s="7"/>
       <c r="G394" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F394,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H394" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F394,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I394" s="7"/>
       <c r="J394" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F394,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16309,16 +16656,16 @@
       </c>
       <c r="F395" s="7"/>
       <c r="G395" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F395,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H395" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F395,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I395" s="7"/>
       <c r="J395" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F395,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16337,16 +16684,16 @@
       </c>
       <c r="F396" s="7"/>
       <c r="G396" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F396,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H396" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F396,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I396" s="7"/>
       <c r="J396" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F396,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16365,16 +16712,16 @@
       </c>
       <c r="F397" s="7"/>
       <c r="G397" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F397,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H397" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F397,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I397" s="7"/>
       <c r="J397" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F397,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16393,16 +16740,16 @@
       </c>
       <c r="F398" s="7"/>
       <c r="G398" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F398,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H398" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F398,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I398" s="7"/>
       <c r="J398" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F398,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16421,16 +16768,16 @@
       </c>
       <c r="F399" s="7"/>
       <c r="G399" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F399,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H399" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F399,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I399" s="7"/>
       <c r="J399" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F399,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16449,16 +16796,16 @@
       </c>
       <c r="F400" s="7"/>
       <c r="G400" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F400,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H400" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F400,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I400" s="7"/>
       <c r="J400" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F400,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16477,16 +16824,16 @@
       </c>
       <c r="F401" s="7"/>
       <c r="G401" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F401,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H401" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F401,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I401" s="7"/>
       <c r="J401" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F401,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16505,16 +16852,16 @@
       </c>
       <c r="F402" s="7"/>
       <c r="G402" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F402,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H402" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F402,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I402" s="7"/>
       <c r="J402" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F402,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16533,16 +16880,16 @@
       </c>
       <c r="F403" s="7"/>
       <c r="G403" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F403,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H403" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F403,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I403" s="7"/>
       <c r="J403" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F403,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16561,16 +16908,16 @@
       </c>
       <c r="F404" s="7"/>
       <c r="G404" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F404,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H404" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F404,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I404" s="7"/>
       <c r="J404" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F404,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16589,16 +16936,16 @@
       </c>
       <c r="F405" s="7"/>
       <c r="G405" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F405,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H405" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F405,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I405" s="7"/>
       <c r="J405" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F405,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16617,16 +16964,16 @@
       </c>
       <c r="F406" s="7"/>
       <c r="G406" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F406,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H406" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F406,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I406" s="7"/>
       <c r="J406" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F406,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16645,16 +16992,16 @@
       </c>
       <c r="F407" s="7"/>
       <c r="G407" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F407,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H407" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F407,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I407" s="7"/>
       <c r="J407" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F407,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16673,16 +17020,16 @@
       </c>
       <c r="F408" s="7"/>
       <c r="G408" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F408,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H408" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F408,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I408" s="7"/>
       <c r="J408" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F408,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16701,16 +17048,16 @@
       </c>
       <c r="F409" s="7"/>
       <c r="G409" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F409,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H409" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F409,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I409" s="7"/>
       <c r="J409" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F409,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16729,16 +17076,16 @@
       </c>
       <c r="F410" s="7"/>
       <c r="G410" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F410,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H410" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F410,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I410" s="7"/>
       <c r="J410" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F410,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16757,16 +17104,16 @@
       </c>
       <c r="F411" s="7"/>
       <c r="G411" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F411,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H411" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F411,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I411" s="7"/>
       <c r="J411" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F411,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16785,16 +17132,16 @@
       </c>
       <c r="F412" s="7"/>
       <c r="G412" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F412,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H412" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F412,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I412" s="7"/>
       <c r="J412" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F412,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16813,16 +17160,16 @@
       </c>
       <c r="F413" s="7"/>
       <c r="G413" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F413,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H413" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F413,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I413" s="7"/>
       <c r="J413" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F413,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16841,16 +17188,16 @@
       </c>
       <c r="F414" s="7"/>
       <c r="G414" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F414,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H414" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F414,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I414" s="7"/>
       <c r="J414" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F414,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16869,16 +17216,16 @@
       </c>
       <c r="F415" s="7"/>
       <c r="G415" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F415,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H415" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F415,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I415" s="7"/>
       <c r="J415" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F415,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16897,16 +17244,16 @@
       </c>
       <c r="F416" s="7"/>
       <c r="G416" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F416,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H416" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F416,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I416" s="7"/>
       <c r="J416" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F416,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16925,16 +17272,16 @@
       </c>
       <c r="F417" s="7"/>
       <c r="G417" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F417,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H417" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F417,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I417" s="7"/>
       <c r="J417" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F417,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16953,16 +17300,16 @@
       </c>
       <c r="F418" s="7"/>
       <c r="G418" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F418,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H418" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F418,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I418" s="7"/>
       <c r="J418" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F418,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16981,16 +17328,16 @@
       </c>
       <c r="F419" s="7"/>
       <c r="G419" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F419,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H419" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F419,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I419" s="7"/>
       <c r="J419" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F419,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17009,16 +17356,16 @@
       </c>
       <c r="F420" s="7"/>
       <c r="G420" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F420,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H420" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F420,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I420" s="7"/>
       <c r="J420" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F420,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17037,16 +17384,16 @@
       </c>
       <c r="F421" s="7"/>
       <c r="G421" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F421,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H421" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F421,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I421" s="7"/>
       <c r="J421" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F421,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17065,16 +17412,16 @@
       </c>
       <c r="F422" s="7"/>
       <c r="G422" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F422,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H422" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F422,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I422" s="7"/>
       <c r="J422" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F422,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17093,16 +17440,16 @@
       </c>
       <c r="F423" s="7"/>
       <c r="G423" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F423,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H423" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F423,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I423" s="7"/>
       <c r="J423" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F423,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17121,16 +17468,16 @@
       </c>
       <c r="F424" s="7"/>
       <c r="G424" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F424,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H424" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F424,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I424" s="7"/>
       <c r="J424" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F424,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17149,16 +17496,16 @@
       </c>
       <c r="F425" s="7"/>
       <c r="G425" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F425,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H425" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F425,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I425" s="7"/>
       <c r="J425" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F425,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17177,16 +17524,16 @@
       </c>
       <c r="F426" s="7"/>
       <c r="G426" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F426,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H426" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F426,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I426" s="7"/>
       <c r="J426" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F426,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17205,16 +17552,16 @@
       </c>
       <c r="F427" s="7"/>
       <c r="G427" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F427,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H427" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F427,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I427" s="7"/>
       <c r="J427" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F427,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17233,16 +17580,16 @@
       </c>
       <c r="F428" s="7"/>
       <c r="G428" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F428,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H428" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F428,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I428" s="7"/>
       <c r="J428" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F428,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17261,16 +17608,16 @@
       </c>
       <c r="F429" s="7"/>
       <c r="G429" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F429,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H429" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F429,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I429" s="7"/>
       <c r="J429" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F429,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17289,16 +17636,16 @@
       </c>
       <c r="F430" s="7"/>
       <c r="G430" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F430,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H430" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F430,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I430" s="7"/>
       <c r="J430" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F430,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17317,16 +17664,16 @@
       </c>
       <c r="F431" s="7"/>
       <c r="G431" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F431,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H431" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F431,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I431" s="7"/>
       <c r="J431" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F431,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17345,16 +17692,16 @@
       </c>
       <c r="F432" s="7"/>
       <c r="G432" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F432,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H432" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F432,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I432" s="7"/>
       <c r="J432" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F432,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17373,16 +17720,16 @@
       </c>
       <c r="F433" s="7"/>
       <c r="G433" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F433,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H433" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F433,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I433" s="7"/>
       <c r="J433" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F433,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17401,16 +17748,16 @@
       </c>
       <c r="F434" s="7"/>
       <c r="G434" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F434,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H434" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F434,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I434" s="7"/>
       <c r="J434" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F434,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17429,16 +17776,16 @@
       </c>
       <c r="F435" s="7"/>
       <c r="G435" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F435,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H435" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F435,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I435" s="7"/>
       <c r="J435" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F435,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17457,16 +17804,16 @@
       </c>
       <c r="F436" s="7"/>
       <c r="G436" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F436,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H436" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F436,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I436" s="7"/>
       <c r="J436" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F436,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17485,16 +17832,16 @@
       </c>
       <c r="F437" s="7"/>
       <c r="G437" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F437,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H437" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F437,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I437" s="7"/>
       <c r="J437" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F437,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17513,16 +17860,16 @@
       </c>
       <c r="F438" s="7"/>
       <c r="G438" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F438,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H438" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F438,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I438" s="7"/>
       <c r="J438" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F438,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17541,16 +17888,16 @@
       </c>
       <c r="F439" s="7"/>
       <c r="G439" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F439,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H439" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F439,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I439" s="7"/>
       <c r="J439" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F439,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17569,16 +17916,16 @@
       </c>
       <c r="F440" s="7"/>
       <c r="G440" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F440,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H440" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F440,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I440" s="7"/>
       <c r="J440" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F440,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17597,16 +17944,16 @@
       </c>
       <c r="F441" s="7"/>
       <c r="G441" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F441,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H441" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F441,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I441" s="7"/>
       <c r="J441" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F441,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17625,16 +17972,16 @@
       </c>
       <c r="F442" s="7"/>
       <c r="G442" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F442,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H442" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F442,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I442" s="7"/>
       <c r="J442" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F442,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17653,16 +18000,16 @@
       </c>
       <c r="F443" s="7"/>
       <c r="G443" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F443,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H443" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F443,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I443" s="7"/>
       <c r="J443" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F443,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17681,16 +18028,16 @@
       </c>
       <c r="F444" s="7"/>
       <c r="G444" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F444,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H444" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F444,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I444" s="7"/>
       <c r="J444" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F444,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17709,16 +18056,16 @@
       </c>
       <c r="F445" s="7"/>
       <c r="G445" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F445,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H445" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F445,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I445" s="7"/>
       <c r="J445" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F445,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17737,16 +18084,16 @@
       </c>
       <c r="F446" s="7"/>
       <c r="G446" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F446,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H446" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F446,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I446" s="7"/>
       <c r="J446" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F446,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17765,16 +18112,16 @@
       </c>
       <c r="F447" s="7"/>
       <c r="G447" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F447,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H447" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F447,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I447" s="7"/>
       <c r="J447" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F447,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17793,16 +18140,16 @@
       </c>
       <c r="F448" s="7"/>
       <c r="G448" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F448,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H448" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F448,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I448" s="7"/>
       <c r="J448" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F448,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17821,16 +18168,16 @@
       </c>
       <c r="F449" s="7"/>
       <c r="G449" s="7">
-        <f t="shared" si="18"/>
+        <f>IFERROR(VLOOKUP($F449,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H449" s="7">
-        <f t="shared" si="19"/>
+        <f>IFERROR(VLOOKUP($F449,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I449" s="7"/>
       <c r="J449" s="7">
-        <f t="shared" si="20"/>
+        <f>IFERROR(VLOOKUP($F449,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17849,16 +18196,16 @@
       </c>
       <c r="F450" s="7"/>
       <c r="G450" s="7">
-        <f t="shared" ref="G450:G467" si="21">IFERROR(VLOOKUP($F450,$A:$B,2,0),0)</f>
+        <f>IFERROR(VLOOKUP($F450,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H450" s="7">
-        <f t="shared" ref="H450:H467" si="22">IFERROR(VLOOKUP($F450,$A:$D,3,0),0)</f>
+        <f>IFERROR(VLOOKUP($F450,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I450" s="7"/>
       <c r="J450" s="7">
-        <f t="shared" ref="J450:J467" si="23">IFERROR(VLOOKUP($F450,$A:$D,4,0),0)</f>
+        <f>IFERROR(VLOOKUP($F450,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17877,16 +18224,16 @@
       </c>
       <c r="F451" s="7"/>
       <c r="G451" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F451,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H451" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F451,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I451" s="7"/>
       <c r="J451" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F451,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17905,16 +18252,16 @@
       </c>
       <c r="F452" s="7"/>
       <c r="G452" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F452,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H452" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F452,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I452" s="7"/>
       <c r="J452" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F452,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17933,16 +18280,16 @@
       </c>
       <c r="F453" s="7"/>
       <c r="G453" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F453,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H453" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F453,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I453" s="7"/>
       <c r="J453" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F453,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17961,16 +18308,16 @@
       </c>
       <c r="F454" s="7"/>
       <c r="G454" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F454,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H454" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F454,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I454" s="7"/>
       <c r="J454" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F454,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17989,16 +18336,16 @@
       </c>
       <c r="F455" s="7"/>
       <c r="G455" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F455,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H455" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F455,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I455" s="7"/>
       <c r="J455" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F455,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18017,16 +18364,16 @@
       </c>
       <c r="F456" s="7"/>
       <c r="G456" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F456,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H456" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F456,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I456" s="7"/>
       <c r="J456" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F456,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18045,16 +18392,16 @@
       </c>
       <c r="F457" s="7"/>
       <c r="G457" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F457,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H457" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F457,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I457" s="7"/>
       <c r="J457" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F457,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18073,16 +18420,16 @@
       </c>
       <c r="F458" s="7"/>
       <c r="G458" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F458,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H458" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F458,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I458" s="7"/>
       <c r="J458" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F458,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18101,16 +18448,16 @@
       </c>
       <c r="F459" s="7"/>
       <c r="G459" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F459,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H459" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F459,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I459" s="7"/>
       <c r="J459" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F459,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18129,16 +18476,16 @@
       </c>
       <c r="F460" s="7"/>
       <c r="G460" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F460,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H460" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F460,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I460" s="7"/>
       <c r="J460" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F460,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18157,16 +18504,16 @@
       </c>
       <c r="F461" s="7"/>
       <c r="G461" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F461,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H461" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F461,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I461" s="7"/>
       <c r="J461" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F461,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18185,16 +18532,16 @@
       </c>
       <c r="F462" s="7"/>
       <c r="G462" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F462,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H462" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F462,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I462" s="7"/>
       <c r="J462" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F462,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18213,16 +18560,16 @@
       </c>
       <c r="F463" s="7"/>
       <c r="G463" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F463,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H463" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F463,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I463" s="7"/>
       <c r="J463" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F463,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18241,16 +18588,16 @@
       </c>
       <c r="F464" s="7"/>
       <c r="G464" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F464,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H464" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F464,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I464" s="7"/>
       <c r="J464" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F464,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18269,16 +18616,16 @@
       </c>
       <c r="F465" s="7"/>
       <c r="G465" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F465,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H465" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F465,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I465" s="7"/>
       <c r="J465" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F465,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18297,16 +18644,16 @@
       </c>
       <c r="F466" s="7"/>
       <c r="G466" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F466,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H466" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F466,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I466" s="7"/>
       <c r="J466" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F466,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18325,16 +18672,16 @@
       </c>
       <c r="F467" s="7"/>
       <c r="G467" s="7">
-        <f t="shared" si="21"/>
+        <f>IFERROR(VLOOKUP($F467,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H467" s="7">
-        <f t="shared" si="22"/>
+        <f>IFERROR(VLOOKUP($F467,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I467" s="7"/>
       <c r="J467" s="7">
-        <f t="shared" si="23"/>
+        <f>IFERROR(VLOOKUP($F467,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -20067,76 +20414,118 @@
         <v>34431</v>
       </c>
     </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A591" s="13">
+        <v>79040263</v>
+      </c>
+      <c r="B591" s="13" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C591" s="13" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D591" s="36">
+        <v>37881</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L510"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A378:A410 A412:A581 A1:A372 A584:A1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
+  <conditionalFormatting sqref="A592:A1048576 A378:A410 A412:A581 A1:A372 A584:A590">
+    <cfRule type="duplicateValues" dxfId="33" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45:F49">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A581 A584:A1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+  <conditionalFormatting sqref="A592:A1048576 A1:A581 A584:A590">
+    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A378:B379 A382:B410 A380:A381 A412:B581 A1:B122 A124:B176 A123 A178:B372 A177 A584:B1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
+  <conditionalFormatting sqref="A592:B1048576 A378:B379 A382:B410 A380:A381 A412:B581 A1:B122 A124:B176 A123 A178:B372 A177 A584:B590">
+    <cfRule type="duplicateValues" dxfId="24" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A382:B410 A380:A381 A1:B122 A412:B581 A124:B176 A123 A178:B379 A177 A584:B1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="35"/>
+  <conditionalFormatting sqref="A592:B1048576 A382:B410 A380:A381 A1:B122 A412:B581 A124:B176 A123 A178:B379 A177 A584:B590">
+    <cfRule type="duplicateValues" dxfId="23" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C468:C581 C114:C389 C1:C112 C584:C1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="37"/>
+  <conditionalFormatting sqref="C468:C581 C114:C389 C1:C112 C584:C590 C592:C1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="11" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B178:B581 B1:B122 B124:B176 B584:B1048576">
+  <conditionalFormatting sqref="B592:B1048576 B178:B581 B1:B122 B124:B176 B584:B590">
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A592:C1048576 A177 A1:C122 A124:C176 A123 C123 C177 A178:C581 A584:C590">
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F9">
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:A583">
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:A583">
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:B583">
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:B583">
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C582:C583">
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B582:B583">
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:C583">
     <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A177 A1:C122 A124:C176 A123 C123 C177 A178:C581 A584:C1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  <conditionalFormatting sqref="A1:A590 A592:A1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  <conditionalFormatting sqref="A591">
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:A583">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  <conditionalFormatting sqref="A591">
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:A583">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  <conditionalFormatting sqref="A591:B591">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:B583">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  <conditionalFormatting sqref="A591:B591">
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:B583">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+  <conditionalFormatting sqref="C591">
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C582:C583">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+  <conditionalFormatting sqref="B591">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B582:B583">
+  <conditionalFormatting sqref="A591:C591">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:C583">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A591">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/매입가.xlsx
+++ b/data/매입가.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="1213">
   <si>
     <t>주문상품</t>
   </si>
@@ -3694,6 +3694,14 @@
   </si>
   <si>
     <t>A03224</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보아르아가미니휴대용젖병소독기-화이트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A03231</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4005,157 +4013,7 @@
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="58">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5561,7 +5419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L591"/>
+  <dimension ref="A1:L592"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="28" bestFit="1" customWidth="1"/>
@@ -5621,16 +5479,16 @@
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7">
-        <f>IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
+        <f t="shared" ref="G2:G65" si="0">IFERROR(VLOOKUP($F2,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H2" s="7">
-        <f>IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
+        <f t="shared" ref="H2:H65" si="1">IFERROR(VLOOKUP($F2,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7">
-        <f>IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
+        <f t="shared" ref="J2:J65" si="2">IFERROR(VLOOKUP($F2,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" t="s">
@@ -5652,16 +5510,16 @@
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7">
-        <f>IFERROR(VLOOKUP($F3,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H3" s="7">
-        <f>IFERROR(VLOOKUP($F3,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7">
-        <f>IFERROR(VLOOKUP($F3,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" t="s">
@@ -5683,16 +5541,16 @@
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7">
-        <f>IFERROR(VLOOKUP($F4,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H4" s="7">
-        <f>IFERROR(VLOOKUP($F4,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7">
-        <f>IFERROR(VLOOKUP($F4,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" t="s">
@@ -5714,16 +5572,16 @@
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7">
-        <f>IFERROR(VLOOKUP($F5,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H5" s="7">
-        <f>IFERROR(VLOOKUP($F5,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7">
-        <f>IFERROR(VLOOKUP($F5,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" t="s">
@@ -5745,16 +5603,16 @@
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7">
-        <f>IFERROR(VLOOKUP($F6,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6" s="7">
-        <f>IFERROR(VLOOKUP($F6,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7">
-        <f>IFERROR(VLOOKUP($F6,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" t="s">
@@ -5776,16 +5634,16 @@
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7">
-        <f>IFERROR(VLOOKUP($F7,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H7" s="7">
-        <f>IFERROR(VLOOKUP($F7,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7">
-        <f>IFERROR(VLOOKUP($F7,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" t="s">
@@ -5807,16 +5665,16 @@
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7">
-        <f>IFERROR(VLOOKUP($F8,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H8" s="7">
-        <f>IFERROR(VLOOKUP($F8,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7">
-        <f>IFERROR(VLOOKUP($F8,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="5" t="s">
@@ -5838,16 +5696,16 @@
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7">
-        <f>IFERROR(VLOOKUP($F9,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H9" s="7">
-        <f>IFERROR(VLOOKUP($F9,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7">
-        <f>IFERROR(VLOOKUP($F9,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="5" t="s">
@@ -5869,16 +5727,16 @@
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7">
-        <f>IFERROR(VLOOKUP($F10,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H10" s="7">
-        <f>IFERROR(VLOOKUP($F10,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7">
-        <f>IFERROR(VLOOKUP($F10,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="5" t="s">
@@ -5900,16 +5758,16 @@
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7">
-        <f>IFERROR(VLOOKUP($F11,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H11" s="7">
-        <f>IFERROR(VLOOKUP($F11,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7">
-        <f>IFERROR(VLOOKUP($F11,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="5" t="s">
@@ -5931,16 +5789,16 @@
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7">
-        <f>IFERROR(VLOOKUP($F12,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H12" s="7">
-        <f>IFERROR(VLOOKUP($F12,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7">
-        <f>IFERROR(VLOOKUP($F12,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5959,16 +5817,16 @@
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7">
-        <f>IFERROR(VLOOKUP($F13,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H13" s="7">
-        <f>IFERROR(VLOOKUP($F13,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7">
-        <f>IFERROR(VLOOKUP($F13,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5987,16 +5845,16 @@
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7">
-        <f>IFERROR(VLOOKUP($F14,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H14" s="7">
-        <f>IFERROR(VLOOKUP($F14,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7">
-        <f>IFERROR(VLOOKUP($F14,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6015,16 +5873,16 @@
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7">
-        <f>IFERROR(VLOOKUP($F15,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H15" s="7">
-        <f>IFERROR(VLOOKUP($F15,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7">
-        <f>IFERROR(VLOOKUP($F15,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6043,16 +5901,16 @@
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7">
-        <f>IFERROR(VLOOKUP($F16,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <f>IFERROR(VLOOKUP($F16,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7">
-        <f>IFERROR(VLOOKUP($F16,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6071,16 +5929,16 @@
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7">
-        <f>IFERROR(VLOOKUP($F17,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H17" s="7">
-        <f>IFERROR(VLOOKUP($F17,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7">
-        <f>IFERROR(VLOOKUP($F17,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6099,16 +5957,16 @@
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7">
-        <f>IFERROR(VLOOKUP($F18,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H18" s="7">
-        <f>IFERROR(VLOOKUP($F18,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7">
-        <f>IFERROR(VLOOKUP($F18,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6127,16 +5985,16 @@
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7">
-        <f>IFERROR(VLOOKUP($F19,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H19" s="7">
-        <f>IFERROR(VLOOKUP($F19,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7">
-        <f>IFERROR(VLOOKUP($F19,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6155,16 +6013,16 @@
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7">
-        <f>IFERROR(VLOOKUP($F20,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H20" s="7">
-        <f>IFERROR(VLOOKUP($F20,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7">
-        <f>IFERROR(VLOOKUP($F20,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6183,16 +6041,16 @@
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7">
-        <f>IFERROR(VLOOKUP($F21,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H21" s="7">
-        <f>IFERROR(VLOOKUP($F21,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7">
-        <f>IFERROR(VLOOKUP($F21,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6211,16 +6069,16 @@
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7">
-        <f>IFERROR(VLOOKUP($F22,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H22" s="7">
-        <f>IFERROR(VLOOKUP($F22,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7">
-        <f>IFERROR(VLOOKUP($F22,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6239,16 +6097,16 @@
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7">
-        <f>IFERROR(VLOOKUP($F23,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H23" s="7">
-        <f>IFERROR(VLOOKUP($F23,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7">
-        <f>IFERROR(VLOOKUP($F23,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6267,16 +6125,16 @@
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7">
-        <f>IFERROR(VLOOKUP($F24,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H24" s="7">
-        <f>IFERROR(VLOOKUP($F24,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7">
-        <f>IFERROR(VLOOKUP($F24,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6295,16 +6153,16 @@
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7">
-        <f>IFERROR(VLOOKUP($F25,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H25" s="7">
-        <f>IFERROR(VLOOKUP($F25,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7">
-        <f>IFERROR(VLOOKUP($F25,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6323,16 +6181,16 @@
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7">
-        <f>IFERROR(VLOOKUP($F26,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H26" s="7">
-        <f>IFERROR(VLOOKUP($F26,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7">
-        <f>IFERROR(VLOOKUP($F26,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6351,16 +6209,16 @@
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7">
-        <f>IFERROR(VLOOKUP($F27,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H27" s="7">
-        <f>IFERROR(VLOOKUP($F27,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7">
-        <f>IFERROR(VLOOKUP($F27,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6379,16 +6237,16 @@
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7">
-        <f>IFERROR(VLOOKUP($F28,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H28" s="7">
-        <f>IFERROR(VLOOKUP($F28,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7">
-        <f>IFERROR(VLOOKUP($F28,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6407,16 +6265,16 @@
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f>IFERROR(VLOOKUP($F29,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H29" s="7">
-        <f>IFERROR(VLOOKUP($F29,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="7">
-        <f>IFERROR(VLOOKUP($F29,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6435,16 +6293,16 @@
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7">
-        <f>IFERROR(VLOOKUP($F30,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H30" s="7">
-        <f>IFERROR(VLOOKUP($F30,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7">
-        <f>IFERROR(VLOOKUP($F30,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6463,16 +6321,16 @@
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7">
-        <f>IFERROR(VLOOKUP($F31,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H31" s="7">
-        <f>IFERROR(VLOOKUP($F31,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="7">
-        <f>IFERROR(VLOOKUP($F31,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6491,16 +6349,16 @@
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7">
-        <f>IFERROR(VLOOKUP($F32,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H32" s="7">
-        <f>IFERROR(VLOOKUP($F32,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7">
-        <f>IFERROR(VLOOKUP($F32,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6519,16 +6377,16 @@
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7">
-        <f>IFERROR(VLOOKUP($F33,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H33" s="7">
-        <f>IFERROR(VLOOKUP($F33,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="7">
-        <f>IFERROR(VLOOKUP($F33,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6547,16 +6405,16 @@
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7">
-        <f>IFERROR(VLOOKUP($F34,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H34" s="7">
-        <f>IFERROR(VLOOKUP($F34,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7">
-        <f>IFERROR(VLOOKUP($F34,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6575,16 +6433,16 @@
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7">
-        <f>IFERROR(VLOOKUP($F35,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H35" s="7">
-        <f>IFERROR(VLOOKUP($F35,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7">
-        <f>IFERROR(VLOOKUP($F35,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6603,16 +6461,16 @@
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7">
-        <f>IFERROR(VLOOKUP($F36,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H36" s="7">
-        <f>IFERROR(VLOOKUP($F36,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7">
-        <f>IFERROR(VLOOKUP($F36,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6631,16 +6489,16 @@
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7">
-        <f>IFERROR(VLOOKUP($F37,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H37" s="7">
-        <f>IFERROR(VLOOKUP($F37,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="7">
-        <f>IFERROR(VLOOKUP($F37,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6659,16 +6517,16 @@
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7">
-        <f>IFERROR(VLOOKUP($F38,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H38" s="7">
-        <f>IFERROR(VLOOKUP($F38,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7">
-        <f>IFERROR(VLOOKUP($F38,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6687,16 +6545,16 @@
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7">
-        <f>IFERROR(VLOOKUP($F39,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H39" s="7">
-        <f>IFERROR(VLOOKUP($F39,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7">
-        <f>IFERROR(VLOOKUP($F39,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6715,16 +6573,16 @@
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7">
-        <f>IFERROR(VLOOKUP($F40,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H40" s="7">
-        <f>IFERROR(VLOOKUP($F40,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="7">
-        <f>IFERROR(VLOOKUP($F40,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6743,16 +6601,16 @@
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7">
-        <f>IFERROR(VLOOKUP($F41,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H41" s="7">
-        <f>IFERROR(VLOOKUP($F41,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="7">
-        <f>IFERROR(VLOOKUP($F41,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6772,16 +6630,16 @@
       <c r="E42" s="4"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7">
-        <f>IFERROR(VLOOKUP($F42,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H42" s="7">
-        <f>IFERROR(VLOOKUP($F42,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="7">
-        <f>IFERROR(VLOOKUP($F42,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6800,16 +6658,16 @@
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7">
-        <f>IFERROR(VLOOKUP($F43,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H43" s="7">
-        <f>IFERROR(VLOOKUP($F43,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I43" s="7"/>
       <c r="J43" s="7">
-        <f>IFERROR(VLOOKUP($F43,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6828,16 +6686,16 @@
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7">
-        <f>IFERROR(VLOOKUP($F44,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H44" s="7">
-        <f>IFERROR(VLOOKUP($F44,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7">
-        <f>IFERROR(VLOOKUP($F44,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6856,16 +6714,16 @@
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7">
-        <f>IFERROR(VLOOKUP($F45,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H45" s="7">
-        <f>IFERROR(VLOOKUP($F45,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="7">
-        <f>IFERROR(VLOOKUP($F45,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6884,16 +6742,16 @@
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7">
-        <f>IFERROR(VLOOKUP($F46,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H46" s="7">
-        <f>IFERROR(VLOOKUP($F46,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I46" s="7"/>
       <c r="J46" s="7">
-        <f>IFERROR(VLOOKUP($F46,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6912,16 +6770,16 @@
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7">
-        <f>IFERROR(VLOOKUP($F47,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H47" s="7">
-        <f>IFERROR(VLOOKUP($F47,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="7">
-        <f>IFERROR(VLOOKUP($F47,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6940,16 +6798,16 @@
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7">
-        <f>IFERROR(VLOOKUP($F48,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H48" s="7">
-        <f>IFERROR(VLOOKUP($F48,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="7">
-        <f>IFERROR(VLOOKUP($F48,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6968,16 +6826,16 @@
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7">
-        <f>IFERROR(VLOOKUP($F49,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H49" s="7">
-        <f>IFERROR(VLOOKUP($F49,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7">
-        <f>IFERROR(VLOOKUP($F49,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6996,16 +6854,16 @@
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7">
-        <f>IFERROR(VLOOKUP($F50,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H50" s="7">
-        <f>IFERROR(VLOOKUP($F50,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="7">
-        <f>IFERROR(VLOOKUP($F50,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7024,16 +6882,16 @@
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7">
-        <f>IFERROR(VLOOKUP($F51,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H51" s="7">
-        <f>IFERROR(VLOOKUP($F51,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I51" s="7"/>
       <c r="J51" s="7">
-        <f>IFERROR(VLOOKUP($F51,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7052,16 +6910,16 @@
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7">
-        <f>IFERROR(VLOOKUP($F52,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H52" s="7">
-        <f>IFERROR(VLOOKUP($F52,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I52" s="7"/>
       <c r="J52" s="7">
-        <f>IFERROR(VLOOKUP($F52,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7080,16 +6938,16 @@
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7">
-        <f>IFERROR(VLOOKUP($F53,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H53" s="7">
-        <f>IFERROR(VLOOKUP($F53,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="7">
-        <f>IFERROR(VLOOKUP($F53,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7108,16 +6966,16 @@
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7">
-        <f>IFERROR(VLOOKUP($F54,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H54" s="7">
-        <f>IFERROR(VLOOKUP($F54,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I54" s="7"/>
       <c r="J54" s="7">
-        <f>IFERROR(VLOOKUP($F54,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7136,16 +6994,16 @@
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7">
-        <f>IFERROR(VLOOKUP($F55,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H55" s="7">
-        <f>IFERROR(VLOOKUP($F55,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="7">
-        <f>IFERROR(VLOOKUP($F55,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7164,16 +7022,16 @@
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7">
-        <f>IFERROR(VLOOKUP($F56,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H56" s="7">
-        <f>IFERROR(VLOOKUP($F56,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="7">
-        <f>IFERROR(VLOOKUP($F56,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7192,16 +7050,16 @@
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="7">
-        <f>IFERROR(VLOOKUP($F57,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H57" s="7">
-        <f>IFERROR(VLOOKUP($F57,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="7">
-        <f>IFERROR(VLOOKUP($F57,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7220,16 +7078,16 @@
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7">
-        <f>IFERROR(VLOOKUP($F58,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H58" s="7">
-        <f>IFERROR(VLOOKUP($F58,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="7">
-        <f>IFERROR(VLOOKUP($F58,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7248,16 +7106,16 @@
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="7">
-        <f>IFERROR(VLOOKUP($F59,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H59" s="7">
-        <f>IFERROR(VLOOKUP($F59,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7">
-        <f>IFERROR(VLOOKUP($F59,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7276,16 +7134,16 @@
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7">
-        <f>IFERROR(VLOOKUP($F60,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H60" s="7">
-        <f>IFERROR(VLOOKUP($F60,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="7">
-        <f>IFERROR(VLOOKUP($F60,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7304,16 +7162,16 @@
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7">
-        <f>IFERROR(VLOOKUP($F61,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H61" s="7">
-        <f>IFERROR(VLOOKUP($F61,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="7">
-        <f>IFERROR(VLOOKUP($F61,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7332,16 +7190,16 @@
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7">
-        <f>IFERROR(VLOOKUP($F62,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H62" s="7">
-        <f>IFERROR(VLOOKUP($F62,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="7">
-        <f>IFERROR(VLOOKUP($F62,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7360,16 +7218,16 @@
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7">
-        <f>IFERROR(VLOOKUP($F63,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H63" s="7">
-        <f>IFERROR(VLOOKUP($F63,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="7">
-        <f>IFERROR(VLOOKUP($F63,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7388,16 +7246,16 @@
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7">
-        <f>IFERROR(VLOOKUP($F64,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H64" s="7">
-        <f>IFERROR(VLOOKUP($F64,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="7">
-        <f>IFERROR(VLOOKUP($F64,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7416,16 +7274,16 @@
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7">
-        <f>IFERROR(VLOOKUP($F65,$A:$B,2,0),0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H65" s="7">
-        <f>IFERROR(VLOOKUP($F65,$A:$D,3,0),0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="7">
-        <f>IFERROR(VLOOKUP($F65,$A:$D,4,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7444,16 +7302,16 @@
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7">
-        <f>IFERROR(VLOOKUP($F66,$A:$B,2,0),0)</f>
+        <f t="shared" ref="G66:G129" si="3">IFERROR(VLOOKUP($F66,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H66" s="7">
-        <f>IFERROR(VLOOKUP($F66,$A:$D,3,0),0)</f>
+        <f t="shared" ref="H66:H129" si="4">IFERROR(VLOOKUP($F66,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="7">
-        <f>IFERROR(VLOOKUP($F66,$A:$D,4,0),0)</f>
+        <f t="shared" ref="J66:J129" si="5">IFERROR(VLOOKUP($F66,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7472,16 +7330,16 @@
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7">
-        <f>IFERROR(VLOOKUP($F67,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H67" s="7">
-        <f>IFERROR(VLOOKUP($F67,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="7">
-        <f>IFERROR(VLOOKUP($F67,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7500,16 +7358,16 @@
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7">
-        <f>IFERROR(VLOOKUP($F68,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H68" s="7">
-        <f>IFERROR(VLOOKUP($F68,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="7">
-        <f>IFERROR(VLOOKUP($F68,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7528,16 +7386,16 @@
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7">
-        <f>IFERROR(VLOOKUP($F69,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H69" s="7">
-        <f>IFERROR(VLOOKUP($F69,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="7">
-        <f>IFERROR(VLOOKUP($F69,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7556,16 +7414,16 @@
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7">
-        <f>IFERROR(VLOOKUP($F70,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H70" s="7">
-        <f>IFERROR(VLOOKUP($F70,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="7">
-        <f>IFERROR(VLOOKUP($F70,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7584,16 +7442,16 @@
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="7">
-        <f>IFERROR(VLOOKUP($F71,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H71" s="7">
-        <f>IFERROR(VLOOKUP($F71,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="7">
-        <f>IFERROR(VLOOKUP($F71,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7612,16 +7470,16 @@
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7">
-        <f>IFERROR(VLOOKUP($F72,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H72" s="7">
-        <f>IFERROR(VLOOKUP($F72,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="7">
-        <f>IFERROR(VLOOKUP($F72,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7640,16 +7498,16 @@
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7">
-        <f>IFERROR(VLOOKUP($F73,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H73" s="7">
-        <f>IFERROR(VLOOKUP($F73,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I73" s="7"/>
       <c r="J73" s="7">
-        <f>IFERROR(VLOOKUP($F73,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7668,16 +7526,16 @@
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7">
-        <f>IFERROR(VLOOKUP($F74,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H74" s="7">
-        <f>IFERROR(VLOOKUP($F74,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="7">
-        <f>IFERROR(VLOOKUP($F74,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7696,16 +7554,16 @@
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7">
-        <f>IFERROR(VLOOKUP($F75,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H75" s="7">
-        <f>IFERROR(VLOOKUP($F75,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="7">
-        <f>IFERROR(VLOOKUP($F75,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7724,16 +7582,16 @@
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7">
-        <f>IFERROR(VLOOKUP($F76,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H76" s="7">
-        <f>IFERROR(VLOOKUP($F76,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="7">
-        <f>IFERROR(VLOOKUP($F76,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7752,16 +7610,16 @@
       </c>
       <c r="F77" s="7"/>
       <c r="G77" s="7">
-        <f>IFERROR(VLOOKUP($F77,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H77" s="7">
-        <f>IFERROR(VLOOKUP($F77,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="7">
-        <f>IFERROR(VLOOKUP($F77,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7780,16 +7638,16 @@
       </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7">
-        <f>IFERROR(VLOOKUP($F78,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H78" s="7">
-        <f>IFERROR(VLOOKUP($F78,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I78" s="7"/>
       <c r="J78" s="7">
-        <f>IFERROR(VLOOKUP($F78,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7808,16 +7666,16 @@
       </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7">
-        <f>IFERROR(VLOOKUP($F79,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H79" s="7">
-        <f>IFERROR(VLOOKUP($F79,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="7">
-        <f>IFERROR(VLOOKUP($F79,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7836,16 +7694,16 @@
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7">
-        <f>IFERROR(VLOOKUP($F80,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H80" s="7">
-        <f>IFERROR(VLOOKUP($F80,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I80" s="7"/>
       <c r="J80" s="7">
-        <f>IFERROR(VLOOKUP($F80,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7864,16 +7722,16 @@
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7">
-        <f>IFERROR(VLOOKUP($F81,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H81" s="7">
-        <f>IFERROR(VLOOKUP($F81,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I81" s="7"/>
       <c r="J81" s="7">
-        <f>IFERROR(VLOOKUP($F81,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7892,16 +7750,16 @@
       </c>
       <c r="F82" s="7"/>
       <c r="G82" s="7">
-        <f>IFERROR(VLOOKUP($F82,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H82" s="7">
-        <f>IFERROR(VLOOKUP($F82,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="7">
-        <f>IFERROR(VLOOKUP($F82,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7920,16 +7778,16 @@
       </c>
       <c r="F83" s="7"/>
       <c r="G83" s="7">
-        <f>IFERROR(VLOOKUP($F83,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H83" s="7">
-        <f>IFERROR(VLOOKUP($F83,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="7">
-        <f>IFERROR(VLOOKUP($F83,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7948,16 +7806,16 @@
       </c>
       <c r="F84" s="7"/>
       <c r="G84" s="7">
-        <f>IFERROR(VLOOKUP($F84,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H84" s="7">
-        <f>IFERROR(VLOOKUP($F84,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="7">
-        <f>IFERROR(VLOOKUP($F84,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -7976,16 +7834,16 @@
       </c>
       <c r="F85" s="7"/>
       <c r="G85" s="7">
-        <f>IFERROR(VLOOKUP($F85,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H85" s="7">
-        <f>IFERROR(VLOOKUP($F85,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="7">
-        <f>IFERROR(VLOOKUP($F85,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8004,16 +7862,16 @@
       </c>
       <c r="F86" s="7"/>
       <c r="G86" s="7">
-        <f>IFERROR(VLOOKUP($F86,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H86" s="7">
-        <f>IFERROR(VLOOKUP($F86,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I86" s="7"/>
       <c r="J86" s="7">
-        <f>IFERROR(VLOOKUP($F86,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8032,16 +7890,16 @@
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7">
-        <f>IFERROR(VLOOKUP($F87,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H87" s="7">
-        <f>IFERROR(VLOOKUP($F87,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="7">
-        <f>IFERROR(VLOOKUP($F87,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8060,16 +7918,16 @@
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7">
-        <f>IFERROR(VLOOKUP($F88,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H88" s="7">
-        <f>IFERROR(VLOOKUP($F88,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="7">
-        <f>IFERROR(VLOOKUP($F88,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8088,16 +7946,16 @@
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7">
-        <f>IFERROR(VLOOKUP($F89,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H89" s="7">
-        <f>IFERROR(VLOOKUP($F89,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="7">
-        <f>IFERROR(VLOOKUP($F89,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8116,16 +7974,16 @@
       </c>
       <c r="F90" s="7"/>
       <c r="G90" s="7">
-        <f>IFERROR(VLOOKUP($F90,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H90" s="7">
-        <f>IFERROR(VLOOKUP($F90,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="7">
-        <f>IFERROR(VLOOKUP($F90,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8144,16 +8002,16 @@
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7">
-        <f>IFERROR(VLOOKUP($F91,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H91" s="7">
-        <f>IFERROR(VLOOKUP($F91,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I91" s="7"/>
       <c r="J91" s="7">
-        <f>IFERROR(VLOOKUP($F91,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8172,16 +8030,16 @@
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="7">
-        <f>IFERROR(VLOOKUP($F92,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H92" s="7">
-        <f>IFERROR(VLOOKUP($F92,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="7">
-        <f>IFERROR(VLOOKUP($F92,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8200,16 +8058,16 @@
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7">
-        <f>IFERROR(VLOOKUP($F93,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H93" s="7">
-        <f>IFERROR(VLOOKUP($F93,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I93" s="7"/>
       <c r="J93" s="7">
-        <f>IFERROR(VLOOKUP($F93,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8228,16 +8086,16 @@
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7">
-        <f>IFERROR(VLOOKUP($F94,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H94" s="7">
-        <f>IFERROR(VLOOKUP($F94,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I94" s="7"/>
       <c r="J94" s="7">
-        <f>IFERROR(VLOOKUP($F94,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8256,16 +8114,16 @@
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7">
-        <f>IFERROR(VLOOKUP($F95,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H95" s="7">
-        <f>IFERROR(VLOOKUP($F95,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I95" s="7"/>
       <c r="J95" s="7">
-        <f>IFERROR(VLOOKUP($F95,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8284,16 +8142,16 @@
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7">
-        <f>IFERROR(VLOOKUP($F96,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H96" s="7">
-        <f>IFERROR(VLOOKUP($F96,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I96" s="7"/>
       <c r="J96" s="7">
-        <f>IFERROR(VLOOKUP($F96,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8312,16 +8170,16 @@
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="7">
-        <f>IFERROR(VLOOKUP($F97,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H97" s="7">
-        <f>IFERROR(VLOOKUP($F97,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="7">
-        <f>IFERROR(VLOOKUP($F97,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8340,16 +8198,16 @@
       </c>
       <c r="F98" s="7"/>
       <c r="G98" s="7">
-        <f>IFERROR(VLOOKUP($F98,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H98" s="7">
-        <f>IFERROR(VLOOKUP($F98,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="7">
-        <f>IFERROR(VLOOKUP($F98,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8368,16 +8226,16 @@
       </c>
       <c r="F99" s="7"/>
       <c r="G99" s="7">
-        <f>IFERROR(VLOOKUP($F99,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H99" s="7">
-        <f>IFERROR(VLOOKUP($F99,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="7">
-        <f>IFERROR(VLOOKUP($F99,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8396,16 +8254,16 @@
       </c>
       <c r="F100" s="7"/>
       <c r="G100" s="7">
-        <f>IFERROR(VLOOKUP($F100,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H100" s="7">
-        <f>IFERROR(VLOOKUP($F100,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="7">
-        <f>IFERROR(VLOOKUP($F100,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8424,16 +8282,16 @@
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7">
-        <f>IFERROR(VLOOKUP($F101,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H101" s="7">
-        <f>IFERROR(VLOOKUP($F101,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="7">
-        <f>IFERROR(VLOOKUP($F101,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8452,16 +8310,16 @@
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7">
-        <f>IFERROR(VLOOKUP($F102,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H102" s="7">
-        <f>IFERROR(VLOOKUP($F102,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I102" s="7"/>
       <c r="J102" s="7">
-        <f>IFERROR(VLOOKUP($F102,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8480,16 +8338,16 @@
       </c>
       <c r="F103" s="7"/>
       <c r="G103" s="7">
-        <f>IFERROR(VLOOKUP($F103,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H103" s="7">
-        <f>IFERROR(VLOOKUP($F103,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7">
-        <f>IFERROR(VLOOKUP($F103,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8508,16 +8366,16 @@
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7">
-        <f>IFERROR(VLOOKUP($F104,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H104" s="7">
-        <f>IFERROR(VLOOKUP($F104,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I104" s="7"/>
       <c r="J104" s="7">
-        <f>IFERROR(VLOOKUP($F104,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8536,16 +8394,16 @@
       </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7">
-        <f>IFERROR(VLOOKUP($F105,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H105" s="7">
-        <f>IFERROR(VLOOKUP($F105,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7">
-        <f>IFERROR(VLOOKUP($F105,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8564,16 +8422,16 @@
       </c>
       <c r="F106" s="7"/>
       <c r="G106" s="7">
-        <f>IFERROR(VLOOKUP($F106,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H106" s="7">
-        <f>IFERROR(VLOOKUP($F106,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I106" s="7"/>
       <c r="J106" s="7">
-        <f>IFERROR(VLOOKUP($F106,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8592,16 +8450,16 @@
       </c>
       <c r="F107" s="7"/>
       <c r="G107" s="7">
-        <f>IFERROR(VLOOKUP($F107,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H107" s="7">
-        <f>IFERROR(VLOOKUP($F107,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I107" s="7"/>
       <c r="J107" s="7">
-        <f>IFERROR(VLOOKUP($F107,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8620,16 +8478,16 @@
       </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7">
-        <f>IFERROR(VLOOKUP($F108,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H108" s="7">
-        <f>IFERROR(VLOOKUP($F108,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I108" s="7"/>
       <c r="J108" s="7">
-        <f>IFERROR(VLOOKUP($F108,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8648,16 +8506,16 @@
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7">
-        <f>IFERROR(VLOOKUP($F109,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H109" s="7">
-        <f>IFERROR(VLOOKUP($F109,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I109" s="7"/>
       <c r="J109" s="7">
-        <f>IFERROR(VLOOKUP($F109,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8676,16 +8534,16 @@
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7">
-        <f>IFERROR(VLOOKUP($F110,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H110" s="7">
-        <f>IFERROR(VLOOKUP($F110,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I110" s="7"/>
       <c r="J110" s="7">
-        <f>IFERROR(VLOOKUP($F110,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8704,16 +8562,16 @@
       </c>
       <c r="F111" s="7"/>
       <c r="G111" s="7">
-        <f>IFERROR(VLOOKUP($F111,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H111" s="7">
-        <f>IFERROR(VLOOKUP($F111,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I111" s="7"/>
       <c r="J111" s="7">
-        <f>IFERROR(VLOOKUP($F111,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8732,16 +8590,16 @@
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7">
-        <f>IFERROR(VLOOKUP($F112,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H112" s="7">
-        <f>IFERROR(VLOOKUP($F112,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I112" s="7"/>
       <c r="J112" s="7">
-        <f>IFERROR(VLOOKUP($F112,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8760,16 +8618,16 @@
       </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7">
-        <f>IFERROR(VLOOKUP($F113,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H113" s="7">
-        <f>IFERROR(VLOOKUP($F113,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I113" s="7"/>
       <c r="J113" s="7">
-        <f>IFERROR(VLOOKUP($F113,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8788,16 +8646,16 @@
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7">
-        <f>IFERROR(VLOOKUP($F114,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H114" s="7">
-        <f>IFERROR(VLOOKUP($F114,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="7">
-        <f>IFERROR(VLOOKUP($F114,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8816,16 +8674,16 @@
       </c>
       <c r="F115" s="7"/>
       <c r="G115" s="7">
-        <f>IFERROR(VLOOKUP($F115,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H115" s="7">
-        <f>IFERROR(VLOOKUP($F115,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I115" s="7"/>
       <c r="J115" s="7">
-        <f>IFERROR(VLOOKUP($F115,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8844,16 +8702,16 @@
       </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7">
-        <f>IFERROR(VLOOKUP($F116,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H116" s="7">
-        <f>IFERROR(VLOOKUP($F116,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I116" s="7"/>
       <c r="J116" s="7">
-        <f>IFERROR(VLOOKUP($F116,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8872,16 +8730,16 @@
       </c>
       <c r="F117" s="7"/>
       <c r="G117" s="7">
-        <f>IFERROR(VLOOKUP($F117,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H117" s="7">
-        <f>IFERROR(VLOOKUP($F117,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I117" s="7"/>
       <c r="J117" s="7">
-        <f>IFERROR(VLOOKUP($F117,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8900,16 +8758,16 @@
       </c>
       <c r="F118" s="7"/>
       <c r="G118" s="7">
-        <f>IFERROR(VLOOKUP($F118,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H118" s="7">
-        <f>IFERROR(VLOOKUP($F118,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I118" s="7"/>
       <c r="J118" s="7">
-        <f>IFERROR(VLOOKUP($F118,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8928,16 +8786,16 @@
       </c>
       <c r="F119" s="7"/>
       <c r="G119" s="7">
-        <f>IFERROR(VLOOKUP($F119,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H119" s="7">
-        <f>IFERROR(VLOOKUP($F119,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I119" s="7"/>
       <c r="J119" s="7">
-        <f>IFERROR(VLOOKUP($F119,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8956,16 +8814,16 @@
       </c>
       <c r="F120" s="7"/>
       <c r="G120" s="7">
-        <f>IFERROR(VLOOKUP($F120,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H120" s="7">
-        <f>IFERROR(VLOOKUP($F120,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I120" s="7"/>
       <c r="J120" s="7">
-        <f>IFERROR(VLOOKUP($F120,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -8984,16 +8842,16 @@
       </c>
       <c r="F121" s="7"/>
       <c r="G121" s="7">
-        <f>IFERROR(VLOOKUP($F121,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H121" s="7">
-        <f>IFERROR(VLOOKUP($F121,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I121" s="7"/>
       <c r="J121" s="7">
-        <f>IFERROR(VLOOKUP($F121,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9012,16 +8870,16 @@
       </c>
       <c r="F122" s="7"/>
       <c r="G122" s="7">
-        <f>IFERROR(VLOOKUP($F122,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H122" s="7">
-        <f>IFERROR(VLOOKUP($F122,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I122" s="7"/>
       <c r="J122" s="7">
-        <f>IFERROR(VLOOKUP($F122,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9040,16 +8898,16 @@
       </c>
       <c r="F123" s="7"/>
       <c r="G123" s="7">
-        <f>IFERROR(VLOOKUP($F123,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H123" s="7">
-        <f>IFERROR(VLOOKUP($F123,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="7">
-        <f>IFERROR(VLOOKUP($F123,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9068,16 +8926,16 @@
       </c>
       <c r="F124" s="7"/>
       <c r="G124" s="7">
-        <f>IFERROR(VLOOKUP($F124,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H124" s="7">
-        <f>IFERROR(VLOOKUP($F124,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I124" s="7"/>
       <c r="J124" s="7">
-        <f>IFERROR(VLOOKUP($F124,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9096,16 +8954,16 @@
       </c>
       <c r="F125" s="7"/>
       <c r="G125" s="7">
-        <f>IFERROR(VLOOKUP($F125,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H125" s="7">
-        <f>IFERROR(VLOOKUP($F125,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I125" s="7"/>
       <c r="J125" s="7">
-        <f>IFERROR(VLOOKUP($F125,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9124,16 +8982,16 @@
       </c>
       <c r="F126" s="7"/>
       <c r="G126" s="7">
-        <f>IFERROR(VLOOKUP($F126,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H126" s="7">
-        <f>IFERROR(VLOOKUP($F126,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I126" s="7"/>
       <c r="J126" s="7">
-        <f>IFERROR(VLOOKUP($F126,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9152,16 +9010,16 @@
       </c>
       <c r="F127" s="7"/>
       <c r="G127" s="7">
-        <f>IFERROR(VLOOKUP($F127,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H127" s="7">
-        <f>IFERROR(VLOOKUP($F127,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I127" s="7"/>
       <c r="J127" s="7">
-        <f>IFERROR(VLOOKUP($F127,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9180,16 +9038,16 @@
       </c>
       <c r="F128" s="7"/>
       <c r="G128" s="7">
-        <f>IFERROR(VLOOKUP($F128,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H128" s="7">
-        <f>IFERROR(VLOOKUP($F128,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I128" s="7"/>
       <c r="J128" s="7">
-        <f>IFERROR(VLOOKUP($F128,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9208,16 +9066,16 @@
       </c>
       <c r="F129" s="7"/>
       <c r="G129" s="7">
-        <f>IFERROR(VLOOKUP($F129,$A:$B,2,0),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H129" s="7">
-        <f>IFERROR(VLOOKUP($F129,$A:$D,3,0),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I129" s="7"/>
       <c r="J129" s="7">
-        <f>IFERROR(VLOOKUP($F129,$A:$D,4,0),0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9236,16 +9094,16 @@
       </c>
       <c r="F130" s="7"/>
       <c r="G130" s="7">
-        <f>IFERROR(VLOOKUP($F130,$A:$B,2,0),0)</f>
+        <f t="shared" ref="G130:G193" si="6">IFERROR(VLOOKUP($F130,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H130" s="7">
-        <f>IFERROR(VLOOKUP($F130,$A:$D,3,0),0)</f>
+        <f t="shared" ref="H130:H193" si="7">IFERROR(VLOOKUP($F130,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I130" s="7"/>
       <c r="J130" s="7">
-        <f>IFERROR(VLOOKUP($F130,$A:$D,4,0),0)</f>
+        <f t="shared" ref="J130:J193" si="8">IFERROR(VLOOKUP($F130,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -9264,16 +9122,16 @@
       </c>
       <c r="F131" s="7"/>
       <c r="G131" s="7">
-        <f>IFERROR(VLOOKUP($F131,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H131" s="7">
-        <f>IFERROR(VLOOKUP($F131,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I131" s="7"/>
       <c r="J131" s="7">
-        <f>IFERROR(VLOOKUP($F131,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9292,16 +9150,16 @@
       </c>
       <c r="F132" s="7"/>
       <c r="G132" s="7">
-        <f>IFERROR(VLOOKUP($F132,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H132" s="7">
-        <f>IFERROR(VLOOKUP($F132,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I132" s="7"/>
       <c r="J132" s="7">
-        <f>IFERROR(VLOOKUP($F132,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9320,16 +9178,16 @@
       </c>
       <c r="F133" s="7"/>
       <c r="G133" s="7">
-        <f>IFERROR(VLOOKUP($F133,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H133" s="7">
-        <f>IFERROR(VLOOKUP($F133,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I133" s="7"/>
       <c r="J133" s="7">
-        <f>IFERROR(VLOOKUP($F133,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9348,16 +9206,16 @@
       </c>
       <c r="F134" s="7"/>
       <c r="G134" s="7">
-        <f>IFERROR(VLOOKUP($F134,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H134" s="7">
-        <f>IFERROR(VLOOKUP($F134,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I134" s="7"/>
       <c r="J134" s="7">
-        <f>IFERROR(VLOOKUP($F134,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9376,16 +9234,16 @@
       </c>
       <c r="F135" s="7"/>
       <c r="G135" s="7">
-        <f>IFERROR(VLOOKUP($F135,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H135" s="7">
-        <f>IFERROR(VLOOKUP($F135,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I135" s="7"/>
       <c r="J135" s="7">
-        <f>IFERROR(VLOOKUP($F135,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9404,16 +9262,16 @@
       </c>
       <c r="F136" s="7"/>
       <c r="G136" s="7">
-        <f>IFERROR(VLOOKUP($F136,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H136" s="7">
-        <f>IFERROR(VLOOKUP($F136,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I136" s="7"/>
       <c r="J136" s="7">
-        <f>IFERROR(VLOOKUP($F136,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9432,16 +9290,16 @@
       </c>
       <c r="F137" s="7"/>
       <c r="G137" s="7">
-        <f>IFERROR(VLOOKUP($F137,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H137" s="7">
-        <f>IFERROR(VLOOKUP($F137,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I137" s="7"/>
       <c r="J137" s="7">
-        <f>IFERROR(VLOOKUP($F137,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9460,16 +9318,16 @@
       </c>
       <c r="F138" s="7"/>
       <c r="G138" s="7">
-        <f>IFERROR(VLOOKUP($F138,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H138" s="7">
-        <f>IFERROR(VLOOKUP($F138,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I138" s="7"/>
       <c r="J138" s="7">
-        <f>IFERROR(VLOOKUP($F138,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9488,16 +9346,16 @@
       </c>
       <c r="F139" s="7"/>
       <c r="G139" s="7">
-        <f>IFERROR(VLOOKUP($F139,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H139" s="7">
-        <f>IFERROR(VLOOKUP($F139,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I139" s="7"/>
       <c r="J139" s="7">
-        <f>IFERROR(VLOOKUP($F139,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9516,16 +9374,16 @@
       </c>
       <c r="F140" s="7"/>
       <c r="G140" s="7">
-        <f>IFERROR(VLOOKUP($F140,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H140" s="7">
-        <f>IFERROR(VLOOKUP($F140,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I140" s="7"/>
       <c r="J140" s="7">
-        <f>IFERROR(VLOOKUP($F140,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9544,16 +9402,16 @@
       </c>
       <c r="F141" s="7"/>
       <c r="G141" s="7">
-        <f>IFERROR(VLOOKUP($F141,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H141" s="7">
-        <f>IFERROR(VLOOKUP($F141,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I141" s="7"/>
       <c r="J141" s="7">
-        <f>IFERROR(VLOOKUP($F141,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9572,16 +9430,16 @@
       </c>
       <c r="F142" s="7"/>
       <c r="G142" s="7">
-        <f>IFERROR(VLOOKUP($F142,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H142" s="7">
-        <f>IFERROR(VLOOKUP($F142,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I142" s="7"/>
       <c r="J142" s="7">
-        <f>IFERROR(VLOOKUP($F142,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9600,16 +9458,16 @@
       </c>
       <c r="F143" s="7"/>
       <c r="G143" s="7">
-        <f>IFERROR(VLOOKUP($F143,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H143" s="7">
-        <f>IFERROR(VLOOKUP($F143,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I143" s="7"/>
       <c r="J143" s="7">
-        <f>IFERROR(VLOOKUP($F143,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9628,16 +9486,16 @@
       </c>
       <c r="F144" s="7"/>
       <c r="G144" s="7">
-        <f>IFERROR(VLOOKUP($F144,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H144" s="7">
-        <f>IFERROR(VLOOKUP($F144,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I144" s="7"/>
       <c r="J144" s="7">
-        <f>IFERROR(VLOOKUP($F144,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9656,16 +9514,16 @@
       </c>
       <c r="F145" s="7"/>
       <c r="G145" s="7">
-        <f>IFERROR(VLOOKUP($F145,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H145" s="7">
-        <f>IFERROR(VLOOKUP($F145,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I145" s="7"/>
       <c r="J145" s="7">
-        <f>IFERROR(VLOOKUP($F145,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9684,16 +9542,16 @@
       </c>
       <c r="F146" s="7"/>
       <c r="G146" s="7">
-        <f>IFERROR(VLOOKUP($F146,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H146" s="7">
-        <f>IFERROR(VLOOKUP($F146,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I146" s="7"/>
       <c r="J146" s="7">
-        <f>IFERROR(VLOOKUP($F146,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9712,16 +9570,16 @@
       </c>
       <c r="F147" s="7"/>
       <c r="G147" s="7">
-        <f>IFERROR(VLOOKUP($F147,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H147" s="7">
-        <f>IFERROR(VLOOKUP($F147,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I147" s="7"/>
       <c r="J147" s="7">
-        <f>IFERROR(VLOOKUP($F147,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9740,16 +9598,16 @@
       </c>
       <c r="F148" s="7"/>
       <c r="G148" s="7">
-        <f>IFERROR(VLOOKUP($F148,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H148" s="7">
-        <f>IFERROR(VLOOKUP($F148,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I148" s="7"/>
       <c r="J148" s="7">
-        <f>IFERROR(VLOOKUP($F148,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9768,16 +9626,16 @@
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7">
-        <f>IFERROR(VLOOKUP($F149,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H149" s="7">
-        <f>IFERROR(VLOOKUP($F149,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I149" s="7"/>
       <c r="J149" s="7">
-        <f>IFERROR(VLOOKUP($F149,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9796,16 +9654,16 @@
       </c>
       <c r="F150" s="7"/>
       <c r="G150" s="7">
-        <f>IFERROR(VLOOKUP($F150,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H150" s="7">
-        <f>IFERROR(VLOOKUP($F150,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I150" s="7"/>
       <c r="J150" s="7">
-        <f>IFERROR(VLOOKUP($F150,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9824,16 +9682,16 @@
       </c>
       <c r="F151" s="7"/>
       <c r="G151" s="7">
-        <f>IFERROR(VLOOKUP($F151,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H151" s="7">
-        <f>IFERROR(VLOOKUP($F151,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="7">
-        <f>IFERROR(VLOOKUP($F151,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9852,16 +9710,16 @@
       </c>
       <c r="F152" s="7"/>
       <c r="G152" s="7">
-        <f>IFERROR(VLOOKUP($F152,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H152" s="7">
-        <f>IFERROR(VLOOKUP($F152,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I152" s="7"/>
       <c r="J152" s="7">
-        <f>IFERROR(VLOOKUP($F152,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9880,16 +9738,16 @@
       </c>
       <c r="F153" s="7"/>
       <c r="G153" s="7">
-        <f>IFERROR(VLOOKUP($F153,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H153" s="7">
-        <f>IFERROR(VLOOKUP($F153,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I153" s="7"/>
       <c r="J153" s="7">
-        <f>IFERROR(VLOOKUP($F153,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9908,16 +9766,16 @@
       </c>
       <c r="F154" s="7"/>
       <c r="G154" s="7">
-        <f>IFERROR(VLOOKUP($F154,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H154" s="7">
-        <f>IFERROR(VLOOKUP($F154,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="7">
-        <f>IFERROR(VLOOKUP($F154,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9936,16 +9794,16 @@
       </c>
       <c r="F155" s="7"/>
       <c r="G155" s="7">
-        <f>IFERROR(VLOOKUP($F155,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H155" s="7">
-        <f>IFERROR(VLOOKUP($F155,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I155" s="7"/>
       <c r="J155" s="7">
-        <f>IFERROR(VLOOKUP($F155,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9964,16 +9822,16 @@
       </c>
       <c r="F156" s="7"/>
       <c r="G156" s="7">
-        <f>IFERROR(VLOOKUP($F156,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H156" s="7">
-        <f>IFERROR(VLOOKUP($F156,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I156" s="7"/>
       <c r="J156" s="7">
-        <f>IFERROR(VLOOKUP($F156,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9992,16 +9850,16 @@
       </c>
       <c r="F157" s="7"/>
       <c r="G157" s="7">
-        <f>IFERROR(VLOOKUP($F157,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H157" s="7">
-        <f>IFERROR(VLOOKUP($F157,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I157" s="7"/>
       <c r="J157" s="7">
-        <f>IFERROR(VLOOKUP($F157,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10020,16 +9878,16 @@
       </c>
       <c r="F158" s="7"/>
       <c r="G158" s="7">
-        <f>IFERROR(VLOOKUP($F158,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H158" s="7">
-        <f>IFERROR(VLOOKUP($F158,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I158" s="7"/>
       <c r="J158" s="7">
-        <f>IFERROR(VLOOKUP($F158,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10048,16 +9906,16 @@
       </c>
       <c r="F159" s="7"/>
       <c r="G159" s="7">
-        <f>IFERROR(VLOOKUP($F159,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H159" s="7">
-        <f>IFERROR(VLOOKUP($F159,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I159" s="7"/>
       <c r="J159" s="7">
-        <f>IFERROR(VLOOKUP($F159,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10076,16 +9934,16 @@
       </c>
       <c r="F160" s="7"/>
       <c r="G160" s="7">
-        <f>IFERROR(VLOOKUP($F160,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H160" s="7">
-        <f>IFERROR(VLOOKUP($F160,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I160" s="7"/>
       <c r="J160" s="7">
-        <f>IFERROR(VLOOKUP($F160,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10104,16 +9962,16 @@
       </c>
       <c r="F161" s="7"/>
       <c r="G161" s="7">
-        <f>IFERROR(VLOOKUP($F161,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H161" s="7">
-        <f>IFERROR(VLOOKUP($F161,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I161" s="7"/>
       <c r="J161" s="7">
-        <f>IFERROR(VLOOKUP($F161,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10132,16 +9990,16 @@
       </c>
       <c r="F162" s="7"/>
       <c r="G162" s="7">
-        <f>IFERROR(VLOOKUP($F162,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H162" s="7">
-        <f>IFERROR(VLOOKUP($F162,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I162" s="7"/>
       <c r="J162" s="7">
-        <f>IFERROR(VLOOKUP($F162,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10160,16 +10018,16 @@
       </c>
       <c r="F163" s="7"/>
       <c r="G163" s="7">
-        <f>IFERROR(VLOOKUP($F163,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H163" s="7">
-        <f>IFERROR(VLOOKUP($F163,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I163" s="7"/>
       <c r="J163" s="7">
-        <f>IFERROR(VLOOKUP($F163,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10188,16 +10046,16 @@
       </c>
       <c r="F164" s="7"/>
       <c r="G164" s="7">
-        <f>IFERROR(VLOOKUP($F164,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H164" s="7">
-        <f>IFERROR(VLOOKUP($F164,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I164" s="7"/>
       <c r="J164" s="7">
-        <f>IFERROR(VLOOKUP($F164,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10216,16 +10074,16 @@
       </c>
       <c r="F165" s="7"/>
       <c r="G165" s="7">
-        <f>IFERROR(VLOOKUP($F165,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H165" s="7">
-        <f>IFERROR(VLOOKUP($F165,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I165" s="7"/>
       <c r="J165" s="7">
-        <f>IFERROR(VLOOKUP($F165,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10244,16 +10102,16 @@
       </c>
       <c r="F166" s="7"/>
       <c r="G166" s="7">
-        <f>IFERROR(VLOOKUP($F166,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H166" s="7">
-        <f>IFERROR(VLOOKUP($F166,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I166" s="7"/>
       <c r="J166" s="7">
-        <f>IFERROR(VLOOKUP($F166,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10272,16 +10130,16 @@
       </c>
       <c r="F167" s="7"/>
       <c r="G167" s="7">
-        <f>IFERROR(VLOOKUP($F167,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H167" s="7">
-        <f>IFERROR(VLOOKUP($F167,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I167" s="7"/>
       <c r="J167" s="7">
-        <f>IFERROR(VLOOKUP($F167,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10300,16 +10158,16 @@
       </c>
       <c r="F168" s="7"/>
       <c r="G168" s="7">
-        <f>IFERROR(VLOOKUP($F168,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H168" s="7">
-        <f>IFERROR(VLOOKUP($F168,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I168" s="7"/>
       <c r="J168" s="7">
-        <f>IFERROR(VLOOKUP($F168,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10328,16 +10186,16 @@
       </c>
       <c r="F169" s="7"/>
       <c r="G169" s="7">
-        <f>IFERROR(VLOOKUP($F169,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H169" s="7">
-        <f>IFERROR(VLOOKUP($F169,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I169" s="7"/>
       <c r="J169" s="7">
-        <f>IFERROR(VLOOKUP($F169,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10356,16 +10214,16 @@
       </c>
       <c r="F170" s="7"/>
       <c r="G170" s="7">
-        <f>IFERROR(VLOOKUP($F170,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H170" s="7">
-        <f>IFERROR(VLOOKUP($F170,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I170" s="7"/>
       <c r="J170" s="7">
-        <f>IFERROR(VLOOKUP($F170,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10384,16 +10242,16 @@
       </c>
       <c r="F171" s="7"/>
       <c r="G171" s="7">
-        <f>IFERROR(VLOOKUP($F171,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H171" s="7">
-        <f>IFERROR(VLOOKUP($F171,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I171" s="7"/>
       <c r="J171" s="7">
-        <f>IFERROR(VLOOKUP($F171,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10412,16 +10270,16 @@
       </c>
       <c r="F172" s="7"/>
       <c r="G172" s="7">
-        <f>IFERROR(VLOOKUP($F172,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H172" s="7">
-        <f>IFERROR(VLOOKUP($F172,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I172" s="7"/>
       <c r="J172" s="7">
-        <f>IFERROR(VLOOKUP($F172,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10440,16 +10298,16 @@
       </c>
       <c r="F173" s="7"/>
       <c r="G173" s="7">
-        <f>IFERROR(VLOOKUP($F173,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H173" s="7">
-        <f>IFERROR(VLOOKUP($F173,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I173" s="7"/>
       <c r="J173" s="7">
-        <f>IFERROR(VLOOKUP($F173,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10468,16 +10326,16 @@
       </c>
       <c r="F174" s="7"/>
       <c r="G174" s="7">
-        <f>IFERROR(VLOOKUP($F174,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H174" s="7">
-        <f>IFERROR(VLOOKUP($F174,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I174" s="7"/>
       <c r="J174" s="7">
-        <f>IFERROR(VLOOKUP($F174,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10496,16 +10354,16 @@
       </c>
       <c r="F175" s="7"/>
       <c r="G175" s="7">
-        <f>IFERROR(VLOOKUP($F175,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H175" s="7">
-        <f>IFERROR(VLOOKUP($F175,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I175" s="7"/>
       <c r="J175" s="7">
-        <f>IFERROR(VLOOKUP($F175,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10524,16 +10382,16 @@
       </c>
       <c r="F176" s="7"/>
       <c r="G176" s="7">
-        <f>IFERROR(VLOOKUP($F176,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H176" s="7">
-        <f>IFERROR(VLOOKUP($F176,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I176" s="7"/>
       <c r="J176" s="7">
-        <f>IFERROR(VLOOKUP($F176,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10552,16 +10410,16 @@
       </c>
       <c r="F177" s="7"/>
       <c r="G177" s="7">
-        <f>IFERROR(VLOOKUP($F177,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H177" s="7">
-        <f>IFERROR(VLOOKUP($F177,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I177" s="7"/>
       <c r="J177" s="7">
-        <f>IFERROR(VLOOKUP($F177,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10580,16 +10438,16 @@
       </c>
       <c r="F178" s="7"/>
       <c r="G178" s="7">
-        <f>IFERROR(VLOOKUP($F178,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H178" s="7">
-        <f>IFERROR(VLOOKUP($F178,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I178" s="7"/>
       <c r="J178" s="7">
-        <f>IFERROR(VLOOKUP($F178,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10608,16 +10466,16 @@
       </c>
       <c r="F179" s="7"/>
       <c r="G179" s="7">
-        <f>IFERROR(VLOOKUP($F179,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H179" s="7">
-        <f>IFERROR(VLOOKUP($F179,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I179" s="7"/>
       <c r="J179" s="7">
-        <f>IFERROR(VLOOKUP($F179,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10636,16 +10494,16 @@
       </c>
       <c r="F180" s="7"/>
       <c r="G180" s="7">
-        <f>IFERROR(VLOOKUP($F180,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H180" s="7">
-        <f>IFERROR(VLOOKUP($F180,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I180" s="7"/>
       <c r="J180" s="7">
-        <f>IFERROR(VLOOKUP($F180,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10664,16 +10522,16 @@
       </c>
       <c r="F181" s="7"/>
       <c r="G181" s="7">
-        <f>IFERROR(VLOOKUP($F181,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H181" s="7">
-        <f>IFERROR(VLOOKUP($F181,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I181" s="7"/>
       <c r="J181" s="7">
-        <f>IFERROR(VLOOKUP($F181,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10692,16 +10550,16 @@
       </c>
       <c r="F182" s="7"/>
       <c r="G182" s="7">
-        <f>IFERROR(VLOOKUP($F182,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H182" s="7">
-        <f>IFERROR(VLOOKUP($F182,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I182" s="7"/>
       <c r="J182" s="7">
-        <f>IFERROR(VLOOKUP($F182,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10720,16 +10578,16 @@
       </c>
       <c r="F183" s="7"/>
       <c r="G183" s="7">
-        <f>IFERROR(VLOOKUP($F183,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H183" s="7">
-        <f>IFERROR(VLOOKUP($F183,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I183" s="7"/>
       <c r="J183" s="7">
-        <f>IFERROR(VLOOKUP($F183,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10748,16 +10606,16 @@
       </c>
       <c r="F184" s="7"/>
       <c r="G184" s="7">
-        <f>IFERROR(VLOOKUP($F184,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H184" s="7">
-        <f>IFERROR(VLOOKUP($F184,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I184" s="7"/>
       <c r="J184" s="7">
-        <f>IFERROR(VLOOKUP($F184,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10776,16 +10634,16 @@
       </c>
       <c r="F185" s="7"/>
       <c r="G185" s="7">
-        <f>IFERROR(VLOOKUP($F185,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H185" s="7">
-        <f>IFERROR(VLOOKUP($F185,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I185" s="7"/>
       <c r="J185" s="7">
-        <f>IFERROR(VLOOKUP($F185,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10804,16 +10662,16 @@
       </c>
       <c r="F186" s="7"/>
       <c r="G186" s="7">
-        <f>IFERROR(VLOOKUP($F186,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H186" s="7">
-        <f>IFERROR(VLOOKUP($F186,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I186" s="7"/>
       <c r="J186" s="7">
-        <f>IFERROR(VLOOKUP($F186,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10832,16 +10690,16 @@
       </c>
       <c r="F187" s="7"/>
       <c r="G187" s="7">
-        <f>IFERROR(VLOOKUP($F187,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H187" s="7">
-        <f>IFERROR(VLOOKUP($F187,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I187" s="7"/>
       <c r="J187" s="7">
-        <f>IFERROR(VLOOKUP($F187,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10860,16 +10718,16 @@
       </c>
       <c r="F188" s="7"/>
       <c r="G188" s="7">
-        <f>IFERROR(VLOOKUP($F188,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H188" s="7">
-        <f>IFERROR(VLOOKUP($F188,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I188" s="7"/>
       <c r="J188" s="7">
-        <f>IFERROR(VLOOKUP($F188,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10888,16 +10746,16 @@
       </c>
       <c r="F189" s="7"/>
       <c r="G189" s="7">
-        <f>IFERROR(VLOOKUP($F189,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H189" s="7">
-        <f>IFERROR(VLOOKUP($F189,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I189" s="7"/>
       <c r="J189" s="7">
-        <f>IFERROR(VLOOKUP($F189,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10916,16 +10774,16 @@
       </c>
       <c r="F190" s="7"/>
       <c r="G190" s="7">
-        <f>IFERROR(VLOOKUP($F190,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H190" s="7">
-        <f>IFERROR(VLOOKUP($F190,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I190" s="7"/>
       <c r="J190" s="7">
-        <f>IFERROR(VLOOKUP($F190,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10944,16 +10802,16 @@
       </c>
       <c r="F191" s="7"/>
       <c r="G191" s="7">
-        <f>IFERROR(VLOOKUP($F191,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H191" s="7">
-        <f>IFERROR(VLOOKUP($F191,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I191" s="7"/>
       <c r="J191" s="7">
-        <f>IFERROR(VLOOKUP($F191,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -10972,16 +10830,16 @@
       </c>
       <c r="F192" s="7"/>
       <c r="G192" s="7">
-        <f>IFERROR(VLOOKUP($F192,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H192" s="7">
-        <f>IFERROR(VLOOKUP($F192,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I192" s="7"/>
       <c r="J192" s="7">
-        <f>IFERROR(VLOOKUP($F192,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -11000,16 +10858,16 @@
       </c>
       <c r="F193" s="7"/>
       <c r="G193" s="7">
-        <f>IFERROR(VLOOKUP($F193,$A:$B,2,0),0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H193" s="7">
-        <f>IFERROR(VLOOKUP($F193,$A:$D,3,0),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I193" s="7"/>
       <c r="J193" s="7">
-        <f>IFERROR(VLOOKUP($F193,$A:$D,4,0),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -11028,16 +10886,16 @@
       </c>
       <c r="F194" s="7"/>
       <c r="G194" s="7">
-        <f>IFERROR(VLOOKUP($F194,$A:$B,2,0),0)</f>
+        <f t="shared" ref="G194:G257" si="9">IFERROR(VLOOKUP($F194,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H194" s="7">
-        <f>IFERROR(VLOOKUP($F194,$A:$D,3,0),0)</f>
+        <f t="shared" ref="H194:H257" si="10">IFERROR(VLOOKUP($F194,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I194" s="7"/>
       <c r="J194" s="7">
-        <f>IFERROR(VLOOKUP($F194,$A:$D,4,0),0)</f>
+        <f t="shared" ref="J194:J257" si="11">IFERROR(VLOOKUP($F194,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -11056,16 +10914,16 @@
       </c>
       <c r="F195" s="7"/>
       <c r="G195" s="7">
-        <f>IFERROR(VLOOKUP($F195,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H195" s="7">
-        <f>IFERROR(VLOOKUP($F195,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I195" s="7"/>
       <c r="J195" s="7">
-        <f>IFERROR(VLOOKUP($F195,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11084,16 +10942,16 @@
       </c>
       <c r="F196" s="7"/>
       <c r="G196" s="7">
-        <f>IFERROR(VLOOKUP($F196,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H196" s="7">
-        <f>IFERROR(VLOOKUP($F196,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I196" s="7"/>
       <c r="J196" s="7">
-        <f>IFERROR(VLOOKUP($F196,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11112,16 +10970,16 @@
       </c>
       <c r="F197" s="7"/>
       <c r="G197" s="7">
-        <f>IFERROR(VLOOKUP($F197,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H197" s="7">
-        <f>IFERROR(VLOOKUP($F197,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I197" s="7"/>
       <c r="J197" s="7">
-        <f>IFERROR(VLOOKUP($F197,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11140,16 +10998,16 @@
       </c>
       <c r="F198" s="7"/>
       <c r="G198" s="7">
-        <f>IFERROR(VLOOKUP($F198,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H198" s="7">
-        <f>IFERROR(VLOOKUP($F198,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I198" s="7"/>
       <c r="J198" s="7">
-        <f>IFERROR(VLOOKUP($F198,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11168,16 +11026,16 @@
       </c>
       <c r="F199" s="7"/>
       <c r="G199" s="7">
-        <f>IFERROR(VLOOKUP($F199,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H199" s="7">
-        <f>IFERROR(VLOOKUP($F199,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I199" s="7"/>
       <c r="J199" s="7">
-        <f>IFERROR(VLOOKUP($F199,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11196,16 +11054,16 @@
       </c>
       <c r="F200" s="7"/>
       <c r="G200" s="7">
-        <f>IFERROR(VLOOKUP($F200,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H200" s="7">
-        <f>IFERROR(VLOOKUP($F200,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I200" s="7"/>
       <c r="J200" s="7">
-        <f>IFERROR(VLOOKUP($F200,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11224,16 +11082,16 @@
       </c>
       <c r="F201" s="7"/>
       <c r="G201" s="7">
-        <f>IFERROR(VLOOKUP($F201,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H201" s="7">
-        <f>IFERROR(VLOOKUP($F201,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I201" s="7"/>
       <c r="J201" s="7">
-        <f>IFERROR(VLOOKUP($F201,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11252,16 +11110,16 @@
       </c>
       <c r="F202" s="7"/>
       <c r="G202" s="7">
-        <f>IFERROR(VLOOKUP($F202,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H202" s="7">
-        <f>IFERROR(VLOOKUP($F202,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I202" s="7"/>
       <c r="J202" s="7">
-        <f>IFERROR(VLOOKUP($F202,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11280,16 +11138,16 @@
       </c>
       <c r="F203" s="7"/>
       <c r="G203" s="7">
-        <f>IFERROR(VLOOKUP($F203,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H203" s="7">
-        <f>IFERROR(VLOOKUP($F203,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I203" s="7"/>
       <c r="J203" s="7">
-        <f>IFERROR(VLOOKUP($F203,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11308,16 +11166,16 @@
       </c>
       <c r="F204" s="7"/>
       <c r="G204" s="7">
-        <f>IFERROR(VLOOKUP($F204,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H204" s="7">
-        <f>IFERROR(VLOOKUP($F204,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I204" s="7"/>
       <c r="J204" s="7">
-        <f>IFERROR(VLOOKUP($F204,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11336,16 +11194,16 @@
       </c>
       <c r="F205" s="7"/>
       <c r="G205" s="7">
-        <f>IFERROR(VLOOKUP($F205,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H205" s="7">
-        <f>IFERROR(VLOOKUP($F205,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I205" s="7"/>
       <c r="J205" s="7">
-        <f>IFERROR(VLOOKUP($F205,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11364,16 +11222,16 @@
       </c>
       <c r="F206" s="7"/>
       <c r="G206" s="7">
-        <f>IFERROR(VLOOKUP($F206,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H206" s="7">
-        <f>IFERROR(VLOOKUP($F206,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I206" s="7"/>
       <c r="J206" s="7">
-        <f>IFERROR(VLOOKUP($F206,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11392,16 +11250,16 @@
       </c>
       <c r="F207" s="7"/>
       <c r="G207" s="7">
-        <f>IFERROR(VLOOKUP($F207,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H207" s="7">
-        <f>IFERROR(VLOOKUP($F207,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I207" s="7"/>
       <c r="J207" s="7">
-        <f>IFERROR(VLOOKUP($F207,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11420,16 +11278,16 @@
       </c>
       <c r="F208" s="7"/>
       <c r="G208" s="7">
-        <f>IFERROR(VLOOKUP($F208,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H208" s="7">
-        <f>IFERROR(VLOOKUP($F208,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I208" s="7"/>
       <c r="J208" s="7">
-        <f>IFERROR(VLOOKUP($F208,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11448,16 +11306,16 @@
       </c>
       <c r="F209" s="7"/>
       <c r="G209" s="7">
-        <f>IFERROR(VLOOKUP($F209,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H209" s="7">
-        <f>IFERROR(VLOOKUP($F209,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I209" s="7"/>
       <c r="J209" s="7">
-        <f>IFERROR(VLOOKUP($F209,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11476,16 +11334,16 @@
       </c>
       <c r="F210" s="7"/>
       <c r="G210" s="7">
-        <f>IFERROR(VLOOKUP($F210,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H210" s="7">
-        <f>IFERROR(VLOOKUP($F210,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I210" s="7"/>
       <c r="J210" s="7">
-        <f>IFERROR(VLOOKUP($F210,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11504,16 +11362,16 @@
       </c>
       <c r="F211" s="7"/>
       <c r="G211" s="7">
-        <f>IFERROR(VLOOKUP($F211,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H211" s="7">
-        <f>IFERROR(VLOOKUP($F211,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I211" s="7"/>
       <c r="J211" s="7">
-        <f>IFERROR(VLOOKUP($F211,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11532,16 +11390,16 @@
       </c>
       <c r="F212" s="7"/>
       <c r="G212" s="7">
-        <f>IFERROR(VLOOKUP($F212,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H212" s="7">
-        <f>IFERROR(VLOOKUP($F212,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I212" s="7"/>
       <c r="J212" s="7">
-        <f>IFERROR(VLOOKUP($F212,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11560,16 +11418,16 @@
       </c>
       <c r="F213" s="7"/>
       <c r="G213" s="7">
-        <f>IFERROR(VLOOKUP($F213,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H213" s="7">
-        <f>IFERROR(VLOOKUP($F213,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I213" s="7"/>
       <c r="J213" s="7">
-        <f>IFERROR(VLOOKUP($F213,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11588,16 +11446,16 @@
       </c>
       <c r="F214" s="7"/>
       <c r="G214" s="7">
-        <f>IFERROR(VLOOKUP($F214,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H214" s="7">
-        <f>IFERROR(VLOOKUP($F214,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I214" s="7"/>
       <c r="J214" s="7">
-        <f>IFERROR(VLOOKUP($F214,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11616,16 +11474,16 @@
       </c>
       <c r="F215" s="7"/>
       <c r="G215" s="7">
-        <f>IFERROR(VLOOKUP($F215,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H215" s="7">
-        <f>IFERROR(VLOOKUP($F215,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I215" s="7"/>
       <c r="J215" s="7">
-        <f>IFERROR(VLOOKUP($F215,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11644,16 +11502,16 @@
       </c>
       <c r="F216" s="7"/>
       <c r="G216" s="7">
-        <f>IFERROR(VLOOKUP($F216,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H216" s="7">
-        <f>IFERROR(VLOOKUP($F216,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I216" s="7"/>
       <c r="J216" s="7">
-        <f>IFERROR(VLOOKUP($F216,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11672,16 +11530,16 @@
       </c>
       <c r="F217" s="7"/>
       <c r="G217" s="7">
-        <f>IFERROR(VLOOKUP($F217,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H217" s="7">
-        <f>IFERROR(VLOOKUP($F217,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I217" s="7"/>
       <c r="J217" s="7">
-        <f>IFERROR(VLOOKUP($F217,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11700,16 +11558,16 @@
       </c>
       <c r="F218" s="7"/>
       <c r="G218" s="7">
-        <f>IFERROR(VLOOKUP($F218,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H218" s="7">
-        <f>IFERROR(VLOOKUP($F218,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I218" s="7"/>
       <c r="J218" s="7">
-        <f>IFERROR(VLOOKUP($F218,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11728,16 +11586,16 @@
       </c>
       <c r="F219" s="7"/>
       <c r="G219" s="7">
-        <f>IFERROR(VLOOKUP($F219,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H219" s="7">
-        <f>IFERROR(VLOOKUP($F219,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I219" s="7"/>
       <c r="J219" s="7">
-        <f>IFERROR(VLOOKUP($F219,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11756,16 +11614,16 @@
       </c>
       <c r="F220" s="7"/>
       <c r="G220" s="7">
-        <f>IFERROR(VLOOKUP($F220,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H220" s="7">
-        <f>IFERROR(VLOOKUP($F220,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I220" s="7"/>
       <c r="J220" s="7">
-        <f>IFERROR(VLOOKUP($F220,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11784,16 +11642,16 @@
       </c>
       <c r="F221" s="7"/>
       <c r="G221" s="7">
-        <f>IFERROR(VLOOKUP($F221,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H221" s="7">
-        <f>IFERROR(VLOOKUP($F221,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I221" s="7"/>
       <c r="J221" s="7">
-        <f>IFERROR(VLOOKUP($F221,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11812,16 +11670,16 @@
       </c>
       <c r="F222" s="7"/>
       <c r="G222" s="7">
-        <f>IFERROR(VLOOKUP($F222,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H222" s="7">
-        <f>IFERROR(VLOOKUP($F222,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I222" s="7"/>
       <c r="J222" s="7">
-        <f>IFERROR(VLOOKUP($F222,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11840,16 +11698,16 @@
       </c>
       <c r="F223" s="7"/>
       <c r="G223" s="7">
-        <f>IFERROR(VLOOKUP($F223,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H223" s="7">
-        <f>IFERROR(VLOOKUP($F223,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I223" s="7"/>
       <c r="J223" s="7">
-        <f>IFERROR(VLOOKUP($F223,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11868,16 +11726,16 @@
       </c>
       <c r="F224" s="7"/>
       <c r="G224" s="7">
-        <f>IFERROR(VLOOKUP($F224,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H224" s="7">
-        <f>IFERROR(VLOOKUP($F224,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I224" s="7"/>
       <c r="J224" s="7">
-        <f>IFERROR(VLOOKUP($F224,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11896,16 +11754,16 @@
       </c>
       <c r="F225" s="7"/>
       <c r="G225" s="7">
-        <f>IFERROR(VLOOKUP($F225,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H225" s="7">
-        <f>IFERROR(VLOOKUP($F225,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I225" s="7"/>
       <c r="J225" s="7">
-        <f>IFERROR(VLOOKUP($F225,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11924,16 +11782,16 @@
       </c>
       <c r="F226" s="7"/>
       <c r="G226" s="7">
-        <f>IFERROR(VLOOKUP($F226,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H226" s="7">
-        <f>IFERROR(VLOOKUP($F226,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I226" s="7"/>
       <c r="J226" s="7">
-        <f>IFERROR(VLOOKUP($F226,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11952,16 +11810,16 @@
       </c>
       <c r="F227" s="7"/>
       <c r="G227" s="7">
-        <f>IFERROR(VLOOKUP($F227,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H227" s="7">
-        <f>IFERROR(VLOOKUP($F227,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I227" s="7"/>
       <c r="J227" s="7">
-        <f>IFERROR(VLOOKUP($F227,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -11980,16 +11838,16 @@
       </c>
       <c r="F228" s="7"/>
       <c r="G228" s="7">
-        <f>IFERROR(VLOOKUP($F228,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H228" s="7">
-        <f>IFERROR(VLOOKUP($F228,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I228" s="7"/>
       <c r="J228" s="7">
-        <f>IFERROR(VLOOKUP($F228,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12008,16 +11866,16 @@
       </c>
       <c r="F229" s="7"/>
       <c r="G229" s="7">
-        <f>IFERROR(VLOOKUP($F229,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H229" s="7">
-        <f>IFERROR(VLOOKUP($F229,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I229" s="7"/>
       <c r="J229" s="7">
-        <f>IFERROR(VLOOKUP($F229,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12036,16 +11894,16 @@
       </c>
       <c r="F230" s="7"/>
       <c r="G230" s="7">
-        <f>IFERROR(VLOOKUP($F230,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H230" s="7">
-        <f>IFERROR(VLOOKUP($F230,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I230" s="7"/>
       <c r="J230" s="7">
-        <f>IFERROR(VLOOKUP($F230,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12064,16 +11922,16 @@
       </c>
       <c r="F231" s="7"/>
       <c r="G231" s="7">
-        <f>IFERROR(VLOOKUP($F231,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H231" s="7">
-        <f>IFERROR(VLOOKUP($F231,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I231" s="7"/>
       <c r="J231" s="7">
-        <f>IFERROR(VLOOKUP($F231,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12092,16 +11950,16 @@
       </c>
       <c r="F232" s="7"/>
       <c r="G232" s="7">
-        <f>IFERROR(VLOOKUP($F232,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H232" s="7">
-        <f>IFERROR(VLOOKUP($F232,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I232" s="7"/>
       <c r="J232" s="7">
-        <f>IFERROR(VLOOKUP($F232,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12120,16 +11978,16 @@
       </c>
       <c r="F233" s="7"/>
       <c r="G233" s="7">
-        <f>IFERROR(VLOOKUP($F233,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H233" s="7">
-        <f>IFERROR(VLOOKUP($F233,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I233" s="7"/>
       <c r="J233" s="7">
-        <f>IFERROR(VLOOKUP($F233,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12148,16 +12006,16 @@
       </c>
       <c r="F234" s="7"/>
       <c r="G234" s="7">
-        <f>IFERROR(VLOOKUP($F234,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H234" s="7">
-        <f>IFERROR(VLOOKUP($F234,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I234" s="7"/>
       <c r="J234" s="7">
-        <f>IFERROR(VLOOKUP($F234,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12176,16 +12034,16 @@
       </c>
       <c r="F235" s="7"/>
       <c r="G235" s="7">
-        <f>IFERROR(VLOOKUP($F235,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H235" s="7">
-        <f>IFERROR(VLOOKUP($F235,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I235" s="7"/>
       <c r="J235" s="7">
-        <f>IFERROR(VLOOKUP($F235,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12204,16 +12062,16 @@
       </c>
       <c r="F236" s="7"/>
       <c r="G236" s="7">
-        <f>IFERROR(VLOOKUP($F236,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H236" s="7">
-        <f>IFERROR(VLOOKUP($F236,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I236" s="7"/>
       <c r="J236" s="7">
-        <f>IFERROR(VLOOKUP($F236,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12232,16 +12090,16 @@
       </c>
       <c r="F237" s="7"/>
       <c r="G237" s="7">
-        <f>IFERROR(VLOOKUP($F237,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H237" s="7">
-        <f>IFERROR(VLOOKUP($F237,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I237" s="7"/>
       <c r="J237" s="7">
-        <f>IFERROR(VLOOKUP($F237,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12260,16 +12118,16 @@
       </c>
       <c r="F238" s="7"/>
       <c r="G238" s="7">
-        <f>IFERROR(VLOOKUP($F238,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H238" s="7">
-        <f>IFERROR(VLOOKUP($F238,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I238" s="7"/>
       <c r="J238" s="7">
-        <f>IFERROR(VLOOKUP($F238,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12288,16 +12146,16 @@
       </c>
       <c r="F239" s="7"/>
       <c r="G239" s="7">
-        <f>IFERROR(VLOOKUP($F239,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H239" s="7">
-        <f>IFERROR(VLOOKUP($F239,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I239" s="7"/>
       <c r="J239" s="7">
-        <f>IFERROR(VLOOKUP($F239,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12316,16 +12174,16 @@
       </c>
       <c r="F240" s="7"/>
       <c r="G240" s="7">
-        <f>IFERROR(VLOOKUP($F240,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H240" s="7">
-        <f>IFERROR(VLOOKUP($F240,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I240" s="7"/>
       <c r="J240" s="7">
-        <f>IFERROR(VLOOKUP($F240,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12344,16 +12202,16 @@
       </c>
       <c r="F241" s="7"/>
       <c r="G241" s="7">
-        <f>IFERROR(VLOOKUP($F241,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H241" s="7">
-        <f>IFERROR(VLOOKUP($F241,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I241" s="7"/>
       <c r="J241" s="7">
-        <f>IFERROR(VLOOKUP($F241,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12372,16 +12230,16 @@
       </c>
       <c r="F242" s="7"/>
       <c r="G242" s="7">
-        <f>IFERROR(VLOOKUP($F242,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H242" s="7">
-        <f>IFERROR(VLOOKUP($F242,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I242" s="7"/>
       <c r="J242" s="7">
-        <f>IFERROR(VLOOKUP($F242,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12400,16 +12258,16 @@
       </c>
       <c r="F243" s="7"/>
       <c r="G243" s="7">
-        <f>IFERROR(VLOOKUP($F243,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H243" s="7">
-        <f>IFERROR(VLOOKUP($F243,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I243" s="7"/>
       <c r="J243" s="7">
-        <f>IFERROR(VLOOKUP($F243,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12428,16 +12286,16 @@
       </c>
       <c r="F244" s="7"/>
       <c r="G244" s="7">
-        <f>IFERROR(VLOOKUP($F244,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H244" s="7">
-        <f>IFERROR(VLOOKUP($F244,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I244" s="7"/>
       <c r="J244" s="7">
-        <f>IFERROR(VLOOKUP($F244,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12456,16 +12314,16 @@
       </c>
       <c r="F245" s="7"/>
       <c r="G245" s="7">
-        <f>IFERROR(VLOOKUP($F245,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H245" s="7">
-        <f>IFERROR(VLOOKUP($F245,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I245" s="7"/>
       <c r="J245" s="7">
-        <f>IFERROR(VLOOKUP($F245,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12484,16 +12342,16 @@
       </c>
       <c r="F246" s="7"/>
       <c r="G246" s="7">
-        <f>IFERROR(VLOOKUP($F246,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H246" s="7">
-        <f>IFERROR(VLOOKUP($F246,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I246" s="7"/>
       <c r="J246" s="7">
-        <f>IFERROR(VLOOKUP($F246,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12512,16 +12370,16 @@
       </c>
       <c r="F247" s="7"/>
       <c r="G247" s="7">
-        <f>IFERROR(VLOOKUP($F247,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H247" s="7">
-        <f>IFERROR(VLOOKUP($F247,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I247" s="7"/>
       <c r="J247" s="7">
-        <f>IFERROR(VLOOKUP($F247,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12540,16 +12398,16 @@
       </c>
       <c r="F248" s="7"/>
       <c r="G248" s="7">
-        <f>IFERROR(VLOOKUP($F248,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H248" s="7">
-        <f>IFERROR(VLOOKUP($F248,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I248" s="7"/>
       <c r="J248" s="7">
-        <f>IFERROR(VLOOKUP($F248,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12568,16 +12426,16 @@
       </c>
       <c r="F249" s="7"/>
       <c r="G249" s="7">
-        <f>IFERROR(VLOOKUP($F249,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H249" s="7">
-        <f>IFERROR(VLOOKUP($F249,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I249" s="7"/>
       <c r="J249" s="7">
-        <f>IFERROR(VLOOKUP($F249,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12596,16 +12454,16 @@
       </c>
       <c r="F250" s="7"/>
       <c r="G250" s="7">
-        <f>IFERROR(VLOOKUP($F250,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H250" s="7">
-        <f>IFERROR(VLOOKUP($F250,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I250" s="7"/>
       <c r="J250" s="7">
-        <f>IFERROR(VLOOKUP($F250,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12624,16 +12482,16 @@
       </c>
       <c r="F251" s="7"/>
       <c r="G251" s="7">
-        <f>IFERROR(VLOOKUP($F251,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H251" s="7">
-        <f>IFERROR(VLOOKUP($F251,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I251" s="7"/>
       <c r="J251" s="7">
-        <f>IFERROR(VLOOKUP($F251,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12652,16 +12510,16 @@
       </c>
       <c r="F252" s="7"/>
       <c r="G252" s="7">
-        <f>IFERROR(VLOOKUP($F252,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H252" s="7">
-        <f>IFERROR(VLOOKUP($F252,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I252" s="7"/>
       <c r="J252" s="7">
-        <f>IFERROR(VLOOKUP($F252,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12680,16 +12538,16 @@
       </c>
       <c r="F253" s="7"/>
       <c r="G253" s="7">
-        <f>IFERROR(VLOOKUP($F253,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H253" s="7">
-        <f>IFERROR(VLOOKUP($F253,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I253" s="7"/>
       <c r="J253" s="7">
-        <f>IFERROR(VLOOKUP($F253,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12708,16 +12566,16 @@
       </c>
       <c r="F254" s="7"/>
       <c r="G254" s="7">
-        <f>IFERROR(VLOOKUP($F254,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H254" s="7">
-        <f>IFERROR(VLOOKUP($F254,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I254" s="7"/>
       <c r="J254" s="7">
-        <f>IFERROR(VLOOKUP($F254,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12736,16 +12594,16 @@
       </c>
       <c r="F255" s="7"/>
       <c r="G255" s="7">
-        <f>IFERROR(VLOOKUP($F255,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H255" s="7">
-        <f>IFERROR(VLOOKUP($F255,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I255" s="7"/>
       <c r="J255" s="7">
-        <f>IFERROR(VLOOKUP($F255,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12764,16 +12622,16 @@
       </c>
       <c r="F256" s="7"/>
       <c r="G256" s="7">
-        <f>IFERROR(VLOOKUP($F256,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H256" s="7">
-        <f>IFERROR(VLOOKUP($F256,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I256" s="7"/>
       <c r="J256" s="7">
-        <f>IFERROR(VLOOKUP($F256,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12792,16 +12650,16 @@
       </c>
       <c r="F257" s="40"/>
       <c r="G257" s="40">
-        <f>IFERROR(VLOOKUP($F257,$A:$B,2,0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H257" s="40">
-        <f>IFERROR(VLOOKUP($F257,$A:$D,3,0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I257" s="40"/>
       <c r="J257" s="40">
-        <f>IFERROR(VLOOKUP($F257,$A:$D,4,0),0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12820,16 +12678,16 @@
       </c>
       <c r="F258" s="7"/>
       <c r="G258" s="7">
-        <f>IFERROR(VLOOKUP($F258,$A:$B,2,0),0)</f>
+        <f t="shared" ref="G258:G321" si="12">IFERROR(VLOOKUP($F258,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H258" s="7">
-        <f>IFERROR(VLOOKUP($F258,$A:$D,3,0),0)</f>
+        <f t="shared" ref="H258:H321" si="13">IFERROR(VLOOKUP($F258,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I258" s="7"/>
       <c r="J258" s="7">
-        <f>IFERROR(VLOOKUP($F258,$A:$D,4,0),0)</f>
+        <f t="shared" ref="J258:J321" si="14">IFERROR(VLOOKUP($F258,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -12848,16 +12706,16 @@
       </c>
       <c r="F259" s="7"/>
       <c r="G259" s="7">
-        <f>IFERROR(VLOOKUP($F259,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H259" s="7">
-        <f>IFERROR(VLOOKUP($F259,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I259" s="7"/>
       <c r="J259" s="7">
-        <f>IFERROR(VLOOKUP($F259,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -12876,16 +12734,16 @@
       </c>
       <c r="F260" s="7"/>
       <c r="G260" s="7">
-        <f>IFERROR(VLOOKUP($F260,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H260" s="7">
-        <f>IFERROR(VLOOKUP($F260,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I260" s="7"/>
       <c r="J260" s="7">
-        <f>IFERROR(VLOOKUP($F260,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -12904,16 +12762,16 @@
       </c>
       <c r="F261" s="7"/>
       <c r="G261" s="7">
-        <f>IFERROR(VLOOKUP($F261,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H261" s="7">
-        <f>IFERROR(VLOOKUP($F261,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I261" s="7"/>
       <c r="J261" s="7">
-        <f>IFERROR(VLOOKUP($F261,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -12932,16 +12790,16 @@
       </c>
       <c r="F262" s="7"/>
       <c r="G262" s="7">
-        <f>IFERROR(VLOOKUP($F262,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H262" s="7">
-        <f>IFERROR(VLOOKUP($F262,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I262" s="7"/>
       <c r="J262" s="7">
-        <f>IFERROR(VLOOKUP($F262,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -12960,16 +12818,16 @@
       </c>
       <c r="F263" s="7"/>
       <c r="G263" s="7">
-        <f>IFERROR(VLOOKUP($F263,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H263" s="7">
-        <f>IFERROR(VLOOKUP($F263,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I263" s="7"/>
       <c r="J263" s="7">
-        <f>IFERROR(VLOOKUP($F263,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -12988,16 +12846,16 @@
       </c>
       <c r="F264" s="7"/>
       <c r="G264" s="7">
-        <f>IFERROR(VLOOKUP($F264,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H264" s="7">
-        <f>IFERROR(VLOOKUP($F264,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I264" s="7"/>
       <c r="J264" s="7">
-        <f>IFERROR(VLOOKUP($F264,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13016,16 +12874,16 @@
       </c>
       <c r="F265" s="7"/>
       <c r="G265" s="7">
-        <f>IFERROR(VLOOKUP($F265,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H265" s="7">
-        <f>IFERROR(VLOOKUP($F265,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I265" s="7"/>
       <c r="J265" s="7">
-        <f>IFERROR(VLOOKUP($F265,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13044,16 +12902,16 @@
       </c>
       <c r="F266" s="7"/>
       <c r="G266" s="7">
-        <f>IFERROR(VLOOKUP($F266,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H266" s="7">
-        <f>IFERROR(VLOOKUP($F266,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I266" s="7"/>
       <c r="J266" s="7">
-        <f>IFERROR(VLOOKUP($F266,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13072,16 +12930,16 @@
       </c>
       <c r="F267" s="7"/>
       <c r="G267" s="7">
-        <f>IFERROR(VLOOKUP($F267,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H267" s="7">
-        <f>IFERROR(VLOOKUP($F267,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7">
-        <f>IFERROR(VLOOKUP($F267,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13100,16 +12958,16 @@
       </c>
       <c r="F268" s="7"/>
       <c r="G268" s="7">
-        <f>IFERROR(VLOOKUP($F268,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H268" s="7">
-        <f>IFERROR(VLOOKUP($F268,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I268" s="7"/>
       <c r="J268" s="7">
-        <f>IFERROR(VLOOKUP($F268,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13128,16 +12986,16 @@
       </c>
       <c r="F269" s="7"/>
       <c r="G269" s="7">
-        <f>IFERROR(VLOOKUP($F269,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H269" s="7">
-        <f>IFERROR(VLOOKUP($F269,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I269" s="7"/>
       <c r="J269" s="7">
-        <f>IFERROR(VLOOKUP($F269,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13156,16 +13014,16 @@
       </c>
       <c r="F270" s="7"/>
       <c r="G270" s="7">
-        <f>IFERROR(VLOOKUP($F270,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H270" s="7">
-        <f>IFERROR(VLOOKUP($F270,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I270" s="7"/>
       <c r="J270" s="7">
-        <f>IFERROR(VLOOKUP($F270,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13184,16 +13042,16 @@
       </c>
       <c r="F271" s="7"/>
       <c r="G271" s="7">
-        <f>IFERROR(VLOOKUP($F271,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H271" s="7">
-        <f>IFERROR(VLOOKUP($F271,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I271" s="7"/>
       <c r="J271" s="7">
-        <f>IFERROR(VLOOKUP($F271,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13212,16 +13070,16 @@
       </c>
       <c r="F272" s="7"/>
       <c r="G272" s="7">
-        <f>IFERROR(VLOOKUP($F272,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H272" s="7">
-        <f>IFERROR(VLOOKUP($F272,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I272" s="7"/>
       <c r="J272" s="7">
-        <f>IFERROR(VLOOKUP($F272,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13240,16 +13098,16 @@
       </c>
       <c r="F273" s="7"/>
       <c r="G273" s="7">
-        <f>IFERROR(VLOOKUP($F273,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H273" s="7">
-        <f>IFERROR(VLOOKUP($F273,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I273" s="7"/>
       <c r="J273" s="7">
-        <f>IFERROR(VLOOKUP($F273,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13268,16 +13126,16 @@
       </c>
       <c r="F274" s="7"/>
       <c r="G274" s="7">
-        <f>IFERROR(VLOOKUP($F274,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H274" s="7">
-        <f>IFERROR(VLOOKUP($F274,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I274" s="7"/>
       <c r="J274" s="7">
-        <f>IFERROR(VLOOKUP($F274,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13296,16 +13154,16 @@
       </c>
       <c r="F275" s="7"/>
       <c r="G275" s="7">
-        <f>IFERROR(VLOOKUP($F275,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H275" s="7">
-        <f>IFERROR(VLOOKUP($F275,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I275" s="7"/>
       <c r="J275" s="7">
-        <f>IFERROR(VLOOKUP($F275,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13324,16 +13182,16 @@
       </c>
       <c r="F276" s="7"/>
       <c r="G276" s="7">
-        <f>IFERROR(VLOOKUP($F276,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H276" s="7">
-        <f>IFERROR(VLOOKUP($F276,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I276" s="7"/>
       <c r="J276" s="7">
-        <f>IFERROR(VLOOKUP($F276,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13352,16 +13210,16 @@
       </c>
       <c r="F277" s="7"/>
       <c r="G277" s="7">
-        <f>IFERROR(VLOOKUP($F277,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H277" s="7">
-        <f>IFERROR(VLOOKUP($F277,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I277" s="7"/>
       <c r="J277" s="7">
-        <f>IFERROR(VLOOKUP($F277,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13380,16 +13238,16 @@
       </c>
       <c r="F278" s="7"/>
       <c r="G278" s="7">
-        <f>IFERROR(VLOOKUP($F278,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H278" s="7">
-        <f>IFERROR(VLOOKUP($F278,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I278" s="7"/>
       <c r="J278" s="7">
-        <f>IFERROR(VLOOKUP($F278,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13408,16 +13266,16 @@
       </c>
       <c r="F279" s="7"/>
       <c r="G279" s="7">
-        <f>IFERROR(VLOOKUP($F279,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H279" s="7">
-        <f>IFERROR(VLOOKUP($F279,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I279" s="7"/>
       <c r="J279" s="7">
-        <f>IFERROR(VLOOKUP($F279,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13436,16 +13294,16 @@
       </c>
       <c r="F280" s="7"/>
       <c r="G280" s="7">
-        <f>IFERROR(VLOOKUP($F280,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H280" s="7">
-        <f>IFERROR(VLOOKUP($F280,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I280" s="7"/>
       <c r="J280" s="7">
-        <f>IFERROR(VLOOKUP($F280,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13464,16 +13322,16 @@
       </c>
       <c r="F281" s="7"/>
       <c r="G281" s="7">
-        <f>IFERROR(VLOOKUP($F281,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H281" s="7">
-        <f>IFERROR(VLOOKUP($F281,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I281" s="7"/>
       <c r="J281" s="7">
-        <f>IFERROR(VLOOKUP($F281,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13492,16 +13350,16 @@
       </c>
       <c r="F282" s="7"/>
       <c r="G282" s="7">
-        <f>IFERROR(VLOOKUP($F282,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H282" s="7">
-        <f>IFERROR(VLOOKUP($F282,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I282" s="7"/>
       <c r="J282" s="7">
-        <f>IFERROR(VLOOKUP($F282,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13520,16 +13378,16 @@
       </c>
       <c r="F283" s="7"/>
       <c r="G283" s="7">
-        <f>IFERROR(VLOOKUP($F283,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H283" s="7">
-        <f>IFERROR(VLOOKUP($F283,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I283" s="7"/>
       <c r="J283" s="7">
-        <f>IFERROR(VLOOKUP($F283,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13548,16 +13406,16 @@
       </c>
       <c r="F284" s="7"/>
       <c r="G284" s="7">
-        <f>IFERROR(VLOOKUP($F284,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H284" s="7">
-        <f>IFERROR(VLOOKUP($F284,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I284" s="7"/>
       <c r="J284" s="7">
-        <f>IFERROR(VLOOKUP($F284,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13576,16 +13434,16 @@
       </c>
       <c r="F285" s="7"/>
       <c r="G285" s="7">
-        <f>IFERROR(VLOOKUP($F285,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H285" s="7">
-        <f>IFERROR(VLOOKUP($F285,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I285" s="7"/>
       <c r="J285" s="7">
-        <f>IFERROR(VLOOKUP($F285,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13604,16 +13462,16 @@
       </c>
       <c r="F286" s="7"/>
       <c r="G286" s="7">
-        <f>IFERROR(VLOOKUP($F286,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H286" s="7">
-        <f>IFERROR(VLOOKUP($F286,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I286" s="7"/>
       <c r="J286" s="7">
-        <f>IFERROR(VLOOKUP($F286,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13632,16 +13490,16 @@
       </c>
       <c r="F287" s="7"/>
       <c r="G287" s="7">
-        <f>IFERROR(VLOOKUP($F287,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H287" s="7">
-        <f>IFERROR(VLOOKUP($F287,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I287" s="7"/>
       <c r="J287" s="7">
-        <f>IFERROR(VLOOKUP($F287,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13660,16 +13518,16 @@
       </c>
       <c r="F288" s="7"/>
       <c r="G288" s="7">
-        <f>IFERROR(VLOOKUP($F288,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H288" s="7">
-        <f>IFERROR(VLOOKUP($F288,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I288" s="7"/>
       <c r="J288" s="7">
-        <f>IFERROR(VLOOKUP($F288,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13688,16 +13546,16 @@
       </c>
       <c r="F289" s="7"/>
       <c r="G289" s="7">
-        <f>IFERROR(VLOOKUP($F289,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H289" s="7">
-        <f>IFERROR(VLOOKUP($F289,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I289" s="7"/>
       <c r="J289" s="7">
-        <f>IFERROR(VLOOKUP($F289,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13716,16 +13574,16 @@
       </c>
       <c r="F290" s="7"/>
       <c r="G290" s="7">
-        <f>IFERROR(VLOOKUP($F290,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H290" s="7">
-        <f>IFERROR(VLOOKUP($F290,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I290" s="7"/>
       <c r="J290" s="7">
-        <f>IFERROR(VLOOKUP($F290,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13744,16 +13602,16 @@
       </c>
       <c r="F291" s="7"/>
       <c r="G291" s="7">
-        <f>IFERROR(VLOOKUP($F291,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H291" s="7">
-        <f>IFERROR(VLOOKUP($F291,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I291" s="7"/>
       <c r="J291" s="7">
-        <f>IFERROR(VLOOKUP($F291,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13772,16 +13630,16 @@
       </c>
       <c r="F292" s="7"/>
       <c r="G292" s="7">
-        <f>IFERROR(VLOOKUP($F292,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H292" s="7">
-        <f>IFERROR(VLOOKUP($F292,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I292" s="7"/>
       <c r="J292" s="7">
-        <f>IFERROR(VLOOKUP($F292,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13800,16 +13658,16 @@
       </c>
       <c r="F293" s="7"/>
       <c r="G293" s="7">
-        <f>IFERROR(VLOOKUP($F293,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H293" s="7">
-        <f>IFERROR(VLOOKUP($F293,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I293" s="7"/>
       <c r="J293" s="7">
-        <f>IFERROR(VLOOKUP($F293,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13828,16 +13686,16 @@
       </c>
       <c r="F294" s="7"/>
       <c r="G294" s="7">
-        <f>IFERROR(VLOOKUP($F294,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H294" s="7">
-        <f>IFERROR(VLOOKUP($F294,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I294" s="7"/>
       <c r="J294" s="7">
-        <f>IFERROR(VLOOKUP($F294,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13856,16 +13714,16 @@
       </c>
       <c r="F295" s="7"/>
       <c r="G295" s="7">
-        <f>IFERROR(VLOOKUP($F295,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H295" s="7">
-        <f>IFERROR(VLOOKUP($F295,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I295" s="7"/>
       <c r="J295" s="7">
-        <f>IFERROR(VLOOKUP($F295,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13884,16 +13742,16 @@
       </c>
       <c r="F296" s="7"/>
       <c r="G296" s="7">
-        <f>IFERROR(VLOOKUP($F296,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H296" s="7">
-        <f>IFERROR(VLOOKUP($F296,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I296" s="7"/>
       <c r="J296" s="7">
-        <f>IFERROR(VLOOKUP($F296,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13912,16 +13770,16 @@
       </c>
       <c r="F297" s="7"/>
       <c r="G297" s="7">
-        <f>IFERROR(VLOOKUP($F297,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H297" s="7">
-        <f>IFERROR(VLOOKUP($F297,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I297" s="7"/>
       <c r="J297" s="7">
-        <f>IFERROR(VLOOKUP($F297,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13940,16 +13798,16 @@
       </c>
       <c r="F298" s="7"/>
       <c r="G298" s="7">
-        <f>IFERROR(VLOOKUP($F298,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H298" s="7">
-        <f>IFERROR(VLOOKUP($F298,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I298" s="7"/>
       <c r="J298" s="7">
-        <f>IFERROR(VLOOKUP($F298,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13968,16 +13826,16 @@
       </c>
       <c r="F299" s="7"/>
       <c r="G299" s="7">
-        <f>IFERROR(VLOOKUP($F299,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H299" s="7">
-        <f>IFERROR(VLOOKUP($F299,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I299" s="7"/>
       <c r="J299" s="7">
-        <f>IFERROR(VLOOKUP($F299,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -13996,16 +13854,16 @@
       </c>
       <c r="F300" s="7"/>
       <c r="G300" s="7">
-        <f>IFERROR(VLOOKUP($F300,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H300" s="7">
-        <f>IFERROR(VLOOKUP($F300,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I300" s="7"/>
       <c r="J300" s="7">
-        <f>IFERROR(VLOOKUP($F300,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14024,16 +13882,16 @@
       </c>
       <c r="F301" s="7"/>
       <c r="G301" s="7">
-        <f>IFERROR(VLOOKUP($F301,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H301" s="7">
-        <f>IFERROR(VLOOKUP($F301,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I301" s="7"/>
       <c r="J301" s="7">
-        <f>IFERROR(VLOOKUP($F301,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14052,16 +13910,16 @@
       </c>
       <c r="F302" s="7"/>
       <c r="G302" s="7">
-        <f>IFERROR(VLOOKUP($F302,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H302" s="7">
-        <f>IFERROR(VLOOKUP($F302,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I302" s="7"/>
       <c r="J302" s="7">
-        <f>IFERROR(VLOOKUP($F302,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14080,16 +13938,16 @@
       </c>
       <c r="F303" s="7"/>
       <c r="G303" s="7">
-        <f>IFERROR(VLOOKUP($F303,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H303" s="7">
-        <f>IFERROR(VLOOKUP($F303,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I303" s="7"/>
       <c r="J303" s="7">
-        <f>IFERROR(VLOOKUP($F303,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14108,16 +13966,16 @@
       </c>
       <c r="F304" s="7"/>
       <c r="G304" s="7">
-        <f>IFERROR(VLOOKUP($F304,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H304" s="7">
-        <f>IFERROR(VLOOKUP($F304,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I304" s="7"/>
       <c r="J304" s="7">
-        <f>IFERROR(VLOOKUP($F304,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14136,16 +13994,16 @@
       </c>
       <c r="F305" s="7"/>
       <c r="G305" s="7">
-        <f>IFERROR(VLOOKUP($F305,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H305" s="7">
-        <f>IFERROR(VLOOKUP($F305,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I305" s="7"/>
       <c r="J305" s="7">
-        <f>IFERROR(VLOOKUP($F305,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14164,16 +14022,16 @@
       </c>
       <c r="F306" s="7"/>
       <c r="G306" s="7">
-        <f>IFERROR(VLOOKUP($F306,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H306" s="7">
-        <f>IFERROR(VLOOKUP($F306,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I306" s="7"/>
       <c r="J306" s="7">
-        <f>IFERROR(VLOOKUP($F306,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14192,16 +14050,16 @@
       </c>
       <c r="F307" s="7"/>
       <c r="G307" s="7">
-        <f>IFERROR(VLOOKUP($F307,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H307" s="7">
-        <f>IFERROR(VLOOKUP($F307,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I307" s="7"/>
       <c r="J307" s="7">
-        <f>IFERROR(VLOOKUP($F307,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14220,16 +14078,16 @@
       </c>
       <c r="F308" s="7"/>
       <c r="G308" s="7">
-        <f>IFERROR(VLOOKUP($F308,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H308" s="7">
-        <f>IFERROR(VLOOKUP($F308,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I308" s="7"/>
       <c r="J308" s="7">
-        <f>IFERROR(VLOOKUP($F308,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14248,16 +14106,16 @@
       </c>
       <c r="F309" s="7"/>
       <c r="G309" s="7">
-        <f>IFERROR(VLOOKUP($F309,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H309" s="7">
-        <f>IFERROR(VLOOKUP($F309,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I309" s="7"/>
       <c r="J309" s="7">
-        <f>IFERROR(VLOOKUP($F309,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14276,16 +14134,16 @@
       </c>
       <c r="F310" s="7"/>
       <c r="G310" s="7">
-        <f>IFERROR(VLOOKUP($F310,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H310" s="7">
-        <f>IFERROR(VLOOKUP($F310,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I310" s="7"/>
       <c r="J310" s="7">
-        <f>IFERROR(VLOOKUP($F310,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14304,16 +14162,16 @@
       </c>
       <c r="F311" s="7"/>
       <c r="G311" s="7">
-        <f>IFERROR(VLOOKUP($F311,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H311" s="7">
-        <f>IFERROR(VLOOKUP($F311,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I311" s="7"/>
       <c r="J311" s="7">
-        <f>IFERROR(VLOOKUP($F311,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14332,16 +14190,16 @@
       </c>
       <c r="F312" s="7"/>
       <c r="G312" s="7">
-        <f>IFERROR(VLOOKUP($F312,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H312" s="7">
-        <f>IFERROR(VLOOKUP($F312,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I312" s="7"/>
       <c r="J312" s="7">
-        <f>IFERROR(VLOOKUP($F312,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14360,16 +14218,16 @@
       </c>
       <c r="F313" s="7"/>
       <c r="G313" s="7">
-        <f>IFERROR(VLOOKUP($F313,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H313" s="7">
-        <f>IFERROR(VLOOKUP($F313,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I313" s="7"/>
       <c r="J313" s="7">
-        <f>IFERROR(VLOOKUP($F313,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14388,16 +14246,16 @@
       </c>
       <c r="F314" s="7"/>
       <c r="G314" s="7">
-        <f>IFERROR(VLOOKUP($F314,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H314" s="7">
-        <f>IFERROR(VLOOKUP($F314,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I314" s="7"/>
       <c r="J314" s="7">
-        <f>IFERROR(VLOOKUP($F314,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14416,16 +14274,16 @@
       </c>
       <c r="F315" s="7"/>
       <c r="G315" s="7">
-        <f>IFERROR(VLOOKUP($F315,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H315" s="7">
-        <f>IFERROR(VLOOKUP($F315,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I315" s="7"/>
       <c r="J315" s="7">
-        <f>IFERROR(VLOOKUP($F315,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14444,16 +14302,16 @@
       </c>
       <c r="F316" s="7"/>
       <c r="G316" s="7">
-        <f>IFERROR(VLOOKUP($F316,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H316" s="7">
-        <f>IFERROR(VLOOKUP($F316,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I316" s="7"/>
       <c r="J316" s="7">
-        <f>IFERROR(VLOOKUP($F316,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14472,16 +14330,16 @@
       </c>
       <c r="F317" s="7"/>
       <c r="G317" s="7">
-        <f>IFERROR(VLOOKUP($F317,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H317" s="7">
-        <f>IFERROR(VLOOKUP($F317,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I317" s="7"/>
       <c r="J317" s="7">
-        <f>IFERROR(VLOOKUP($F317,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14500,16 +14358,16 @@
       </c>
       <c r="F318" s="7"/>
       <c r="G318" s="7">
-        <f>IFERROR(VLOOKUP($F318,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H318" s="7">
-        <f>IFERROR(VLOOKUP($F318,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I318" s="7"/>
       <c r="J318" s="7">
-        <f>IFERROR(VLOOKUP($F318,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14528,16 +14386,16 @@
       </c>
       <c r="F319" s="7"/>
       <c r="G319" s="7">
-        <f>IFERROR(VLOOKUP($F319,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H319" s="7">
-        <f>IFERROR(VLOOKUP($F319,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I319" s="7"/>
       <c r="J319" s="7">
-        <f>IFERROR(VLOOKUP($F319,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14556,16 +14414,16 @@
       </c>
       <c r="F320" s="7"/>
       <c r="G320" s="7">
-        <f>IFERROR(VLOOKUP($F320,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H320" s="7">
-        <f>IFERROR(VLOOKUP($F320,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I320" s="7"/>
       <c r="J320" s="7">
-        <f>IFERROR(VLOOKUP($F320,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14584,16 +14442,16 @@
       </c>
       <c r="F321" s="7"/>
       <c r="G321" s="7">
-        <f>IFERROR(VLOOKUP($F321,$A:$B,2,0),0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H321" s="7">
-        <f>IFERROR(VLOOKUP($F321,$A:$D,3,0),0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I321" s="7"/>
       <c r="J321" s="7">
-        <f>IFERROR(VLOOKUP($F321,$A:$D,4,0),0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -14612,16 +14470,16 @@
       </c>
       <c r="F322" s="7"/>
       <c r="G322" s="7">
-        <f>IFERROR(VLOOKUP($F322,$A:$B,2,0),0)</f>
+        <f t="shared" ref="G322:G385" si="15">IFERROR(VLOOKUP($F322,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H322" s="7">
-        <f>IFERROR(VLOOKUP($F322,$A:$D,3,0),0)</f>
+        <f t="shared" ref="H322:H385" si="16">IFERROR(VLOOKUP($F322,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I322" s="7"/>
       <c r="J322" s="7">
-        <f>IFERROR(VLOOKUP($F322,$A:$D,4,0),0)</f>
+        <f t="shared" ref="J322:J385" si="17">IFERROR(VLOOKUP($F322,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14640,16 +14498,16 @@
       </c>
       <c r="F323" s="7"/>
       <c r="G323" s="7">
-        <f>IFERROR(VLOOKUP($F323,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H323" s="7">
-        <f>IFERROR(VLOOKUP($F323,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I323" s="7"/>
       <c r="J323" s="7">
-        <f>IFERROR(VLOOKUP($F323,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14668,16 +14526,16 @@
       </c>
       <c r="F324" s="7"/>
       <c r="G324" s="7">
-        <f>IFERROR(VLOOKUP($F324,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H324" s="7">
-        <f>IFERROR(VLOOKUP($F324,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I324" s="7"/>
       <c r="J324" s="7">
-        <f>IFERROR(VLOOKUP($F324,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14696,16 +14554,16 @@
       </c>
       <c r="F325" s="7"/>
       <c r="G325" s="7">
-        <f>IFERROR(VLOOKUP($F325,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H325" s="7">
-        <f>IFERROR(VLOOKUP($F325,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I325" s="7"/>
       <c r="J325" s="7">
-        <f>IFERROR(VLOOKUP($F325,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14724,16 +14582,16 @@
       </c>
       <c r="F326" s="7"/>
       <c r="G326" s="7">
-        <f>IFERROR(VLOOKUP($F326,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H326" s="7">
-        <f>IFERROR(VLOOKUP($F326,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I326" s="7"/>
       <c r="J326" s="7">
-        <f>IFERROR(VLOOKUP($F326,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14752,16 +14610,16 @@
       </c>
       <c r="F327" s="7"/>
       <c r="G327" s="7">
-        <f>IFERROR(VLOOKUP($F327,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H327" s="7">
-        <f>IFERROR(VLOOKUP($F327,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I327" s="7"/>
       <c r="J327" s="7">
-        <f>IFERROR(VLOOKUP($F327,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14780,16 +14638,16 @@
       </c>
       <c r="F328" s="7"/>
       <c r="G328" s="7">
-        <f>IFERROR(VLOOKUP($F328,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H328" s="7">
-        <f>IFERROR(VLOOKUP($F328,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I328" s="7"/>
       <c r="J328" s="7">
-        <f>IFERROR(VLOOKUP($F328,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14808,16 +14666,16 @@
       </c>
       <c r="F329" s="7"/>
       <c r="G329" s="7">
-        <f>IFERROR(VLOOKUP($F329,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H329" s="7">
-        <f>IFERROR(VLOOKUP($F329,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I329" s="7"/>
       <c r="J329" s="7">
-        <f>IFERROR(VLOOKUP($F329,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14836,16 +14694,16 @@
       </c>
       <c r="F330" s="7"/>
       <c r="G330" s="7">
-        <f>IFERROR(VLOOKUP($F330,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H330" s="7">
-        <f>IFERROR(VLOOKUP($F330,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I330" s="7"/>
       <c r="J330" s="7">
-        <f>IFERROR(VLOOKUP($F330,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14864,16 +14722,16 @@
       </c>
       <c r="F331" s="7"/>
       <c r="G331" s="7">
-        <f>IFERROR(VLOOKUP($F331,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H331" s="7">
-        <f>IFERROR(VLOOKUP($F331,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I331" s="7"/>
       <c r="J331" s="7">
-        <f>IFERROR(VLOOKUP($F331,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14892,16 +14750,16 @@
       </c>
       <c r="F332" s="7"/>
       <c r="G332" s="7">
-        <f>IFERROR(VLOOKUP($F332,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H332" s="7">
-        <f>IFERROR(VLOOKUP($F332,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I332" s="7"/>
       <c r="J332" s="7">
-        <f>IFERROR(VLOOKUP($F332,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14920,16 +14778,16 @@
       </c>
       <c r="F333" s="7"/>
       <c r="G333" s="7">
-        <f>IFERROR(VLOOKUP($F333,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H333" s="7">
-        <f>IFERROR(VLOOKUP($F333,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I333" s="7"/>
       <c r="J333" s="7">
-        <f>IFERROR(VLOOKUP($F333,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14948,16 +14806,16 @@
       </c>
       <c r="F334" s="7"/>
       <c r="G334" s="7">
-        <f>IFERROR(VLOOKUP($F334,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H334" s="7">
-        <f>IFERROR(VLOOKUP($F334,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I334" s="7"/>
       <c r="J334" s="7">
-        <f>IFERROR(VLOOKUP($F334,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14976,16 +14834,16 @@
       </c>
       <c r="F335" s="7"/>
       <c r="G335" s="7">
-        <f>IFERROR(VLOOKUP($F335,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H335" s="7">
-        <f>IFERROR(VLOOKUP($F335,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I335" s="7"/>
       <c r="J335" s="7">
-        <f>IFERROR(VLOOKUP($F335,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15004,16 +14862,16 @@
       </c>
       <c r="F336" s="7"/>
       <c r="G336" s="7">
-        <f>IFERROR(VLOOKUP($F336,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H336" s="7">
-        <f>IFERROR(VLOOKUP($F336,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I336" s="7"/>
       <c r="J336" s="7">
-        <f>IFERROR(VLOOKUP($F336,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15032,16 +14890,16 @@
       </c>
       <c r="F337" s="7"/>
       <c r="G337" s="7">
-        <f>IFERROR(VLOOKUP($F337,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H337" s="7">
-        <f>IFERROR(VLOOKUP($F337,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I337" s="7"/>
       <c r="J337" s="7">
-        <f>IFERROR(VLOOKUP($F337,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15060,16 +14918,16 @@
       </c>
       <c r="F338" s="7"/>
       <c r="G338" s="7">
-        <f>IFERROR(VLOOKUP($F338,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H338" s="7">
-        <f>IFERROR(VLOOKUP($F338,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I338" s="7"/>
       <c r="J338" s="7">
-        <f>IFERROR(VLOOKUP($F338,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15088,16 +14946,16 @@
       </c>
       <c r="F339" s="7"/>
       <c r="G339" s="7">
-        <f>IFERROR(VLOOKUP($F339,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H339" s="7">
-        <f>IFERROR(VLOOKUP($F339,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I339" s="7"/>
       <c r="J339" s="7">
-        <f>IFERROR(VLOOKUP($F339,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15116,16 +14974,16 @@
       </c>
       <c r="F340" s="7"/>
       <c r="G340" s="7">
-        <f>IFERROR(VLOOKUP($F340,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H340" s="7">
-        <f>IFERROR(VLOOKUP($F340,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I340" s="7"/>
       <c r="J340" s="7">
-        <f>IFERROR(VLOOKUP($F340,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15144,16 +15002,16 @@
       </c>
       <c r="F341" s="7"/>
       <c r="G341" s="7">
-        <f>IFERROR(VLOOKUP($F341,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H341" s="7">
-        <f>IFERROR(VLOOKUP($F341,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I341" s="7"/>
       <c r="J341" s="7">
-        <f>IFERROR(VLOOKUP($F341,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15172,16 +15030,16 @@
       </c>
       <c r="F342" s="7"/>
       <c r="G342" s="7">
-        <f>IFERROR(VLOOKUP($F342,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H342" s="7">
-        <f>IFERROR(VLOOKUP($F342,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I342" s="7"/>
       <c r="J342" s="7">
-        <f>IFERROR(VLOOKUP($F342,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15200,16 +15058,16 @@
       </c>
       <c r="F343" s="7"/>
       <c r="G343" s="7">
-        <f>IFERROR(VLOOKUP($F343,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H343" s="7">
-        <f>IFERROR(VLOOKUP($F343,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I343" s="7"/>
       <c r="J343" s="7">
-        <f>IFERROR(VLOOKUP($F343,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15228,16 +15086,16 @@
       </c>
       <c r="F344" s="7"/>
       <c r="G344" s="7">
-        <f>IFERROR(VLOOKUP($F344,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H344" s="7">
-        <f>IFERROR(VLOOKUP($F344,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I344" s="7"/>
       <c r="J344" s="7">
-        <f>IFERROR(VLOOKUP($F344,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15256,16 +15114,16 @@
       </c>
       <c r="F345" s="7"/>
       <c r="G345" s="7">
-        <f>IFERROR(VLOOKUP($F345,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H345" s="7">
-        <f>IFERROR(VLOOKUP($F345,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I345" s="7"/>
       <c r="J345" s="7">
-        <f>IFERROR(VLOOKUP($F345,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15284,16 +15142,16 @@
       </c>
       <c r="F346" s="7"/>
       <c r="G346" s="7">
-        <f>IFERROR(VLOOKUP($F346,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H346" s="7">
-        <f>IFERROR(VLOOKUP($F346,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I346" s="7"/>
       <c r="J346" s="7">
-        <f>IFERROR(VLOOKUP($F346,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15312,16 +15170,16 @@
       </c>
       <c r="F347" s="7"/>
       <c r="G347" s="7">
-        <f>IFERROR(VLOOKUP($F347,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H347" s="7">
-        <f>IFERROR(VLOOKUP($F347,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I347" s="7"/>
       <c r="J347" s="7">
-        <f>IFERROR(VLOOKUP($F347,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15340,16 +15198,16 @@
       </c>
       <c r="F348" s="7"/>
       <c r="G348" s="7">
-        <f>IFERROR(VLOOKUP($F348,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H348" s="7">
-        <f>IFERROR(VLOOKUP($F348,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I348" s="7"/>
       <c r="J348" s="7">
-        <f>IFERROR(VLOOKUP($F348,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15368,16 +15226,16 @@
       </c>
       <c r="F349" s="7"/>
       <c r="G349" s="7">
-        <f>IFERROR(VLOOKUP($F349,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H349" s="7">
-        <f>IFERROR(VLOOKUP($F349,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I349" s="7"/>
       <c r="J349" s="7">
-        <f>IFERROR(VLOOKUP($F349,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15396,16 +15254,16 @@
       </c>
       <c r="F350" s="7"/>
       <c r="G350" s="7">
-        <f>IFERROR(VLOOKUP($F350,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H350" s="7">
-        <f>IFERROR(VLOOKUP($F350,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I350" s="7"/>
       <c r="J350" s="7">
-        <f>IFERROR(VLOOKUP($F350,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15424,16 +15282,16 @@
       </c>
       <c r="F351" s="7"/>
       <c r="G351" s="7">
-        <f>IFERROR(VLOOKUP($F351,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H351" s="7">
-        <f>IFERROR(VLOOKUP($F351,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I351" s="7"/>
       <c r="J351" s="7">
-        <f>IFERROR(VLOOKUP($F351,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15452,16 +15310,16 @@
       </c>
       <c r="F352" s="7"/>
       <c r="G352" s="7">
-        <f>IFERROR(VLOOKUP($F352,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H352" s="7">
-        <f>IFERROR(VLOOKUP($F352,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I352" s="7"/>
       <c r="J352" s="7">
-        <f>IFERROR(VLOOKUP($F352,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15480,16 +15338,16 @@
       </c>
       <c r="F353" s="7"/>
       <c r="G353" s="7">
-        <f>IFERROR(VLOOKUP($F353,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H353" s="7">
-        <f>IFERROR(VLOOKUP($F353,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I353" s="7"/>
       <c r="J353" s="7">
-        <f>IFERROR(VLOOKUP($F353,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15508,16 +15366,16 @@
       </c>
       <c r="F354" s="7"/>
       <c r="G354" s="7">
-        <f>IFERROR(VLOOKUP($F354,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H354" s="7">
-        <f>IFERROR(VLOOKUP($F354,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I354" s="7"/>
       <c r="J354" s="7">
-        <f>IFERROR(VLOOKUP($F354,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15536,16 +15394,16 @@
       </c>
       <c r="F355" s="7"/>
       <c r="G355" s="7">
-        <f>IFERROR(VLOOKUP($F355,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H355" s="7">
-        <f>IFERROR(VLOOKUP($F355,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I355" s="7"/>
       <c r="J355" s="7">
-        <f>IFERROR(VLOOKUP($F355,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15564,16 +15422,16 @@
       </c>
       <c r="F356" s="7"/>
       <c r="G356" s="7">
-        <f>IFERROR(VLOOKUP($F356,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H356" s="7">
-        <f>IFERROR(VLOOKUP($F356,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I356" s="7"/>
       <c r="J356" s="7">
-        <f>IFERROR(VLOOKUP($F356,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15592,16 +15450,16 @@
       </c>
       <c r="F357" s="7"/>
       <c r="G357" s="7">
-        <f>IFERROR(VLOOKUP($F357,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H357" s="7">
-        <f>IFERROR(VLOOKUP($F357,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I357" s="7"/>
       <c r="J357" s="7">
-        <f>IFERROR(VLOOKUP($F357,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15620,16 +15478,16 @@
       </c>
       <c r="F358" s="7"/>
       <c r="G358" s="7">
-        <f>IFERROR(VLOOKUP($F358,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H358" s="7">
-        <f>IFERROR(VLOOKUP($F358,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I358" s="7"/>
       <c r="J358" s="7">
-        <f>IFERROR(VLOOKUP($F358,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15648,16 +15506,16 @@
       </c>
       <c r="F359" s="7"/>
       <c r="G359" s="7">
-        <f>IFERROR(VLOOKUP($F359,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H359" s="7">
-        <f>IFERROR(VLOOKUP($F359,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I359" s="7"/>
       <c r="J359" s="7">
-        <f>IFERROR(VLOOKUP($F359,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15676,16 +15534,16 @@
       </c>
       <c r="F360" s="7"/>
       <c r="G360" s="7">
-        <f>IFERROR(VLOOKUP($F360,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H360" s="7">
-        <f>IFERROR(VLOOKUP($F360,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I360" s="7"/>
       <c r="J360" s="7">
-        <f>IFERROR(VLOOKUP($F360,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15704,16 +15562,16 @@
       </c>
       <c r="F361" s="7"/>
       <c r="G361" s="7">
-        <f>IFERROR(VLOOKUP($F361,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H361" s="7">
-        <f>IFERROR(VLOOKUP($F361,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I361" s="7"/>
       <c r="J361" s="7">
-        <f>IFERROR(VLOOKUP($F361,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15732,16 +15590,16 @@
       </c>
       <c r="F362" s="7"/>
       <c r="G362" s="7">
-        <f>IFERROR(VLOOKUP($F362,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H362" s="7">
-        <f>IFERROR(VLOOKUP($F362,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I362" s="7"/>
       <c r="J362" s="7">
-        <f>IFERROR(VLOOKUP($F362,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15760,16 +15618,16 @@
       </c>
       <c r="F363" s="7"/>
       <c r="G363" s="7">
-        <f>IFERROR(VLOOKUP($F363,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H363" s="7">
-        <f>IFERROR(VLOOKUP($F363,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I363" s="7"/>
       <c r="J363" s="7">
-        <f>IFERROR(VLOOKUP($F363,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15788,16 +15646,16 @@
       </c>
       <c r="F364" s="7"/>
       <c r="G364" s="7">
-        <f>IFERROR(VLOOKUP($F364,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H364" s="7">
-        <f>IFERROR(VLOOKUP($F364,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I364" s="7"/>
       <c r="J364" s="7">
-        <f>IFERROR(VLOOKUP($F364,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15816,16 +15674,16 @@
       </c>
       <c r="F365" s="7"/>
       <c r="G365" s="7">
-        <f>IFERROR(VLOOKUP($F365,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H365" s="7">
-        <f>IFERROR(VLOOKUP($F365,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I365" s="7"/>
       <c r="J365" s="7">
-        <f>IFERROR(VLOOKUP($F365,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15844,16 +15702,16 @@
       </c>
       <c r="F366" s="7"/>
       <c r="G366" s="7">
-        <f>IFERROR(VLOOKUP($F366,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H366" s="7">
-        <f>IFERROR(VLOOKUP($F366,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I366" s="7"/>
       <c r="J366" s="7">
-        <f>IFERROR(VLOOKUP($F366,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15872,16 +15730,16 @@
       </c>
       <c r="F367" s="40"/>
       <c r="G367" s="40">
-        <f>IFERROR(VLOOKUP($F367,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H367" s="40">
-        <f>IFERROR(VLOOKUP($F367,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I367" s="40"/>
       <c r="J367" s="40">
-        <f>IFERROR(VLOOKUP($F367,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15900,16 +15758,16 @@
       </c>
       <c r="F368" s="7"/>
       <c r="G368" s="7">
-        <f>IFERROR(VLOOKUP($F368,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H368" s="7">
-        <f>IFERROR(VLOOKUP($F368,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I368" s="7"/>
       <c r="J368" s="7">
-        <f>IFERROR(VLOOKUP($F368,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15928,16 +15786,16 @@
       </c>
       <c r="F369" s="7"/>
       <c r="G369" s="7">
-        <f>IFERROR(VLOOKUP($F369,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H369" s="7">
-        <f>IFERROR(VLOOKUP($F369,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I369" s="7"/>
       <c r="J369" s="7">
-        <f>IFERROR(VLOOKUP($F369,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15956,16 +15814,16 @@
       </c>
       <c r="F370" s="7"/>
       <c r="G370" s="7">
-        <f>IFERROR(VLOOKUP($F370,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H370" s="7">
-        <f>IFERROR(VLOOKUP($F370,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I370" s="7"/>
       <c r="J370" s="7">
-        <f>IFERROR(VLOOKUP($F370,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -15984,16 +15842,16 @@
       </c>
       <c r="F371" s="7"/>
       <c r="G371" s="7">
-        <f>IFERROR(VLOOKUP($F371,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H371" s="7">
-        <f>IFERROR(VLOOKUP($F371,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I371" s="7"/>
       <c r="J371" s="7">
-        <f>IFERROR(VLOOKUP($F371,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16012,16 +15870,16 @@
       </c>
       <c r="F372" s="7"/>
       <c r="G372" s="7">
-        <f>IFERROR(VLOOKUP($F372,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H372" s="7">
-        <f>IFERROR(VLOOKUP($F372,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I372" s="7"/>
       <c r="J372" s="7">
-        <f>IFERROR(VLOOKUP($F372,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16040,16 +15898,16 @@
       </c>
       <c r="F373" s="7"/>
       <c r="G373" s="7">
-        <f>IFERROR(VLOOKUP($F373,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H373" s="7">
-        <f>IFERROR(VLOOKUP($F373,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I373" s="7"/>
       <c r="J373" s="7">
-        <f>IFERROR(VLOOKUP($F373,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16068,16 +15926,16 @@
       </c>
       <c r="F374" s="7"/>
       <c r="G374" s="7">
-        <f>IFERROR(VLOOKUP($F374,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H374" s="7">
-        <f>IFERROR(VLOOKUP($F374,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I374" s="7"/>
       <c r="J374" s="7">
-        <f>IFERROR(VLOOKUP($F374,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16096,16 +15954,16 @@
       </c>
       <c r="F375" s="7"/>
       <c r="G375" s="7">
-        <f>IFERROR(VLOOKUP($F375,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H375" s="7">
-        <f>IFERROR(VLOOKUP($F375,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I375" s="7"/>
       <c r="J375" s="7">
-        <f>IFERROR(VLOOKUP($F375,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16124,16 +15982,16 @@
       </c>
       <c r="F376" s="7"/>
       <c r="G376" s="7">
-        <f>IFERROR(VLOOKUP($F376,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H376" s="7">
-        <f>IFERROR(VLOOKUP($F376,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I376" s="7"/>
       <c r="J376" s="7">
-        <f>IFERROR(VLOOKUP($F376,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16152,16 +16010,16 @@
       </c>
       <c r="F377" s="7"/>
       <c r="G377" s="7">
-        <f>IFERROR(VLOOKUP($F377,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H377" s="7">
-        <f>IFERROR(VLOOKUP($F377,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I377" s="7"/>
       <c r="J377" s="7">
-        <f>IFERROR(VLOOKUP($F377,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16180,16 +16038,16 @@
       </c>
       <c r="F378" s="7"/>
       <c r="G378" s="7">
-        <f>IFERROR(VLOOKUP($F378,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H378" s="7">
-        <f>IFERROR(VLOOKUP($F378,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I378" s="7"/>
       <c r="J378" s="7">
-        <f>IFERROR(VLOOKUP($F378,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16208,16 +16066,16 @@
       </c>
       <c r="F379" s="7"/>
       <c r="G379" s="7">
-        <f>IFERROR(VLOOKUP($F379,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H379" s="7">
-        <f>IFERROR(VLOOKUP($F379,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I379" s="7"/>
       <c r="J379" s="7">
-        <f>IFERROR(VLOOKUP($F379,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16236,16 +16094,16 @@
       </c>
       <c r="F380" s="7"/>
       <c r="G380" s="7">
-        <f>IFERROR(VLOOKUP($F380,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H380" s="7">
-        <f>IFERROR(VLOOKUP($F380,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I380" s="7"/>
       <c r="J380" s="7">
-        <f>IFERROR(VLOOKUP($F380,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16264,16 +16122,16 @@
       </c>
       <c r="F381" s="7"/>
       <c r="G381" s="7">
-        <f>IFERROR(VLOOKUP($F381,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H381" s="7">
-        <f>IFERROR(VLOOKUP($F381,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I381" s="7"/>
       <c r="J381" s="7">
-        <f>IFERROR(VLOOKUP($F381,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16292,16 +16150,16 @@
       </c>
       <c r="F382" s="7"/>
       <c r="G382" s="7">
-        <f>IFERROR(VLOOKUP($F382,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H382" s="7">
-        <f>IFERROR(VLOOKUP($F382,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I382" s="7"/>
       <c r="J382" s="7">
-        <f>IFERROR(VLOOKUP($F382,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16320,16 +16178,16 @@
       </c>
       <c r="F383" s="7"/>
       <c r="G383" s="7">
-        <f>IFERROR(VLOOKUP($F383,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H383" s="7">
-        <f>IFERROR(VLOOKUP($F383,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I383" s="7"/>
       <c r="J383" s="7">
-        <f>IFERROR(VLOOKUP($F383,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16348,16 +16206,16 @@
       </c>
       <c r="F384" s="7"/>
       <c r="G384" s="7">
-        <f>IFERROR(VLOOKUP($F384,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H384" s="7">
-        <f>IFERROR(VLOOKUP($F384,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I384" s="7"/>
       <c r="J384" s="7">
-        <f>IFERROR(VLOOKUP($F384,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16376,16 +16234,16 @@
       </c>
       <c r="F385" s="7"/>
       <c r="G385" s="7">
-        <f>IFERROR(VLOOKUP($F385,$A:$B,2,0),0)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H385" s="7">
-        <f>IFERROR(VLOOKUP($F385,$A:$D,3,0),0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I385" s="7"/>
       <c r="J385" s="7">
-        <f>IFERROR(VLOOKUP($F385,$A:$D,4,0),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -16404,16 +16262,16 @@
       </c>
       <c r="F386" s="7"/>
       <c r="G386" s="7">
-        <f>IFERROR(VLOOKUP($F386,$A:$B,2,0),0)</f>
+        <f t="shared" ref="G386:G449" si="18">IFERROR(VLOOKUP($F386,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H386" s="7">
-        <f>IFERROR(VLOOKUP($F386,$A:$D,3,0),0)</f>
+        <f t="shared" ref="H386:H449" si="19">IFERROR(VLOOKUP($F386,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I386" s="7"/>
       <c r="J386" s="7">
-        <f>IFERROR(VLOOKUP($F386,$A:$D,4,0),0)</f>
+        <f t="shared" ref="J386:J449" si="20">IFERROR(VLOOKUP($F386,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16432,16 +16290,16 @@
       </c>
       <c r="F387" s="7"/>
       <c r="G387" s="7">
-        <f>IFERROR(VLOOKUP($F387,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H387" s="7">
-        <f>IFERROR(VLOOKUP($F387,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I387" s="7"/>
       <c r="J387" s="7">
-        <f>IFERROR(VLOOKUP($F387,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16460,16 +16318,16 @@
       </c>
       <c r="F388" s="7"/>
       <c r="G388" s="7">
-        <f>IFERROR(VLOOKUP($F388,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H388" s="7">
-        <f>IFERROR(VLOOKUP($F388,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I388" s="7"/>
       <c r="J388" s="7">
-        <f>IFERROR(VLOOKUP($F388,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16488,16 +16346,16 @@
       </c>
       <c r="F389" s="7"/>
       <c r="G389" s="7">
-        <f>IFERROR(VLOOKUP($F389,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H389" s="7">
-        <f>IFERROR(VLOOKUP($F389,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I389" s="7"/>
       <c r="J389" s="7">
-        <f>IFERROR(VLOOKUP($F389,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16516,16 +16374,16 @@
       </c>
       <c r="F390" s="7"/>
       <c r="G390" s="7">
-        <f>IFERROR(VLOOKUP($F390,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H390" s="7">
-        <f>IFERROR(VLOOKUP($F390,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I390" s="7"/>
       <c r="J390" s="7">
-        <f>IFERROR(VLOOKUP($F390,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16544,16 +16402,16 @@
       </c>
       <c r="F391" s="7"/>
       <c r="G391" s="7">
-        <f>IFERROR(VLOOKUP($F391,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H391" s="7">
-        <f>IFERROR(VLOOKUP($F391,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I391" s="7"/>
       <c r="J391" s="7">
-        <f>IFERROR(VLOOKUP($F391,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16572,16 +16430,16 @@
       </c>
       <c r="F392" s="7"/>
       <c r="G392" s="7">
-        <f>IFERROR(VLOOKUP($F392,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H392" s="7">
-        <f>IFERROR(VLOOKUP($F392,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I392" s="7"/>
       <c r="J392" s="7">
-        <f>IFERROR(VLOOKUP($F392,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16600,16 +16458,16 @@
       </c>
       <c r="F393" s="7"/>
       <c r="G393" s="7">
-        <f>IFERROR(VLOOKUP($F393,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H393" s="7">
-        <f>IFERROR(VLOOKUP($F393,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I393" s="7"/>
       <c r="J393" s="7">
-        <f>IFERROR(VLOOKUP($F393,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16628,16 +16486,16 @@
       </c>
       <c r="F394" s="7"/>
       <c r="G394" s="7">
-        <f>IFERROR(VLOOKUP($F394,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H394" s="7">
-        <f>IFERROR(VLOOKUP($F394,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I394" s="7"/>
       <c r="J394" s="7">
-        <f>IFERROR(VLOOKUP($F394,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16656,16 +16514,16 @@
       </c>
       <c r="F395" s="7"/>
       <c r="G395" s="7">
-        <f>IFERROR(VLOOKUP($F395,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H395" s="7">
-        <f>IFERROR(VLOOKUP($F395,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I395" s="7"/>
       <c r="J395" s="7">
-        <f>IFERROR(VLOOKUP($F395,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16684,16 +16542,16 @@
       </c>
       <c r="F396" s="7"/>
       <c r="G396" s="7">
-        <f>IFERROR(VLOOKUP($F396,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H396" s="7">
-        <f>IFERROR(VLOOKUP($F396,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I396" s="7"/>
       <c r="J396" s="7">
-        <f>IFERROR(VLOOKUP($F396,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16712,16 +16570,16 @@
       </c>
       <c r="F397" s="7"/>
       <c r="G397" s="7">
-        <f>IFERROR(VLOOKUP($F397,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H397" s="7">
-        <f>IFERROR(VLOOKUP($F397,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I397" s="7"/>
       <c r="J397" s="7">
-        <f>IFERROR(VLOOKUP($F397,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16740,16 +16598,16 @@
       </c>
       <c r="F398" s="7"/>
       <c r="G398" s="7">
-        <f>IFERROR(VLOOKUP($F398,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H398" s="7">
-        <f>IFERROR(VLOOKUP($F398,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I398" s="7"/>
       <c r="J398" s="7">
-        <f>IFERROR(VLOOKUP($F398,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16768,16 +16626,16 @@
       </c>
       <c r="F399" s="7"/>
       <c r="G399" s="7">
-        <f>IFERROR(VLOOKUP($F399,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H399" s="7">
-        <f>IFERROR(VLOOKUP($F399,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I399" s="7"/>
       <c r="J399" s="7">
-        <f>IFERROR(VLOOKUP($F399,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16796,16 +16654,16 @@
       </c>
       <c r="F400" s="7"/>
       <c r="G400" s="7">
-        <f>IFERROR(VLOOKUP($F400,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H400" s="7">
-        <f>IFERROR(VLOOKUP($F400,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I400" s="7"/>
       <c r="J400" s="7">
-        <f>IFERROR(VLOOKUP($F400,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16824,16 +16682,16 @@
       </c>
       <c r="F401" s="7"/>
       <c r="G401" s="7">
-        <f>IFERROR(VLOOKUP($F401,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H401" s="7">
-        <f>IFERROR(VLOOKUP($F401,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I401" s="7"/>
       <c r="J401" s="7">
-        <f>IFERROR(VLOOKUP($F401,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16852,16 +16710,16 @@
       </c>
       <c r="F402" s="7"/>
       <c r="G402" s="7">
-        <f>IFERROR(VLOOKUP($F402,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H402" s="7">
-        <f>IFERROR(VLOOKUP($F402,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I402" s="7"/>
       <c r="J402" s="7">
-        <f>IFERROR(VLOOKUP($F402,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16880,16 +16738,16 @@
       </c>
       <c r="F403" s="7"/>
       <c r="G403" s="7">
-        <f>IFERROR(VLOOKUP($F403,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H403" s="7">
-        <f>IFERROR(VLOOKUP($F403,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I403" s="7"/>
       <c r="J403" s="7">
-        <f>IFERROR(VLOOKUP($F403,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16908,16 +16766,16 @@
       </c>
       <c r="F404" s="7"/>
       <c r="G404" s="7">
-        <f>IFERROR(VLOOKUP($F404,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H404" s="7">
-        <f>IFERROR(VLOOKUP($F404,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I404" s="7"/>
       <c r="J404" s="7">
-        <f>IFERROR(VLOOKUP($F404,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16936,16 +16794,16 @@
       </c>
       <c r="F405" s="7"/>
       <c r="G405" s="7">
-        <f>IFERROR(VLOOKUP($F405,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H405" s="7">
-        <f>IFERROR(VLOOKUP($F405,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I405" s="7"/>
       <c r="J405" s="7">
-        <f>IFERROR(VLOOKUP($F405,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16964,16 +16822,16 @@
       </c>
       <c r="F406" s="7"/>
       <c r="G406" s="7">
-        <f>IFERROR(VLOOKUP($F406,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H406" s="7">
-        <f>IFERROR(VLOOKUP($F406,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I406" s="7"/>
       <c r="J406" s="7">
-        <f>IFERROR(VLOOKUP($F406,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -16992,16 +16850,16 @@
       </c>
       <c r="F407" s="7"/>
       <c r="G407" s="7">
-        <f>IFERROR(VLOOKUP($F407,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H407" s="7">
-        <f>IFERROR(VLOOKUP($F407,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I407" s="7"/>
       <c r="J407" s="7">
-        <f>IFERROR(VLOOKUP($F407,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17020,16 +16878,16 @@
       </c>
       <c r="F408" s="7"/>
       <c r="G408" s="7">
-        <f>IFERROR(VLOOKUP($F408,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H408" s="7">
-        <f>IFERROR(VLOOKUP($F408,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I408" s="7"/>
       <c r="J408" s="7">
-        <f>IFERROR(VLOOKUP($F408,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17048,16 +16906,16 @@
       </c>
       <c r="F409" s="7"/>
       <c r="G409" s="7">
-        <f>IFERROR(VLOOKUP($F409,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H409" s="7">
-        <f>IFERROR(VLOOKUP($F409,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I409" s="7"/>
       <c r="J409" s="7">
-        <f>IFERROR(VLOOKUP($F409,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17076,16 +16934,16 @@
       </c>
       <c r="F410" s="7"/>
       <c r="G410" s="7">
-        <f>IFERROR(VLOOKUP($F410,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H410" s="7">
-        <f>IFERROR(VLOOKUP($F410,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I410" s="7"/>
       <c r="J410" s="7">
-        <f>IFERROR(VLOOKUP($F410,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17104,16 +16962,16 @@
       </c>
       <c r="F411" s="7"/>
       <c r="G411" s="7">
-        <f>IFERROR(VLOOKUP($F411,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H411" s="7">
-        <f>IFERROR(VLOOKUP($F411,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I411" s="7"/>
       <c r="J411" s="7">
-        <f>IFERROR(VLOOKUP($F411,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17132,16 +16990,16 @@
       </c>
       <c r="F412" s="7"/>
       <c r="G412" s="7">
-        <f>IFERROR(VLOOKUP($F412,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H412" s="7">
-        <f>IFERROR(VLOOKUP($F412,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I412" s="7"/>
       <c r="J412" s="7">
-        <f>IFERROR(VLOOKUP($F412,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17160,16 +17018,16 @@
       </c>
       <c r="F413" s="7"/>
       <c r="G413" s="7">
-        <f>IFERROR(VLOOKUP($F413,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H413" s="7">
-        <f>IFERROR(VLOOKUP($F413,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I413" s="7"/>
       <c r="J413" s="7">
-        <f>IFERROR(VLOOKUP($F413,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17188,16 +17046,16 @@
       </c>
       <c r="F414" s="7"/>
       <c r="G414" s="7">
-        <f>IFERROR(VLOOKUP($F414,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H414" s="7">
-        <f>IFERROR(VLOOKUP($F414,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I414" s="7"/>
       <c r="J414" s="7">
-        <f>IFERROR(VLOOKUP($F414,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17216,16 +17074,16 @@
       </c>
       <c r="F415" s="7"/>
       <c r="G415" s="7">
-        <f>IFERROR(VLOOKUP($F415,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H415" s="7">
-        <f>IFERROR(VLOOKUP($F415,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I415" s="7"/>
       <c r="J415" s="7">
-        <f>IFERROR(VLOOKUP($F415,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17244,16 +17102,16 @@
       </c>
       <c r="F416" s="7"/>
       <c r="G416" s="7">
-        <f>IFERROR(VLOOKUP($F416,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H416" s="7">
-        <f>IFERROR(VLOOKUP($F416,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I416" s="7"/>
       <c r="J416" s="7">
-        <f>IFERROR(VLOOKUP($F416,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17272,16 +17130,16 @@
       </c>
       <c r="F417" s="7"/>
       <c r="G417" s="7">
-        <f>IFERROR(VLOOKUP($F417,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H417" s="7">
-        <f>IFERROR(VLOOKUP($F417,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I417" s="7"/>
       <c r="J417" s="7">
-        <f>IFERROR(VLOOKUP($F417,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17300,16 +17158,16 @@
       </c>
       <c r="F418" s="7"/>
       <c r="G418" s="7">
-        <f>IFERROR(VLOOKUP($F418,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H418" s="7">
-        <f>IFERROR(VLOOKUP($F418,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I418" s="7"/>
       <c r="J418" s="7">
-        <f>IFERROR(VLOOKUP($F418,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17328,16 +17186,16 @@
       </c>
       <c r="F419" s="7"/>
       <c r="G419" s="7">
-        <f>IFERROR(VLOOKUP($F419,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H419" s="7">
-        <f>IFERROR(VLOOKUP($F419,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I419" s="7"/>
       <c r="J419" s="7">
-        <f>IFERROR(VLOOKUP($F419,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17356,16 +17214,16 @@
       </c>
       <c r="F420" s="7"/>
       <c r="G420" s="7">
-        <f>IFERROR(VLOOKUP($F420,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H420" s="7">
-        <f>IFERROR(VLOOKUP($F420,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I420" s="7"/>
       <c r="J420" s="7">
-        <f>IFERROR(VLOOKUP($F420,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17384,16 +17242,16 @@
       </c>
       <c r="F421" s="7"/>
       <c r="G421" s="7">
-        <f>IFERROR(VLOOKUP($F421,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H421" s="7">
-        <f>IFERROR(VLOOKUP($F421,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I421" s="7"/>
       <c r="J421" s="7">
-        <f>IFERROR(VLOOKUP($F421,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17412,16 +17270,16 @@
       </c>
       <c r="F422" s="7"/>
       <c r="G422" s="7">
-        <f>IFERROR(VLOOKUP($F422,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H422" s="7">
-        <f>IFERROR(VLOOKUP($F422,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I422" s="7"/>
       <c r="J422" s="7">
-        <f>IFERROR(VLOOKUP($F422,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17440,16 +17298,16 @@
       </c>
       <c r="F423" s="7"/>
       <c r="G423" s="7">
-        <f>IFERROR(VLOOKUP($F423,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H423" s="7">
-        <f>IFERROR(VLOOKUP($F423,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I423" s="7"/>
       <c r="J423" s="7">
-        <f>IFERROR(VLOOKUP($F423,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17468,16 +17326,16 @@
       </c>
       <c r="F424" s="7"/>
       <c r="G424" s="7">
-        <f>IFERROR(VLOOKUP($F424,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H424" s="7">
-        <f>IFERROR(VLOOKUP($F424,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I424" s="7"/>
       <c r="J424" s="7">
-        <f>IFERROR(VLOOKUP($F424,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17496,16 +17354,16 @@
       </c>
       <c r="F425" s="7"/>
       <c r="G425" s="7">
-        <f>IFERROR(VLOOKUP($F425,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H425" s="7">
-        <f>IFERROR(VLOOKUP($F425,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I425" s="7"/>
       <c r="J425" s="7">
-        <f>IFERROR(VLOOKUP($F425,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17524,16 +17382,16 @@
       </c>
       <c r="F426" s="7"/>
       <c r="G426" s="7">
-        <f>IFERROR(VLOOKUP($F426,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H426" s="7">
-        <f>IFERROR(VLOOKUP($F426,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I426" s="7"/>
       <c r="J426" s="7">
-        <f>IFERROR(VLOOKUP($F426,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17552,16 +17410,16 @@
       </c>
       <c r="F427" s="7"/>
       <c r="G427" s="7">
-        <f>IFERROR(VLOOKUP($F427,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H427" s="7">
-        <f>IFERROR(VLOOKUP($F427,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I427" s="7"/>
       <c r="J427" s="7">
-        <f>IFERROR(VLOOKUP($F427,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17580,16 +17438,16 @@
       </c>
       <c r="F428" s="7"/>
       <c r="G428" s="7">
-        <f>IFERROR(VLOOKUP($F428,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H428" s="7">
-        <f>IFERROR(VLOOKUP($F428,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I428" s="7"/>
       <c r="J428" s="7">
-        <f>IFERROR(VLOOKUP($F428,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17608,16 +17466,16 @@
       </c>
       <c r="F429" s="7"/>
       <c r="G429" s="7">
-        <f>IFERROR(VLOOKUP($F429,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H429" s="7">
-        <f>IFERROR(VLOOKUP($F429,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I429" s="7"/>
       <c r="J429" s="7">
-        <f>IFERROR(VLOOKUP($F429,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17636,16 +17494,16 @@
       </c>
       <c r="F430" s="7"/>
       <c r="G430" s="7">
-        <f>IFERROR(VLOOKUP($F430,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H430" s="7">
-        <f>IFERROR(VLOOKUP($F430,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I430" s="7"/>
       <c r="J430" s="7">
-        <f>IFERROR(VLOOKUP($F430,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17664,16 +17522,16 @@
       </c>
       <c r="F431" s="7"/>
       <c r="G431" s="7">
-        <f>IFERROR(VLOOKUP($F431,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H431" s="7">
-        <f>IFERROR(VLOOKUP($F431,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I431" s="7"/>
       <c r="J431" s="7">
-        <f>IFERROR(VLOOKUP($F431,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17692,16 +17550,16 @@
       </c>
       <c r="F432" s="7"/>
       <c r="G432" s="7">
-        <f>IFERROR(VLOOKUP($F432,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H432" s="7">
-        <f>IFERROR(VLOOKUP($F432,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I432" s="7"/>
       <c r="J432" s="7">
-        <f>IFERROR(VLOOKUP($F432,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17720,16 +17578,16 @@
       </c>
       <c r="F433" s="7"/>
       <c r="G433" s="7">
-        <f>IFERROR(VLOOKUP($F433,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H433" s="7">
-        <f>IFERROR(VLOOKUP($F433,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I433" s="7"/>
       <c r="J433" s="7">
-        <f>IFERROR(VLOOKUP($F433,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17748,16 +17606,16 @@
       </c>
       <c r="F434" s="7"/>
       <c r="G434" s="7">
-        <f>IFERROR(VLOOKUP($F434,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H434" s="7">
-        <f>IFERROR(VLOOKUP($F434,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I434" s="7"/>
       <c r="J434" s="7">
-        <f>IFERROR(VLOOKUP($F434,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17776,16 +17634,16 @@
       </c>
       <c r="F435" s="7"/>
       <c r="G435" s="7">
-        <f>IFERROR(VLOOKUP($F435,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H435" s="7">
-        <f>IFERROR(VLOOKUP($F435,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I435" s="7"/>
       <c r="J435" s="7">
-        <f>IFERROR(VLOOKUP($F435,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17804,16 +17662,16 @@
       </c>
       <c r="F436" s="7"/>
       <c r="G436" s="7">
-        <f>IFERROR(VLOOKUP($F436,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H436" s="7">
-        <f>IFERROR(VLOOKUP($F436,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I436" s="7"/>
       <c r="J436" s="7">
-        <f>IFERROR(VLOOKUP($F436,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17832,16 +17690,16 @@
       </c>
       <c r="F437" s="7"/>
       <c r="G437" s="7">
-        <f>IFERROR(VLOOKUP($F437,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H437" s="7">
-        <f>IFERROR(VLOOKUP($F437,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I437" s="7"/>
       <c r="J437" s="7">
-        <f>IFERROR(VLOOKUP($F437,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17860,16 +17718,16 @@
       </c>
       <c r="F438" s="7"/>
       <c r="G438" s="7">
-        <f>IFERROR(VLOOKUP($F438,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H438" s="7">
-        <f>IFERROR(VLOOKUP($F438,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I438" s="7"/>
       <c r="J438" s="7">
-        <f>IFERROR(VLOOKUP($F438,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17888,16 +17746,16 @@
       </c>
       <c r="F439" s="7"/>
       <c r="G439" s="7">
-        <f>IFERROR(VLOOKUP($F439,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H439" s="7">
-        <f>IFERROR(VLOOKUP($F439,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I439" s="7"/>
       <c r="J439" s="7">
-        <f>IFERROR(VLOOKUP($F439,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17916,16 +17774,16 @@
       </c>
       <c r="F440" s="7"/>
       <c r="G440" s="7">
-        <f>IFERROR(VLOOKUP($F440,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H440" s="7">
-        <f>IFERROR(VLOOKUP($F440,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I440" s="7"/>
       <c r="J440" s="7">
-        <f>IFERROR(VLOOKUP($F440,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17944,16 +17802,16 @@
       </c>
       <c r="F441" s="7"/>
       <c r="G441" s="7">
-        <f>IFERROR(VLOOKUP($F441,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H441" s="7">
-        <f>IFERROR(VLOOKUP($F441,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I441" s="7"/>
       <c r="J441" s="7">
-        <f>IFERROR(VLOOKUP($F441,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -17972,16 +17830,16 @@
       </c>
       <c r="F442" s="7"/>
       <c r="G442" s="7">
-        <f>IFERROR(VLOOKUP($F442,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H442" s="7">
-        <f>IFERROR(VLOOKUP($F442,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I442" s="7"/>
       <c r="J442" s="7">
-        <f>IFERROR(VLOOKUP($F442,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -18000,16 +17858,16 @@
       </c>
       <c r="F443" s="7"/>
       <c r="G443" s="7">
-        <f>IFERROR(VLOOKUP($F443,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H443" s="7">
-        <f>IFERROR(VLOOKUP($F443,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I443" s="7"/>
       <c r="J443" s="7">
-        <f>IFERROR(VLOOKUP($F443,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -18028,16 +17886,16 @@
       </c>
       <c r="F444" s="7"/>
       <c r="G444" s="7">
-        <f>IFERROR(VLOOKUP($F444,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H444" s="7">
-        <f>IFERROR(VLOOKUP($F444,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I444" s="7"/>
       <c r="J444" s="7">
-        <f>IFERROR(VLOOKUP($F444,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -18056,16 +17914,16 @@
       </c>
       <c r="F445" s="7"/>
       <c r="G445" s="7">
-        <f>IFERROR(VLOOKUP($F445,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H445" s="7">
-        <f>IFERROR(VLOOKUP($F445,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I445" s="7"/>
       <c r="J445" s="7">
-        <f>IFERROR(VLOOKUP($F445,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -18084,16 +17942,16 @@
       </c>
       <c r="F446" s="7"/>
       <c r="G446" s="7">
-        <f>IFERROR(VLOOKUP($F446,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H446" s="7">
-        <f>IFERROR(VLOOKUP($F446,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I446" s="7"/>
       <c r="J446" s="7">
-        <f>IFERROR(VLOOKUP($F446,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -18112,16 +17970,16 @@
       </c>
       <c r="F447" s="7"/>
       <c r="G447" s="7">
-        <f>IFERROR(VLOOKUP($F447,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H447" s="7">
-        <f>IFERROR(VLOOKUP($F447,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I447" s="7"/>
       <c r="J447" s="7">
-        <f>IFERROR(VLOOKUP($F447,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -18140,16 +17998,16 @@
       </c>
       <c r="F448" s="7"/>
       <c r="G448" s="7">
-        <f>IFERROR(VLOOKUP($F448,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H448" s="7">
-        <f>IFERROR(VLOOKUP($F448,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I448" s="7"/>
       <c r="J448" s="7">
-        <f>IFERROR(VLOOKUP($F448,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -18168,16 +18026,16 @@
       </c>
       <c r="F449" s="7"/>
       <c r="G449" s="7">
-        <f>IFERROR(VLOOKUP($F449,$A:$B,2,0),0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H449" s="7">
-        <f>IFERROR(VLOOKUP($F449,$A:$D,3,0),0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I449" s="7"/>
       <c r="J449" s="7">
-        <f>IFERROR(VLOOKUP($F449,$A:$D,4,0),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -18196,16 +18054,16 @@
       </c>
       <c r="F450" s="7"/>
       <c r="G450" s="7">
-        <f>IFERROR(VLOOKUP($F450,$A:$B,2,0),0)</f>
+        <f t="shared" ref="G450:G467" si="21">IFERROR(VLOOKUP($F450,$A:$B,2,0),0)</f>
         <v>0</v>
       </c>
       <c r="H450" s="7">
-        <f>IFERROR(VLOOKUP($F450,$A:$D,3,0),0)</f>
+        <f t="shared" ref="H450:H467" si="22">IFERROR(VLOOKUP($F450,$A:$D,3,0),0)</f>
         <v>0</v>
       </c>
       <c r="I450" s="7"/>
       <c r="J450" s="7">
-        <f>IFERROR(VLOOKUP($F450,$A:$D,4,0),0)</f>
+        <f t="shared" ref="J450:J467" si="23">IFERROR(VLOOKUP($F450,$A:$D,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18224,16 +18082,16 @@
       </c>
       <c r="F451" s="7"/>
       <c r="G451" s="7">
-        <f>IFERROR(VLOOKUP($F451,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H451" s="7">
-        <f>IFERROR(VLOOKUP($F451,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I451" s="7"/>
       <c r="J451" s="7">
-        <f>IFERROR(VLOOKUP($F451,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18252,16 +18110,16 @@
       </c>
       <c r="F452" s="7"/>
       <c r="G452" s="7">
-        <f>IFERROR(VLOOKUP($F452,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H452" s="7">
-        <f>IFERROR(VLOOKUP($F452,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I452" s="7"/>
       <c r="J452" s="7">
-        <f>IFERROR(VLOOKUP($F452,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18280,16 +18138,16 @@
       </c>
       <c r="F453" s="7"/>
       <c r="G453" s="7">
-        <f>IFERROR(VLOOKUP($F453,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H453" s="7">
-        <f>IFERROR(VLOOKUP($F453,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I453" s="7"/>
       <c r="J453" s="7">
-        <f>IFERROR(VLOOKUP($F453,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18308,16 +18166,16 @@
       </c>
       <c r="F454" s="7"/>
       <c r="G454" s="7">
-        <f>IFERROR(VLOOKUP($F454,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H454" s="7">
-        <f>IFERROR(VLOOKUP($F454,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I454" s="7"/>
       <c r="J454" s="7">
-        <f>IFERROR(VLOOKUP($F454,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18336,16 +18194,16 @@
       </c>
       <c r="F455" s="7"/>
       <c r="G455" s="7">
-        <f>IFERROR(VLOOKUP($F455,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H455" s="7">
-        <f>IFERROR(VLOOKUP($F455,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I455" s="7"/>
       <c r="J455" s="7">
-        <f>IFERROR(VLOOKUP($F455,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18364,16 +18222,16 @@
       </c>
       <c r="F456" s="7"/>
       <c r="G456" s="7">
-        <f>IFERROR(VLOOKUP($F456,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H456" s="7">
-        <f>IFERROR(VLOOKUP($F456,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I456" s="7"/>
       <c r="J456" s="7">
-        <f>IFERROR(VLOOKUP($F456,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18392,16 +18250,16 @@
       </c>
       <c r="F457" s="7"/>
       <c r="G457" s="7">
-        <f>IFERROR(VLOOKUP($F457,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H457" s="7">
-        <f>IFERROR(VLOOKUP($F457,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I457" s="7"/>
       <c r="J457" s="7">
-        <f>IFERROR(VLOOKUP($F457,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18420,16 +18278,16 @@
       </c>
       <c r="F458" s="7"/>
       <c r="G458" s="7">
-        <f>IFERROR(VLOOKUP($F458,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H458" s="7">
-        <f>IFERROR(VLOOKUP($F458,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I458" s="7"/>
       <c r="J458" s="7">
-        <f>IFERROR(VLOOKUP($F458,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18448,16 +18306,16 @@
       </c>
       <c r="F459" s="7"/>
       <c r="G459" s="7">
-        <f>IFERROR(VLOOKUP($F459,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H459" s="7">
-        <f>IFERROR(VLOOKUP($F459,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I459" s="7"/>
       <c r="J459" s="7">
-        <f>IFERROR(VLOOKUP($F459,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18476,16 +18334,16 @@
       </c>
       <c r="F460" s="7"/>
       <c r="G460" s="7">
-        <f>IFERROR(VLOOKUP($F460,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H460" s="7">
-        <f>IFERROR(VLOOKUP($F460,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I460" s="7"/>
       <c r="J460" s="7">
-        <f>IFERROR(VLOOKUP($F460,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18504,16 +18362,16 @@
       </c>
       <c r="F461" s="7"/>
       <c r="G461" s="7">
-        <f>IFERROR(VLOOKUP($F461,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H461" s="7">
-        <f>IFERROR(VLOOKUP($F461,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I461" s="7"/>
       <c r="J461" s="7">
-        <f>IFERROR(VLOOKUP($F461,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18532,16 +18390,16 @@
       </c>
       <c r="F462" s="7"/>
       <c r="G462" s="7">
-        <f>IFERROR(VLOOKUP($F462,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H462" s="7">
-        <f>IFERROR(VLOOKUP($F462,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I462" s="7"/>
       <c r="J462" s="7">
-        <f>IFERROR(VLOOKUP($F462,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18560,16 +18418,16 @@
       </c>
       <c r="F463" s="7"/>
       <c r="G463" s="7">
-        <f>IFERROR(VLOOKUP($F463,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H463" s="7">
-        <f>IFERROR(VLOOKUP($F463,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I463" s="7"/>
       <c r="J463" s="7">
-        <f>IFERROR(VLOOKUP($F463,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18588,16 +18446,16 @@
       </c>
       <c r="F464" s="7"/>
       <c r="G464" s="7">
-        <f>IFERROR(VLOOKUP($F464,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H464" s="7">
-        <f>IFERROR(VLOOKUP($F464,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I464" s="7"/>
       <c r="J464" s="7">
-        <f>IFERROR(VLOOKUP($F464,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18616,16 +18474,16 @@
       </c>
       <c r="F465" s="7"/>
       <c r="G465" s="7">
-        <f>IFERROR(VLOOKUP($F465,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H465" s="7">
-        <f>IFERROR(VLOOKUP($F465,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I465" s="7"/>
       <c r="J465" s="7">
-        <f>IFERROR(VLOOKUP($F465,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18644,16 +18502,16 @@
       </c>
       <c r="F466" s="7"/>
       <c r="G466" s="7">
-        <f>IFERROR(VLOOKUP($F466,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H466" s="7">
-        <f>IFERROR(VLOOKUP($F466,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I466" s="7"/>
       <c r="J466" s="7">
-        <f>IFERROR(VLOOKUP($F466,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -18672,16 +18530,16 @@
       </c>
       <c r="F467" s="7"/>
       <c r="G467" s="7">
-        <f>IFERROR(VLOOKUP($F467,$A:$B,2,0),0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H467" s="7">
-        <f>IFERROR(VLOOKUP($F467,$A:$D,3,0),0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I467" s="7"/>
       <c r="J467" s="7">
-        <f>IFERROR(VLOOKUP($F467,$A:$D,4,0),0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -20428,103 +20286,142 @@
         <v>37881</v>
       </c>
     </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A592" s="13">
+        <v>79475749</v>
+      </c>
+      <c r="B592" s="13" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C592" s="13" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D592" s="36">
+        <v>68310</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L510"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A592:A1048576 A378:A410 A412:A581 A1:A372 A584:A590">
-    <cfRule type="duplicateValues" dxfId="33" priority="37"/>
+  <conditionalFormatting sqref="A593:A1048576 A378:A410 A412:A581 A1:A372 A584:A590">
+    <cfRule type="duplicateValues" dxfId="42" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45:F49">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A592:A1048576 A1:A581 A584:A590">
-    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+  <conditionalFormatting sqref="A593:A1048576 A1:A581 A584:A590">
+    <cfRule type="duplicateValues" dxfId="35" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A592:B1048576 A378:B379 A382:B410 A380:A381 A412:B581 A1:B122 A124:B176 A123 A178:B372 A177 A584:B590">
-    <cfRule type="duplicateValues" dxfId="24" priority="38"/>
+  <conditionalFormatting sqref="A593:B1048576 A378:B379 A382:B410 A380:A381 A412:B581 A1:B122 A124:B176 A123 A178:B372 A177 A584:B590">
+    <cfRule type="duplicateValues" dxfId="33" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A592:B1048576 A382:B410 A380:A381 A1:B122 A412:B581 A124:B176 A123 A178:B379 A177 A584:B590">
-    <cfRule type="duplicateValues" dxfId="23" priority="45"/>
+  <conditionalFormatting sqref="A593:B1048576 A382:B410 A380:A381 A1:B122 A412:B581 A124:B176 A123 A178:B379 A177 A584:B590">
+    <cfRule type="duplicateValues" dxfId="32" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C468:C581 C114:C389 C1:C112 C584:C590 C592:C1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="47"/>
+  <conditionalFormatting sqref="C468:C581 C114:C389 C1:C112 C584:C590 C593:C1048576">
+    <cfRule type="duplicateValues" dxfId="31" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="21" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B592:B1048576 B178:B581 B1:B122 B124:B176 B584:B590">
+  <conditionalFormatting sqref="B593:B1048576 B178:B581 B1:B122 B124:B176 B584:B590">
+    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A593:C1048576 A177 A1:C122 A124:C176 A123 C123 C177 A178:C581 A584:C590">
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F9">
+    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:A583">
+    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:A583">
+    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:B583">
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A582:B583">
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C582:C583">
+    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B582:B583">
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A592:C1048576 A177 A1:C122 A124:C176 A123 C123 C177 A178:C581 A584:C590">
+  <conditionalFormatting sqref="A582:C583">
     <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+  <conditionalFormatting sqref="A1:A590 A593:A1048576">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:A583">
+  <conditionalFormatting sqref="A591">
     <cfRule type="duplicateValues" dxfId="17" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:A583">
+  <conditionalFormatting sqref="A591">
     <cfRule type="duplicateValues" dxfId="16" priority="11"/>
     <cfRule type="duplicateValues" dxfId="15" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:B583">
+  <conditionalFormatting sqref="A591:B591">
     <cfRule type="duplicateValues" dxfId="14" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:B583">
+  <conditionalFormatting sqref="A591:B591">
     <cfRule type="duplicateValues" dxfId="13" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C582:C583">
+  <conditionalFormatting sqref="C591">
     <cfRule type="duplicateValues" dxfId="12" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B582:B583">
+  <conditionalFormatting sqref="B591">
     <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A582:C583">
+  <conditionalFormatting sqref="A591:C591">
     <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A590 A592:A1048576">
+  <conditionalFormatting sqref="A591">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A591">
+  <conditionalFormatting sqref="A592">
     <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A591">
+  <conditionalFormatting sqref="A592">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A591:B591">
+  <conditionalFormatting sqref="A592:B592">
     <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A591:B591">
+  <conditionalFormatting sqref="A592:B592">
     <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C591">
+  <conditionalFormatting sqref="C592">
     <cfRule type="duplicateValues" dxfId="3" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B591">
+  <conditionalFormatting sqref="B592">
     <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A591:C591">
+  <conditionalFormatting sqref="A592:C592">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A591">
+  <conditionalFormatting sqref="A592">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
